--- a/03_内部設計/022-クラス仕様書/util/ConnectionUtilのクラス仕様書.xlsx
+++ b/03_内部設計/022-クラス仕様書/util/ConnectionUtilのクラス仕様書.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A20E9B34-B099-4569-BC7D-60E5C393E340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8CB3F0B-831F-4CAB-A9D6-F1075C79C37C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="クラス仕様" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">クラス仕様!$A$1:$BI$21</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'メソッド仕様（getCon）'!$A$1:$BI$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'メソッド仕様（getCon）'!$A$1:$BI$38</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="72">
   <si>
     <t>クラス仕様書</t>
   </si>
@@ -315,56 +315,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>※2.1において、ClassNotFoundExceptionをcatchしたときは以下の処理を行う。</t>
-    <rPh sb="42" eb="44">
-      <t>イカ</t>
-    </rPh>
-    <rPh sb="45" eb="47">
-      <t>ショリ</t>
-    </rPh>
-    <rPh sb="48" eb="49">
-      <t>オコナ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>e</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1) 標準エラー出力で「JDBCドライバが見つかりません。」と出力する。</t>
-    <rPh sb="3" eb="5">
-      <t>ヒョウジュン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>シュツリョク</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="31" eb="33">
-      <t>シュツリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>2) printStackTraceメソッドで、コンソールに例外情報を出力する。</t>
-    <rPh sb="30" eb="32">
-      <t>レイガイ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="35" eb="37">
-      <t>シュツリョク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3) 例外をスローする。</t>
-    <rPh sb="3" eb="5">
-      <t>レイガイ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -390,10 +341,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>※3.2において、SQLExceptionをcatchしたときは以下の処理を行う。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>4) 戻り値を返す。</t>
     <rPh sb="3" eb="4">
       <t>モド</t>
@@ -407,15 +354,11 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>1) 標準エラー出力で「JDBCドライバが見つかりません。」と出力する。</t>
+    <t>※3.2において、SQLExceptionをcatchしたとき、スローする。</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>2) printStackTraceメソッドで、コンソールに例外情報を出力する。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>3) 例外をスローする。</t>
+    <t>※2.1において、ClassNotFoundExceptionをcatchしたとき、スローする。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -656,7 +599,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -714,9 +657,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -729,35 +669,17 @@
     <xf numFmtId="49" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -795,6 +717,42 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -809,24 +767,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1178,85 +1118,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="32" t="s">
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="31" t="s">
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="40" t="s">
         <v>29</v>
       </c>
-      <c r="S1" s="31"/>
-      <c r="T1" s="31"/>
-      <c r="U1" s="31"/>
-      <c r="V1" s="31"/>
-      <c r="W1" s="31"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="31"/>
-      <c r="Z1" s="31"/>
-      <c r="AA1" s="31"/>
-      <c r="AB1" s="32" t="s">
+      <c r="S1" s="40"/>
+      <c r="T1" s="40"/>
+      <c r="U1" s="40"/>
+      <c r="V1" s="40"/>
+      <c r="W1" s="40"/>
+      <c r="X1" s="40"/>
+      <c r="Y1" s="40"/>
+      <c r="Z1" s="40"/>
+      <c r="AA1" s="40"/>
+      <c r="AB1" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="AC1" s="32"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="31" t="s">
+      <c r="AC1" s="39"/>
+      <c r="AD1" s="39"/>
+      <c r="AE1" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="AF1" s="31"/>
-      <c r="AG1" s="31"/>
-      <c r="AH1" s="31"/>
-      <c r="AI1" s="31"/>
-      <c r="AJ1" s="31"/>
-      <c r="AK1" s="31"/>
-      <c r="AL1" s="31"/>
-      <c r="AM1" s="31"/>
-      <c r="AN1" s="31"/>
-      <c r="AO1" s="31"/>
-      <c r="AP1" s="31"/>
-      <c r="AQ1" s="32" t="s">
+      <c r="AF1" s="40"/>
+      <c r="AG1" s="40"/>
+      <c r="AH1" s="40"/>
+      <c r="AI1" s="40"/>
+      <c r="AJ1" s="40"/>
+      <c r="AK1" s="40"/>
+      <c r="AL1" s="40"/>
+      <c r="AM1" s="40"/>
+      <c r="AN1" s="40"/>
+      <c r="AO1" s="40"/>
+      <c r="AP1" s="40"/>
+      <c r="AQ1" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="AR1" s="32"/>
-      <c r="AS1" s="32"/>
-      <c r="AT1" s="31" t="s">
+      <c r="AR1" s="39"/>
+      <c r="AS1" s="39"/>
+      <c r="AT1" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="AU1" s="31"/>
-      <c r="AV1" s="31"/>
-      <c r="AW1" s="31"/>
-      <c r="AX1" s="31"/>
-      <c r="AY1" s="31"/>
-      <c r="AZ1" s="31"/>
-      <c r="BA1" s="32" t="s">
+      <c r="AU1" s="40"/>
+      <c r="AV1" s="40"/>
+      <c r="AW1" s="40"/>
+      <c r="AX1" s="40"/>
+      <c r="AY1" s="40"/>
+      <c r="AZ1" s="40"/>
+      <c r="BA1" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="BB1" s="32"/>
-      <c r="BC1" s="32"/>
-      <c r="BD1" s="29">
+      <c r="BB1" s="39"/>
+      <c r="BC1" s="39"/>
+      <c r="BD1" s="41">
         <v>45554</v>
       </c>
-      <c r="BE1" s="29"/>
-      <c r="BF1" s="29"/>
-      <c r="BG1" s="29"/>
-      <c r="BH1" s="29"/>
-      <c r="BI1" s="29"/>
+      <c r="BE1" s="41"/>
+      <c r="BF1" s="41"/>
+      <c r="BG1" s="41"/>
+      <c r="BH1" s="41"/>
+      <c r="BI1" s="41"/>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -1456,82 +1396,82 @@
       <c r="IX1" s="1"/>
     </row>
     <row r="2" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="32" t="s">
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
-      <c r="T2" s="33"/>
-      <c r="U2" s="33"/>
-      <c r="V2" s="33"/>
-      <c r="W2" s="33"/>
-      <c r="X2" s="33"/>
-      <c r="Y2" s="33"/>
-      <c r="Z2" s="33"/>
-      <c r="AA2" s="33"/>
-      <c r="AB2" s="32" t="s">
+      <c r="N2" s="39"/>
+      <c r="O2" s="39"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="45"/>
+      <c r="U2" s="45"/>
+      <c r="V2" s="45"/>
+      <c r="W2" s="45"/>
+      <c r="X2" s="45"/>
+      <c r="Y2" s="45"/>
+      <c r="Z2" s="45"/>
+      <c r="AA2" s="45"/>
+      <c r="AB2" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="31" t="str">
+      <c r="AC2" s="39"/>
+      <c r="AD2" s="39"/>
+      <c r="AE2" s="40" t="str">
         <f>G5</f>
         <v>ConnectionUtil</v>
       </c>
-      <c r="AF2" s="31"/>
-      <c r="AG2" s="31"/>
-      <c r="AH2" s="31"/>
-      <c r="AI2" s="31"/>
-      <c r="AJ2" s="31"/>
-      <c r="AK2" s="31"/>
-      <c r="AL2" s="31"/>
-      <c r="AM2" s="31"/>
-      <c r="AN2" s="31"/>
-      <c r="AO2" s="31"/>
-      <c r="AP2" s="31"/>
-      <c r="AQ2" s="32" t="s">
+      <c r="AF2" s="40"/>
+      <c r="AG2" s="40"/>
+      <c r="AH2" s="40"/>
+      <c r="AI2" s="40"/>
+      <c r="AJ2" s="40"/>
+      <c r="AK2" s="40"/>
+      <c r="AL2" s="40"/>
+      <c r="AM2" s="40"/>
+      <c r="AN2" s="40"/>
+      <c r="AO2" s="40"/>
+      <c r="AP2" s="40"/>
+      <c r="AQ2" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="AR2" s="32"/>
-      <c r="AS2" s="32"/>
-      <c r="AT2" s="31" t="s">
+      <c r="AR2" s="39"/>
+      <c r="AS2" s="39"/>
+      <c r="AT2" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AU2" s="31"/>
-      <c r="AV2" s="31"/>
-      <c r="AW2" s="31"/>
-      <c r="AX2" s="31"/>
-      <c r="AY2" s="31"/>
-      <c r="AZ2" s="31"/>
-      <c r="BA2" s="32" t="s">
+      <c r="AU2" s="40"/>
+      <c r="AV2" s="40"/>
+      <c r="AW2" s="40"/>
+      <c r="AX2" s="40"/>
+      <c r="AY2" s="40"/>
+      <c r="AZ2" s="40"/>
+      <c r="BA2" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="BB2" s="32"/>
-      <c r="BC2" s="32"/>
-      <c r="BD2" s="29">
+      <c r="BB2" s="39"/>
+      <c r="BC2" s="39"/>
+      <c r="BD2" s="41">
         <v>45566</v>
       </c>
-      <c r="BE2" s="29"/>
-      <c r="BF2" s="29"/>
-      <c r="BG2" s="29"/>
-      <c r="BH2" s="29"/>
-      <c r="BI2" s="29"/>
+      <c r="BE2" s="41"/>
+      <c r="BF2" s="41"/>
+      <c r="BG2" s="41"/>
+      <c r="BH2" s="41"/>
+      <c r="BI2" s="41"/>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -1794,1089 +1734,1097 @@
       <c r="BI3" s="3"/>
     </row>
     <row r="4" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="28" t="s">
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="28"/>
-      <c r="U4" s="28"/>
-      <c r="V4" s="28"/>
-      <c r="W4" s="28"/>
-      <c r="X4" s="28"/>
-      <c r="Y4" s="28"/>
-      <c r="Z4" s="28"/>
-      <c r="AA4" s="28"/>
-      <c r="AB4" s="28"/>
-      <c r="AC4" s="28"/>
-      <c r="AD4" s="28"/>
-      <c r="AE4" s="28"/>
-      <c r="AF4" s="28"/>
-      <c r="AG4" s="28"/>
-      <c r="AH4" s="28"/>
-      <c r="AI4" s="28"/>
-      <c r="AJ4" s="28"/>
-      <c r="AK4" s="28"/>
-      <c r="AL4" s="28"/>
-      <c r="AM4" s="28"/>
-      <c r="AN4" s="28"/>
-      <c r="AO4" s="28"/>
-      <c r="AP4" s="28"/>
-      <c r="AQ4" s="28"/>
-      <c r="AR4" s="28"/>
-      <c r="AS4" s="28"/>
-      <c r="AT4" s="28"/>
-      <c r="AU4" s="28"/>
-      <c r="AV4" s="28"/>
-      <c r="AW4" s="28"/>
-      <c r="AX4" s="28"/>
-      <c r="AY4" s="28"/>
-      <c r="AZ4" s="28"/>
-      <c r="BA4" s="28"/>
-      <c r="BB4" s="28"/>
-      <c r="BC4" s="28"/>
-      <c r="BD4" s="28"/>
-      <c r="BE4" s="28"/>
-      <c r="BF4" s="28"/>
-      <c r="BG4" s="28"/>
-      <c r="BH4" s="28"/>
-      <c r="BI4" s="28"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="43"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="43"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="43"/>
+      <c r="T4" s="43"/>
+      <c r="U4" s="43"/>
+      <c r="V4" s="43"/>
+      <c r="W4" s="43"/>
+      <c r="X4" s="43"/>
+      <c r="Y4" s="43"/>
+      <c r="Z4" s="43"/>
+      <c r="AA4" s="43"/>
+      <c r="AB4" s="43"/>
+      <c r="AC4" s="43"/>
+      <c r="AD4" s="43"/>
+      <c r="AE4" s="43"/>
+      <c r="AF4" s="43"/>
+      <c r="AG4" s="43"/>
+      <c r="AH4" s="43"/>
+      <c r="AI4" s="43"/>
+      <c r="AJ4" s="43"/>
+      <c r="AK4" s="43"/>
+      <c r="AL4" s="43"/>
+      <c r="AM4" s="43"/>
+      <c r="AN4" s="43"/>
+      <c r="AO4" s="43"/>
+      <c r="AP4" s="43"/>
+      <c r="AQ4" s="43"/>
+      <c r="AR4" s="43"/>
+      <c r="AS4" s="43"/>
+      <c r="AT4" s="43"/>
+      <c r="AU4" s="43"/>
+      <c r="AV4" s="43"/>
+      <c r="AW4" s="43"/>
+      <c r="AX4" s="43"/>
+      <c r="AY4" s="43"/>
+      <c r="AZ4" s="43"/>
+      <c r="BA4" s="43"/>
+      <c r="BB4" s="43"/>
+      <c r="BC4" s="43"/>
+      <c r="BD4" s="43"/>
+      <c r="BE4" s="43"/>
+      <c r="BF4" s="43"/>
+      <c r="BG4" s="43"/>
+      <c r="BH4" s="43"/>
+      <c r="BI4" s="43"/>
     </row>
     <row r="5" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="28" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="43" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="28"/>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="28"/>
-      <c r="T5" s="28"/>
-      <c r="U5" s="28"/>
-      <c r="V5" s="28"/>
-      <c r="W5" s="28"/>
-      <c r="X5" s="28"/>
-      <c r="Y5" s="28"/>
-      <c r="Z5" s="28"/>
-      <c r="AA5" s="28"/>
-      <c r="AB5" s="28"/>
-      <c r="AC5" s="28"/>
-      <c r="AD5" s="28"/>
-      <c r="AE5" s="28"/>
-      <c r="AF5" s="28"/>
-      <c r="AG5" s="28"/>
-      <c r="AH5" s="28"/>
-      <c r="AI5" s="28"/>
-      <c r="AJ5" s="28"/>
-      <c r="AK5" s="28"/>
-      <c r="AL5" s="28"/>
-      <c r="AM5" s="28"/>
-      <c r="AN5" s="28"/>
-      <c r="AO5" s="28"/>
-      <c r="AP5" s="28"/>
-      <c r="AQ5" s="28"/>
-      <c r="AR5" s="28"/>
-      <c r="AS5" s="28"/>
-      <c r="AT5" s="28"/>
-      <c r="AU5" s="28"/>
-      <c r="AV5" s="28"/>
-      <c r="AW5" s="28"/>
-      <c r="AX5" s="28"/>
-      <c r="AY5" s="28"/>
-      <c r="AZ5" s="28"/>
-      <c r="BA5" s="28"/>
-      <c r="BB5" s="28"/>
-      <c r="BC5" s="28"/>
-      <c r="BD5" s="28"/>
-      <c r="BE5" s="28"/>
-      <c r="BF5" s="28"/>
-      <c r="BG5" s="28"/>
-      <c r="BH5" s="28"/>
-      <c r="BI5" s="28"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="43"/>
+      <c r="O5" s="43"/>
+      <c r="P5" s="43"/>
+      <c r="Q5" s="43"/>
+      <c r="R5" s="43"/>
+      <c r="S5" s="43"/>
+      <c r="T5" s="43"/>
+      <c r="U5" s="43"/>
+      <c r="V5" s="43"/>
+      <c r="W5" s="43"/>
+      <c r="X5" s="43"/>
+      <c r="Y5" s="43"/>
+      <c r="Z5" s="43"/>
+      <c r="AA5" s="43"/>
+      <c r="AB5" s="43"/>
+      <c r="AC5" s="43"/>
+      <c r="AD5" s="43"/>
+      <c r="AE5" s="43"/>
+      <c r="AF5" s="43"/>
+      <c r="AG5" s="43"/>
+      <c r="AH5" s="43"/>
+      <c r="AI5" s="43"/>
+      <c r="AJ5" s="43"/>
+      <c r="AK5" s="43"/>
+      <c r="AL5" s="43"/>
+      <c r="AM5" s="43"/>
+      <c r="AN5" s="43"/>
+      <c r="AO5" s="43"/>
+      <c r="AP5" s="43"/>
+      <c r="AQ5" s="43"/>
+      <c r="AR5" s="43"/>
+      <c r="AS5" s="43"/>
+      <c r="AT5" s="43"/>
+      <c r="AU5" s="43"/>
+      <c r="AV5" s="43"/>
+      <c r="AW5" s="43"/>
+      <c r="AX5" s="43"/>
+      <c r="AY5" s="43"/>
+      <c r="AZ5" s="43"/>
+      <c r="BA5" s="43"/>
+      <c r="BB5" s="43"/>
+      <c r="BC5" s="43"/>
+      <c r="BD5" s="43"/>
+      <c r="BE5" s="43"/>
+      <c r="BF5" s="43"/>
+      <c r="BG5" s="43"/>
+      <c r="BH5" s="43"/>
+      <c r="BI5" s="43"/>
     </row>
     <row r="6" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="28" t="s">
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="28"/>
-      <c r="R6" s="28"/>
-      <c r="S6" s="28"/>
-      <c r="T6" s="28"/>
-      <c r="U6" s="28"/>
-      <c r="V6" s="28"/>
-      <c r="W6" s="28"/>
-      <c r="X6" s="28"/>
-      <c r="Y6" s="28"/>
-      <c r="Z6" s="28"/>
-      <c r="AA6" s="28"/>
-      <c r="AB6" s="28"/>
-      <c r="AC6" s="28"/>
-      <c r="AD6" s="25" t="s">
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="43"/>
+      <c r="M6" s="43"/>
+      <c r="N6" s="43"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="43"/>
+      <c r="Q6" s="43"/>
+      <c r="R6" s="43"/>
+      <c r="S6" s="43"/>
+      <c r="T6" s="43"/>
+      <c r="U6" s="43"/>
+      <c r="V6" s="43"/>
+      <c r="W6" s="43"/>
+      <c r="X6" s="43"/>
+      <c r="Y6" s="43"/>
+      <c r="Z6" s="43"/>
+      <c r="AA6" s="43"/>
+      <c r="AB6" s="43"/>
+      <c r="AC6" s="43"/>
+      <c r="AD6" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="AE6" s="25"/>
-      <c r="AF6" s="25"/>
-      <c r="AG6" s="25"/>
-      <c r="AH6" s="25"/>
-      <c r="AI6" s="25"/>
-      <c r="AJ6" s="28" t="s">
+      <c r="AE6" s="42"/>
+      <c r="AF6" s="42"/>
+      <c r="AG6" s="42"/>
+      <c r="AH6" s="42"/>
+      <c r="AI6" s="42"/>
+      <c r="AJ6" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="AK6" s="28"/>
-      <c r="AL6" s="28"/>
-      <c r="AM6" s="28"/>
-      <c r="AN6" s="28"/>
-      <c r="AO6" s="28"/>
-      <c r="AP6" s="28"/>
-      <c r="AQ6" s="28"/>
-      <c r="AR6" s="28"/>
-      <c r="AS6" s="28"/>
-      <c r="AT6" s="28"/>
-      <c r="AU6" s="28"/>
-      <c r="AV6" s="28"/>
-      <c r="AW6" s="28"/>
-      <c r="AX6" s="28"/>
-      <c r="AY6" s="28"/>
-      <c r="AZ6" s="28"/>
-      <c r="BA6" s="28"/>
-      <c r="BB6" s="28"/>
-      <c r="BC6" s="28"/>
-      <c r="BD6" s="28"/>
-      <c r="BE6" s="28"/>
-      <c r="BF6" s="28"/>
-      <c r="BG6" s="28"/>
-      <c r="BH6" s="28"/>
-      <c r="BI6" s="28"/>
+      <c r="AK6" s="43"/>
+      <c r="AL6" s="43"/>
+      <c r="AM6" s="43"/>
+      <c r="AN6" s="43"/>
+      <c r="AO6" s="43"/>
+      <c r="AP6" s="43"/>
+      <c r="AQ6" s="43"/>
+      <c r="AR6" s="43"/>
+      <c r="AS6" s="43"/>
+      <c r="AT6" s="43"/>
+      <c r="AU6" s="43"/>
+      <c r="AV6" s="43"/>
+      <c r="AW6" s="43"/>
+      <c r="AX6" s="43"/>
+      <c r="AY6" s="43"/>
+      <c r="AZ6" s="43"/>
+      <c r="BA6" s="43"/>
+      <c r="BB6" s="43"/>
+      <c r="BC6" s="43"/>
+      <c r="BD6" s="43"/>
+      <c r="BE6" s="43"/>
+      <c r="BF6" s="43"/>
+      <c r="BG6" s="43"/>
+      <c r="BH6" s="43"/>
+      <c r="BI6" s="43"/>
     </row>
     <row r="8" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25" t="s">
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="25"/>
-      <c r="O8" s="25"/>
-      <c r="P8" s="25"/>
-      <c r="Q8" s="25"/>
-      <c r="R8" s="25"/>
-      <c r="S8" s="25"/>
-      <c r="T8" s="25"/>
-      <c r="U8" s="25" t="s">
+      <c r="L8" s="42"/>
+      <c r="M8" s="42"/>
+      <c r="N8" s="42"/>
+      <c r="O8" s="42"/>
+      <c r="P8" s="42"/>
+      <c r="Q8" s="42"/>
+      <c r="R8" s="42"/>
+      <c r="S8" s="42"/>
+      <c r="T8" s="42"/>
+      <c r="U8" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="V8" s="25"/>
-      <c r="W8" s="25"/>
-      <c r="X8" s="25"/>
-      <c r="Y8" s="25"/>
-      <c r="Z8" s="25"/>
-      <c r="AA8" s="25"/>
-      <c r="AB8" s="25"/>
-      <c r="AC8" s="25"/>
-      <c r="AD8" s="25"/>
-      <c r="AE8" s="25" t="s">
+      <c r="V8" s="42"/>
+      <c r="W8" s="42"/>
+      <c r="X8" s="42"/>
+      <c r="Y8" s="42"/>
+      <c r="Z8" s="42"/>
+      <c r="AA8" s="42"/>
+      <c r="AB8" s="42"/>
+      <c r="AC8" s="42"/>
+      <c r="AD8" s="42"/>
+      <c r="AE8" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="AF8" s="25"/>
-      <c r="AG8" s="25"/>
-      <c r="AH8" s="25"/>
-      <c r="AI8" s="25"/>
-      <c r="AJ8" s="25"/>
-      <c r="AK8" s="25"/>
-      <c r="AL8" s="25"/>
-      <c r="AM8" s="25"/>
-      <c r="AN8" s="25"/>
-      <c r="AO8" s="25" t="s">
+      <c r="AF8" s="42"/>
+      <c r="AG8" s="42"/>
+      <c r="AH8" s="42"/>
+      <c r="AI8" s="42"/>
+      <c r="AJ8" s="42"/>
+      <c r="AK8" s="42"/>
+      <c r="AL8" s="42"/>
+      <c r="AM8" s="42"/>
+      <c r="AN8" s="42"/>
+      <c r="AO8" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="AP8" s="25"/>
-      <c r="AQ8" s="25"/>
-      <c r="AR8" s="25"/>
-      <c r="AS8" s="25"/>
-      <c r="AT8" s="25"/>
-      <c r="AU8" s="25"/>
-      <c r="AV8" s="25"/>
-      <c r="AW8" s="25"/>
-      <c r="AX8" s="25"/>
-      <c r="AY8" s="25"/>
-      <c r="AZ8" s="25"/>
-      <c r="BA8" s="25"/>
-      <c r="BB8" s="25"/>
-      <c r="BC8" s="25"/>
-      <c r="BD8" s="25"/>
-      <c r="BE8" s="25"/>
-      <c r="BF8" s="25"/>
-      <c r="BG8" s="25"/>
-      <c r="BH8" s="25"/>
-      <c r="BI8" s="25"/>
+      <c r="AP8" s="42"/>
+      <c r="AQ8" s="42"/>
+      <c r="AR8" s="42"/>
+      <c r="AS8" s="42"/>
+      <c r="AT8" s="42"/>
+      <c r="AU8" s="42"/>
+      <c r="AV8" s="42"/>
+      <c r="AW8" s="42"/>
+      <c r="AX8" s="42"/>
+      <c r="AY8" s="42"/>
+      <c r="AZ8" s="42"/>
+      <c r="BA8" s="42"/>
+      <c r="BB8" s="42"/>
+      <c r="BC8" s="42"/>
+      <c r="BD8" s="42"/>
+      <c r="BE8" s="42"/>
+      <c r="BF8" s="42"/>
+      <c r="BG8" s="42"/>
+      <c r="BH8" s="42"/>
+      <c r="BI8" s="42"/>
     </row>
     <row r="9" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="34" t="s">
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="L9" s="35"/>
-      <c r="M9" s="35"/>
-      <c r="N9" s="35"/>
-      <c r="O9" s="35"/>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="35"/>
-      <c r="R9" s="35"/>
-      <c r="S9" s="35"/>
-      <c r="T9" s="36"/>
-      <c r="U9" s="34" t="s">
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="28"/>
+      <c r="T9" s="29"/>
+      <c r="U9" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="V9" s="35"/>
-      <c r="W9" s="35"/>
-      <c r="X9" s="35"/>
-      <c r="Y9" s="35"/>
-      <c r="Z9" s="35"/>
-      <c r="AA9" s="35"/>
-      <c r="AB9" s="35"/>
-      <c r="AC9" s="35"/>
-      <c r="AD9" s="36"/>
-      <c r="AE9" s="40" t="s">
+      <c r="V9" s="28"/>
+      <c r="W9" s="28"/>
+      <c r="X9" s="28"/>
+      <c r="Y9" s="28"/>
+      <c r="Z9" s="28"/>
+      <c r="AA9" s="28"/>
+      <c r="AB9" s="28"/>
+      <c r="AC9" s="28"/>
+      <c r="AD9" s="29"/>
+      <c r="AE9" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="AF9" s="41"/>
-      <c r="AG9" s="41"/>
-      <c r="AH9" s="41"/>
-      <c r="AI9" s="41"/>
-      <c r="AJ9" s="41"/>
-      <c r="AK9" s="41"/>
-      <c r="AL9" s="41"/>
-      <c r="AM9" s="41"/>
-      <c r="AN9" s="42"/>
-      <c r="AO9" s="34" t="s">
+      <c r="AF9" s="34"/>
+      <c r="AG9" s="34"/>
+      <c r="AH9" s="34"/>
+      <c r="AI9" s="34"/>
+      <c r="AJ9" s="34"/>
+      <c r="AK9" s="34"/>
+      <c r="AL9" s="34"/>
+      <c r="AM9" s="34"/>
+      <c r="AN9" s="35"/>
+      <c r="AO9" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="AP9" s="35"/>
-      <c r="AQ9" s="35"/>
-      <c r="AR9" s="35"/>
-      <c r="AS9" s="35"/>
-      <c r="AT9" s="35"/>
-      <c r="AU9" s="35"/>
-      <c r="AV9" s="35"/>
-      <c r="AW9" s="35"/>
-      <c r="AX9" s="35"/>
-      <c r="AY9" s="35"/>
-      <c r="AZ9" s="35"/>
-      <c r="BA9" s="35"/>
-      <c r="BB9" s="35"/>
-      <c r="BC9" s="35"/>
-      <c r="BD9" s="35"/>
-      <c r="BE9" s="35"/>
-      <c r="BF9" s="35"/>
-      <c r="BG9" s="35"/>
-      <c r="BH9" s="35"/>
-      <c r="BI9" s="36"/>
+      <c r="AP9" s="28"/>
+      <c r="AQ9" s="28"/>
+      <c r="AR9" s="28"/>
+      <c r="AS9" s="28"/>
+      <c r="AT9" s="28"/>
+      <c r="AU9" s="28"/>
+      <c r="AV9" s="28"/>
+      <c r="AW9" s="28"/>
+      <c r="AX9" s="28"/>
+      <c r="AY9" s="28"/>
+      <c r="AZ9" s="28"/>
+      <c r="BA9" s="28"/>
+      <c r="BB9" s="28"/>
+      <c r="BC9" s="28"/>
+      <c r="BD9" s="28"/>
+      <c r="BE9" s="28"/>
+      <c r="BF9" s="28"/>
+      <c r="BG9" s="28"/>
+      <c r="BH9" s="28"/>
+      <c r="BI9" s="29"/>
     </row>
     <row r="10" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="37"/>
-      <c r="B10" s="38"/>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
-      <c r="J10" s="39"/>
-      <c r="K10" s="37"/>
-      <c r="L10" s="38"/>
-      <c r="M10" s="38"/>
-      <c r="N10" s="38"/>
-      <c r="O10" s="38"/>
-      <c r="P10" s="38"/>
-      <c r="Q10" s="38"/>
-      <c r="R10" s="38"/>
-      <c r="S10" s="38"/>
-      <c r="T10" s="39"/>
-      <c r="U10" s="37"/>
-      <c r="V10" s="38"/>
-      <c r="W10" s="38"/>
-      <c r="X10" s="38"/>
-      <c r="Y10" s="38"/>
-      <c r="Z10" s="38"/>
-      <c r="AA10" s="38"/>
-      <c r="AB10" s="38"/>
-      <c r="AC10" s="38"/>
-      <c r="AD10" s="39"/>
-      <c r="AE10" s="43"/>
-      <c r="AF10" s="44"/>
-      <c r="AG10" s="44"/>
-      <c r="AH10" s="44"/>
-      <c r="AI10" s="44"/>
-      <c r="AJ10" s="44"/>
-      <c r="AK10" s="44"/>
-      <c r="AL10" s="44"/>
-      <c r="AM10" s="44"/>
-      <c r="AN10" s="45"/>
-      <c r="AO10" s="37"/>
-      <c r="AP10" s="38"/>
-      <c r="AQ10" s="38"/>
-      <c r="AR10" s="38"/>
-      <c r="AS10" s="38"/>
-      <c r="AT10" s="38"/>
-      <c r="AU10" s="38"/>
-      <c r="AV10" s="38"/>
-      <c r="AW10" s="38"/>
-      <c r="AX10" s="38"/>
-      <c r="AY10" s="38"/>
-      <c r="AZ10" s="38"/>
-      <c r="BA10" s="38"/>
-      <c r="BB10" s="38"/>
-      <c r="BC10" s="38"/>
-      <c r="BD10" s="38"/>
-      <c r="BE10" s="38"/>
-      <c r="BF10" s="38"/>
-      <c r="BG10" s="38"/>
-      <c r="BH10" s="38"/>
-      <c r="BI10" s="39"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="30"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="32"/>
+      <c r="U10" s="30"/>
+      <c r="V10" s="31"/>
+      <c r="W10" s="31"/>
+      <c r="X10" s="31"/>
+      <c r="Y10" s="31"/>
+      <c r="Z10" s="31"/>
+      <c r="AA10" s="31"/>
+      <c r="AB10" s="31"/>
+      <c r="AC10" s="31"/>
+      <c r="AD10" s="32"/>
+      <c r="AE10" s="36"/>
+      <c r="AF10" s="37"/>
+      <c r="AG10" s="37"/>
+      <c r="AH10" s="37"/>
+      <c r="AI10" s="37"/>
+      <c r="AJ10" s="37"/>
+      <c r="AK10" s="37"/>
+      <c r="AL10" s="37"/>
+      <c r="AM10" s="37"/>
+      <c r="AN10" s="38"/>
+      <c r="AO10" s="30"/>
+      <c r="AP10" s="31"/>
+      <c r="AQ10" s="31"/>
+      <c r="AR10" s="31"/>
+      <c r="AS10" s="31"/>
+      <c r="AT10" s="31"/>
+      <c r="AU10" s="31"/>
+      <c r="AV10" s="31"/>
+      <c r="AW10" s="31"/>
+      <c r="AX10" s="31"/>
+      <c r="AY10" s="31"/>
+      <c r="AZ10" s="31"/>
+      <c r="BA10" s="31"/>
+      <c r="BB10" s="31"/>
+      <c r="BC10" s="31"/>
+      <c r="BD10" s="31"/>
+      <c r="BE10" s="31"/>
+      <c r="BF10" s="31"/>
+      <c r="BG10" s="31"/>
+      <c r="BH10" s="31"/>
+      <c r="BI10" s="32"/>
     </row>
     <row r="11" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="26" t="s">
+      <c r="A11" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-      <c r="D11" s="26"/>
-      <c r="E11" s="26"/>
-      <c r="F11" s="26"/>
-      <c r="G11" s="26"/>
-      <c r="H11" s="26"/>
-      <c r="I11" s="26"/>
-      <c r="J11" s="26"/>
-      <c r="K11" s="26" t="s">
+      <c r="B11" s="47"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="47"/>
+      <c r="E11" s="47"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="47"/>
+      <c r="H11" s="47"/>
+      <c r="I11" s="47"/>
+      <c r="J11" s="47"/>
+      <c r="K11" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="26"/>
-      <c r="O11" s="26"/>
-      <c r="P11" s="26"/>
-      <c r="Q11" s="26"/>
-      <c r="R11" s="26"/>
-      <c r="S11" s="26"/>
-      <c r="T11" s="26"/>
-      <c r="U11" s="26" t="s">
+      <c r="L11" s="47"/>
+      <c r="M11" s="47"/>
+      <c r="N11" s="47"/>
+      <c r="O11" s="47"/>
+      <c r="P11" s="47"/>
+      <c r="Q11" s="47"/>
+      <c r="R11" s="47"/>
+      <c r="S11" s="47"/>
+      <c r="T11" s="47"/>
+      <c r="U11" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="V11" s="26"/>
-      <c r="W11" s="26"/>
-      <c r="X11" s="26"/>
-      <c r="Y11" s="26"/>
-      <c r="Z11" s="26"/>
-      <c r="AA11" s="26"/>
-      <c r="AB11" s="26"/>
-      <c r="AC11" s="26"/>
-      <c r="AD11" s="26"/>
-      <c r="AE11" s="26" t="s">
+      <c r="V11" s="47"/>
+      <c r="W11" s="47"/>
+      <c r="X11" s="47"/>
+      <c r="Y11" s="47"/>
+      <c r="Z11" s="47"/>
+      <c r="AA11" s="47"/>
+      <c r="AB11" s="47"/>
+      <c r="AC11" s="47"/>
+      <c r="AD11" s="47"/>
+      <c r="AE11" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="AF11" s="26"/>
-      <c r="AG11" s="26"/>
-      <c r="AH11" s="26"/>
-      <c r="AI11" s="26"/>
-      <c r="AJ11" s="26"/>
-      <c r="AK11" s="26"/>
-      <c r="AL11" s="26"/>
-      <c r="AM11" s="26"/>
-      <c r="AN11" s="26"/>
-      <c r="AO11" s="27" t="s">
+      <c r="AF11" s="47"/>
+      <c r="AG11" s="47"/>
+      <c r="AH11" s="47"/>
+      <c r="AI11" s="47"/>
+      <c r="AJ11" s="47"/>
+      <c r="AK11" s="47"/>
+      <c r="AL11" s="47"/>
+      <c r="AM11" s="47"/>
+      <c r="AN11" s="47"/>
+      <c r="AO11" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="AP11" s="27"/>
-      <c r="AQ11" s="27"/>
-      <c r="AR11" s="27"/>
-      <c r="AS11" s="27"/>
-      <c r="AT11" s="27"/>
-      <c r="AU11" s="27"/>
-      <c r="AV11" s="27"/>
-      <c r="AW11" s="27"/>
-      <c r="AX11" s="27"/>
-      <c r="AY11" s="27"/>
-      <c r="AZ11" s="27"/>
-      <c r="BA11" s="27"/>
-      <c r="BB11" s="27"/>
-      <c r="BC11" s="27"/>
-      <c r="BD11" s="27"/>
-      <c r="BE11" s="27"/>
-      <c r="BF11" s="27"/>
-      <c r="BG11" s="27"/>
-      <c r="BH11" s="27"/>
-      <c r="BI11" s="27"/>
+      <c r="AP11" s="26"/>
+      <c r="AQ11" s="26"/>
+      <c r="AR11" s="26"/>
+      <c r="AS11" s="26"/>
+      <c r="AT11" s="26"/>
+      <c r="AU11" s="26"/>
+      <c r="AV11" s="26"/>
+      <c r="AW11" s="26"/>
+      <c r="AX11" s="26"/>
+      <c r="AY11" s="26"/>
+      <c r="AZ11" s="26"/>
+      <c r="BA11" s="26"/>
+      <c r="BB11" s="26"/>
+      <c r="BC11" s="26"/>
+      <c r="BD11" s="26"/>
+      <c r="BE11" s="26"/>
+      <c r="BF11" s="26"/>
+      <c r="BG11" s="26"/>
+      <c r="BH11" s="26"/>
+      <c r="BI11" s="26"/>
     </row>
     <row r="12" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-      <c r="D12" s="26"/>
-      <c r="E12" s="26"/>
-      <c r="F12" s="26"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="26"/>
-      <c r="J12" s="26"/>
-      <c r="K12" s="26" t="s">
+      <c r="B12" s="47"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="47"/>
+      <c r="J12" s="47"/>
+      <c r="K12" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="L12" s="26"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="26"/>
-      <c r="O12" s="26"/>
-      <c r="P12" s="26"/>
-      <c r="Q12" s="26"/>
-      <c r="R12" s="26"/>
-      <c r="S12" s="26"/>
-      <c r="T12" s="26"/>
-      <c r="U12" s="26" t="s">
+      <c r="L12" s="47"/>
+      <c r="M12" s="47"/>
+      <c r="N12" s="47"/>
+      <c r="O12" s="47"/>
+      <c r="P12" s="47"/>
+      <c r="Q12" s="47"/>
+      <c r="R12" s="47"/>
+      <c r="S12" s="47"/>
+      <c r="T12" s="47"/>
+      <c r="U12" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="V12" s="26"/>
-      <c r="W12" s="26"/>
-      <c r="X12" s="26"/>
-      <c r="Y12" s="26"/>
-      <c r="Z12" s="26"/>
-      <c r="AA12" s="26"/>
-      <c r="AB12" s="26"/>
-      <c r="AC12" s="26"/>
-      <c r="AD12" s="26"/>
-      <c r="AE12" s="26" t="s">
+      <c r="V12" s="47"/>
+      <c r="W12" s="47"/>
+      <c r="X12" s="47"/>
+      <c r="Y12" s="47"/>
+      <c r="Z12" s="47"/>
+      <c r="AA12" s="47"/>
+      <c r="AB12" s="47"/>
+      <c r="AC12" s="47"/>
+      <c r="AD12" s="47"/>
+      <c r="AE12" s="47" t="s">
         <v>45</v>
       </c>
-      <c r="AF12" s="26"/>
-      <c r="AG12" s="26"/>
-      <c r="AH12" s="26"/>
-      <c r="AI12" s="26"/>
-      <c r="AJ12" s="26"/>
-      <c r="AK12" s="26"/>
-      <c r="AL12" s="26"/>
-      <c r="AM12" s="26"/>
-      <c r="AN12" s="26"/>
-      <c r="AO12" s="27" t="s">
+      <c r="AF12" s="47"/>
+      <c r="AG12" s="47"/>
+      <c r="AH12" s="47"/>
+      <c r="AI12" s="47"/>
+      <c r="AJ12" s="47"/>
+      <c r="AK12" s="47"/>
+      <c r="AL12" s="47"/>
+      <c r="AM12" s="47"/>
+      <c r="AN12" s="47"/>
+      <c r="AO12" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="AP12" s="27"/>
-      <c r="AQ12" s="27"/>
-      <c r="AR12" s="27"/>
-      <c r="AS12" s="27"/>
-      <c r="AT12" s="27"/>
-      <c r="AU12" s="27"/>
-      <c r="AV12" s="27"/>
-      <c r="AW12" s="27"/>
-      <c r="AX12" s="27"/>
-      <c r="AY12" s="27"/>
-      <c r="AZ12" s="27"/>
-      <c r="BA12" s="27"/>
-      <c r="BB12" s="27"/>
-      <c r="BC12" s="27"/>
-      <c r="BD12" s="27"/>
-      <c r="BE12" s="27"/>
-      <c r="BF12" s="27"/>
-      <c r="BG12" s="27"/>
-      <c r="BH12" s="27"/>
-      <c r="BI12" s="27"/>
+      <c r="AP12" s="26"/>
+      <c r="AQ12" s="26"/>
+      <c r="AR12" s="26"/>
+      <c r="AS12" s="26"/>
+      <c r="AT12" s="26"/>
+      <c r="AU12" s="26"/>
+      <c r="AV12" s="26"/>
+      <c r="AW12" s="26"/>
+      <c r="AX12" s="26"/>
+      <c r="AY12" s="26"/>
+      <c r="AZ12" s="26"/>
+      <c r="BA12" s="26"/>
+      <c r="BB12" s="26"/>
+      <c r="BC12" s="26"/>
+      <c r="BD12" s="26"/>
+      <c r="BE12" s="26"/>
+      <c r="BF12" s="26"/>
+      <c r="BG12" s="26"/>
+      <c r="BH12" s="26"/>
+      <c r="BI12" s="26"/>
     </row>
     <row r="13" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="26"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="26"/>
-      <c r="M13" s="26"/>
-      <c r="N13" s="26"/>
-      <c r="O13" s="26"/>
-      <c r="P13" s="26"/>
-      <c r="Q13" s="26"/>
-      <c r="R13" s="26"/>
-      <c r="S13" s="26"/>
-      <c r="T13" s="26"/>
-      <c r="U13" s="26"/>
-      <c r="V13" s="26"/>
-      <c r="W13" s="26"/>
-      <c r="X13" s="26"/>
-      <c r="Y13" s="26"/>
-      <c r="Z13" s="26"/>
-      <c r="AA13" s="26"/>
-      <c r="AB13" s="26"/>
-      <c r="AC13" s="26"/>
-      <c r="AD13" s="26"/>
-      <c r="AE13" s="26"/>
-      <c r="AF13" s="26"/>
-      <c r="AG13" s="26"/>
-      <c r="AH13" s="26"/>
-      <c r="AI13" s="26"/>
-      <c r="AJ13" s="26"/>
-      <c r="AK13" s="26"/>
-      <c r="AL13" s="26"/>
-      <c r="AM13" s="26"/>
-      <c r="AN13" s="26"/>
-      <c r="AO13" s="26"/>
-      <c r="AP13" s="26"/>
-      <c r="AQ13" s="26"/>
-      <c r="AR13" s="26"/>
-      <c r="AS13" s="26"/>
-      <c r="AT13" s="26"/>
-      <c r="AU13" s="26"/>
-      <c r="AV13" s="26"/>
-      <c r="AW13" s="26"/>
-      <c r="AX13" s="26"/>
-      <c r="AY13" s="26"/>
-      <c r="AZ13" s="26"/>
-      <c r="BA13" s="26"/>
-      <c r="BB13" s="26"/>
-      <c r="BC13" s="26"/>
-      <c r="BD13" s="26"/>
-      <c r="BE13" s="26"/>
-      <c r="BF13" s="26"/>
-      <c r="BG13" s="26"/>
-      <c r="BH13" s="26"/>
-      <c r="BI13" s="26"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="47"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="47"/>
+      <c r="K13" s="47"/>
+      <c r="L13" s="47"/>
+      <c r="M13" s="47"/>
+      <c r="N13" s="47"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="47"/>
+      <c r="Q13" s="47"/>
+      <c r="R13" s="47"/>
+      <c r="S13" s="47"/>
+      <c r="T13" s="47"/>
+      <c r="U13" s="47"/>
+      <c r="V13" s="47"/>
+      <c r="W13" s="47"/>
+      <c r="X13" s="47"/>
+      <c r="Y13" s="47"/>
+      <c r="Z13" s="47"/>
+      <c r="AA13" s="47"/>
+      <c r="AB13" s="47"/>
+      <c r="AC13" s="47"/>
+      <c r="AD13" s="47"/>
+      <c r="AE13" s="47"/>
+      <c r="AF13" s="47"/>
+      <c r="AG13" s="47"/>
+      <c r="AH13" s="47"/>
+      <c r="AI13" s="47"/>
+      <c r="AJ13" s="47"/>
+      <c r="AK13" s="47"/>
+      <c r="AL13" s="47"/>
+      <c r="AM13" s="47"/>
+      <c r="AN13" s="47"/>
+      <c r="AO13" s="47"/>
+      <c r="AP13" s="47"/>
+      <c r="AQ13" s="47"/>
+      <c r="AR13" s="47"/>
+      <c r="AS13" s="47"/>
+      <c r="AT13" s="47"/>
+      <c r="AU13" s="47"/>
+      <c r="AV13" s="47"/>
+      <c r="AW13" s="47"/>
+      <c r="AX13" s="47"/>
+      <c r="AY13" s="47"/>
+      <c r="AZ13" s="47"/>
+      <c r="BA13" s="47"/>
+      <c r="BB13" s="47"/>
+      <c r="BC13" s="47"/>
+      <c r="BD13" s="47"/>
+      <c r="BE13" s="47"/>
+      <c r="BF13" s="47"/>
+      <c r="BG13" s="47"/>
+      <c r="BH13" s="47"/>
+      <c r="BI13" s="47"/>
     </row>
     <row r="15" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="25"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="25"/>
-      <c r="N15" s="25"/>
-      <c r="O15" s="25"/>
-      <c r="P15" s="25"/>
-      <c r="Q15" s="25"/>
-      <c r="R15" s="25"/>
-      <c r="S15" s="25"/>
-      <c r="T15" s="25"/>
-      <c r="U15" s="25"/>
-      <c r="V15" s="25"/>
-      <c r="W15" s="25"/>
-      <c r="X15" s="25"/>
-      <c r="Y15" s="25"/>
-      <c r="Z15" s="25"/>
-      <c r="AA15" s="25"/>
-      <c r="AB15" s="25"/>
-      <c r="AC15" s="25"/>
-      <c r="AD15" s="25"/>
-      <c r="AE15" s="25"/>
-      <c r="AF15" s="25"/>
-      <c r="AG15" s="25"/>
-      <c r="AH15" s="25"/>
-      <c r="AI15" s="25"/>
-      <c r="AJ15" s="25"/>
-      <c r="AK15" s="25"/>
-      <c r="AL15" s="25"/>
-      <c r="AM15" s="25"/>
-      <c r="AN15" s="25"/>
-      <c r="AO15" s="25"/>
-      <c r="AP15" s="25"/>
-      <c r="AQ15" s="25"/>
-      <c r="AR15" s="25"/>
-      <c r="AS15" s="25"/>
-      <c r="AT15" s="25"/>
-      <c r="AU15" s="25"/>
-      <c r="AV15" s="25"/>
-      <c r="AW15" s="25"/>
-      <c r="AX15" s="25"/>
-      <c r="AY15" s="25"/>
-      <c r="AZ15" s="25"/>
-      <c r="BA15" s="25"/>
-      <c r="BB15" s="25"/>
-      <c r="BC15" s="25"/>
-      <c r="BD15" s="25"/>
-      <c r="BE15" s="25"/>
-      <c r="BF15" s="25"/>
-      <c r="BG15" s="25"/>
-      <c r="BH15" s="25"/>
-      <c r="BI15" s="25"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="42"/>
+      <c r="I15" s="42"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="42"/>
+      <c r="L15" s="42"/>
+      <c r="M15" s="42"/>
+      <c r="N15" s="42"/>
+      <c r="O15" s="42"/>
+      <c r="P15" s="42"/>
+      <c r="Q15" s="42"/>
+      <c r="R15" s="42"/>
+      <c r="S15" s="42"/>
+      <c r="T15" s="42"/>
+      <c r="U15" s="42"/>
+      <c r="V15" s="42"/>
+      <c r="W15" s="42"/>
+      <c r="X15" s="42"/>
+      <c r="Y15" s="42"/>
+      <c r="Z15" s="42"/>
+      <c r="AA15" s="42"/>
+      <c r="AB15" s="42"/>
+      <c r="AC15" s="42"/>
+      <c r="AD15" s="42"/>
+      <c r="AE15" s="42"/>
+      <c r="AF15" s="42"/>
+      <c r="AG15" s="42"/>
+      <c r="AH15" s="42"/>
+      <c r="AI15" s="42"/>
+      <c r="AJ15" s="42"/>
+      <c r="AK15" s="42"/>
+      <c r="AL15" s="42"/>
+      <c r="AM15" s="42"/>
+      <c r="AN15" s="42"/>
+      <c r="AO15" s="42"/>
+      <c r="AP15" s="42"/>
+      <c r="AQ15" s="42"/>
+      <c r="AR15" s="42"/>
+      <c r="AS15" s="42"/>
+      <c r="AT15" s="42"/>
+      <c r="AU15" s="42"/>
+      <c r="AV15" s="42"/>
+      <c r="AW15" s="42"/>
+      <c r="AX15" s="42"/>
+      <c r="AY15" s="42"/>
+      <c r="AZ15" s="42"/>
+      <c r="BA15" s="42"/>
+      <c r="BB15" s="42"/>
+      <c r="BC15" s="42"/>
+      <c r="BD15" s="42"/>
+      <c r="BE15" s="42"/>
+      <c r="BF15" s="42"/>
+      <c r="BG15" s="42"/>
+      <c r="BH15" s="42"/>
+      <c r="BI15" s="42"/>
     </row>
     <row r="16" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="24"/>
-      <c r="J16" s="24"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="24"/>
-      <c r="N16" s="24"/>
-      <c r="O16" s="24"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="24"/>
-      <c r="R16" s="24"/>
-      <c r="S16" s="24"/>
-      <c r="T16" s="24"/>
-      <c r="U16" s="24"/>
-      <c r="V16" s="24"/>
-      <c r="W16" s="24"/>
-      <c r="X16" s="24"/>
-      <c r="Y16" s="24"/>
-      <c r="Z16" s="24"/>
-      <c r="AA16" s="24"/>
-      <c r="AB16" s="24"/>
-      <c r="AC16" s="24"/>
-      <c r="AD16" s="24"/>
-      <c r="AE16" s="24"/>
-      <c r="AF16" s="24"/>
-      <c r="AG16" s="24"/>
-      <c r="AH16" s="24"/>
-      <c r="AI16" s="24"/>
-      <c r="AJ16" s="24"/>
-      <c r="AK16" s="24"/>
-      <c r="AL16" s="24"/>
-      <c r="AM16" s="24"/>
-      <c r="AN16" s="24"/>
-      <c r="AO16" s="24"/>
-      <c r="AP16" s="24"/>
-      <c r="AQ16" s="24"/>
-      <c r="AR16" s="24"/>
-      <c r="AS16" s="24"/>
-      <c r="AT16" s="24"/>
-      <c r="AU16" s="24"/>
-      <c r="AV16" s="24"/>
-      <c r="AW16" s="24"/>
-      <c r="AX16" s="24"/>
-      <c r="AY16" s="24"/>
-      <c r="AZ16" s="24"/>
-      <c r="BA16" s="24"/>
-      <c r="BB16" s="24"/>
-      <c r="BC16" s="24"/>
-      <c r="BD16" s="24"/>
-      <c r="BE16" s="24"/>
-      <c r="BF16" s="24"/>
-      <c r="BG16" s="24"/>
-      <c r="BH16" s="24"/>
-      <c r="BI16" s="24"/>
+      <c r="B16" s="46"/>
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="46"/>
+      <c r="J16" s="46"/>
+      <c r="K16" s="46"/>
+      <c r="L16" s="46"/>
+      <c r="M16" s="46"/>
+      <c r="N16" s="46"/>
+      <c r="O16" s="46"/>
+      <c r="P16" s="46"/>
+      <c r="Q16" s="46"/>
+      <c r="R16" s="46"/>
+      <c r="S16" s="46"/>
+      <c r="T16" s="46"/>
+      <c r="U16" s="46"/>
+      <c r="V16" s="46"/>
+      <c r="W16" s="46"/>
+      <c r="X16" s="46"/>
+      <c r="Y16" s="46"/>
+      <c r="Z16" s="46"/>
+      <c r="AA16" s="46"/>
+      <c r="AB16" s="46"/>
+      <c r="AC16" s="46"/>
+      <c r="AD16" s="46"/>
+      <c r="AE16" s="46"/>
+      <c r="AF16" s="46"/>
+      <c r="AG16" s="46"/>
+      <c r="AH16" s="46"/>
+      <c r="AI16" s="46"/>
+      <c r="AJ16" s="46"/>
+      <c r="AK16" s="46"/>
+      <c r="AL16" s="46"/>
+      <c r="AM16" s="46"/>
+      <c r="AN16" s="46"/>
+      <c r="AO16" s="46"/>
+      <c r="AP16" s="46"/>
+      <c r="AQ16" s="46"/>
+      <c r="AR16" s="46"/>
+      <c r="AS16" s="46"/>
+      <c r="AT16" s="46"/>
+      <c r="AU16" s="46"/>
+      <c r="AV16" s="46"/>
+      <c r="AW16" s="46"/>
+      <c r="AX16" s="46"/>
+      <c r="AY16" s="46"/>
+      <c r="AZ16" s="46"/>
+      <c r="BA16" s="46"/>
+      <c r="BB16" s="46"/>
+      <c r="BC16" s="46"/>
+      <c r="BD16" s="46"/>
+      <c r="BE16" s="46"/>
+      <c r="BF16" s="46"/>
+      <c r="BG16" s="46"/>
+      <c r="BH16" s="46"/>
+      <c r="BI16" s="46"/>
     </row>
     <row r="17" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="24"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="24"/>
-      <c r="M17" s="24"/>
-      <c r="N17" s="24"/>
-      <c r="O17" s="24"/>
-      <c r="P17" s="24"/>
-      <c r="Q17" s="24"/>
-      <c r="R17" s="24"/>
-      <c r="S17" s="24"/>
-      <c r="T17" s="24"/>
-      <c r="U17" s="24"/>
-      <c r="V17" s="24"/>
-      <c r="W17" s="24"/>
-      <c r="X17" s="24"/>
-      <c r="Y17" s="24"/>
-      <c r="Z17" s="24"/>
-      <c r="AA17" s="24"/>
-      <c r="AB17" s="24"/>
-      <c r="AC17" s="24"/>
-      <c r="AD17" s="24"/>
-      <c r="AE17" s="24"/>
-      <c r="AF17" s="24"/>
-      <c r="AG17" s="24"/>
-      <c r="AH17" s="24"/>
-      <c r="AI17" s="24"/>
-      <c r="AJ17" s="24"/>
-      <c r="AK17" s="24"/>
-      <c r="AL17" s="24"/>
-      <c r="AM17" s="24"/>
-      <c r="AN17" s="24"/>
-      <c r="AO17" s="24"/>
-      <c r="AP17" s="24"/>
-      <c r="AQ17" s="24"/>
-      <c r="AR17" s="24"/>
-      <c r="AS17" s="24"/>
-      <c r="AT17" s="24"/>
-      <c r="AU17" s="24"/>
-      <c r="AV17" s="24"/>
-      <c r="AW17" s="24"/>
-      <c r="AX17" s="24"/>
-      <c r="AY17" s="24"/>
-      <c r="AZ17" s="24"/>
-      <c r="BA17" s="24"/>
-      <c r="BB17" s="24"/>
-      <c r="BC17" s="24"/>
-      <c r="BD17" s="24"/>
-      <c r="BE17" s="24"/>
-      <c r="BF17" s="24"/>
-      <c r="BG17" s="24"/>
-      <c r="BH17" s="24"/>
-      <c r="BI17" s="24"/>
+      <c r="A17" s="46"/>
+      <c r="B17" s="46"/>
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="46"/>
+      <c r="J17" s="46"/>
+      <c r="K17" s="46"/>
+      <c r="L17" s="46"/>
+      <c r="M17" s="46"/>
+      <c r="N17" s="46"/>
+      <c r="O17" s="46"/>
+      <c r="P17" s="46"/>
+      <c r="Q17" s="46"/>
+      <c r="R17" s="46"/>
+      <c r="S17" s="46"/>
+      <c r="T17" s="46"/>
+      <c r="U17" s="46"/>
+      <c r="V17" s="46"/>
+      <c r="W17" s="46"/>
+      <c r="X17" s="46"/>
+      <c r="Y17" s="46"/>
+      <c r="Z17" s="46"/>
+      <c r="AA17" s="46"/>
+      <c r="AB17" s="46"/>
+      <c r="AC17" s="46"/>
+      <c r="AD17" s="46"/>
+      <c r="AE17" s="46"/>
+      <c r="AF17" s="46"/>
+      <c r="AG17" s="46"/>
+      <c r="AH17" s="46"/>
+      <c r="AI17" s="46"/>
+      <c r="AJ17" s="46"/>
+      <c r="AK17" s="46"/>
+      <c r="AL17" s="46"/>
+      <c r="AM17" s="46"/>
+      <c r="AN17" s="46"/>
+      <c r="AO17" s="46"/>
+      <c r="AP17" s="46"/>
+      <c r="AQ17" s="46"/>
+      <c r="AR17" s="46"/>
+      <c r="AS17" s="46"/>
+      <c r="AT17" s="46"/>
+      <c r="AU17" s="46"/>
+      <c r="AV17" s="46"/>
+      <c r="AW17" s="46"/>
+      <c r="AX17" s="46"/>
+      <c r="AY17" s="46"/>
+      <c r="AZ17" s="46"/>
+      <c r="BA17" s="46"/>
+      <c r="BB17" s="46"/>
+      <c r="BC17" s="46"/>
+      <c r="BD17" s="46"/>
+      <c r="BE17" s="46"/>
+      <c r="BF17" s="46"/>
+      <c r="BG17" s="46"/>
+      <c r="BH17" s="46"/>
+      <c r="BI17" s="46"/>
     </row>
     <row r="18" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="24"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-      <c r="I18" s="24"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="24"/>
-      <c r="L18" s="24"/>
-      <c r="M18" s="24"/>
-      <c r="N18" s="24"/>
-      <c r="O18" s="24"/>
-      <c r="P18" s="24"/>
-      <c r="Q18" s="24"/>
-      <c r="R18" s="24"/>
-      <c r="S18" s="24"/>
-      <c r="T18" s="24"/>
-      <c r="U18" s="24"/>
-      <c r="V18" s="24"/>
-      <c r="W18" s="24"/>
-      <c r="X18" s="24"/>
-      <c r="Y18" s="24"/>
-      <c r="Z18" s="24"/>
-      <c r="AA18" s="24"/>
-      <c r="AB18" s="24"/>
-      <c r="AC18" s="24"/>
-      <c r="AD18" s="24"/>
-      <c r="AE18" s="24"/>
-      <c r="AF18" s="24"/>
-      <c r="AG18" s="24"/>
-      <c r="AH18" s="24"/>
-      <c r="AI18" s="24"/>
-      <c r="AJ18" s="24"/>
-      <c r="AK18" s="24"/>
-      <c r="AL18" s="24"/>
-      <c r="AM18" s="24"/>
-      <c r="AN18" s="24"/>
-      <c r="AO18" s="24"/>
-      <c r="AP18" s="24"/>
-      <c r="AQ18" s="24"/>
-      <c r="AR18" s="24"/>
-      <c r="AS18" s="24"/>
-      <c r="AT18" s="24"/>
-      <c r="AU18" s="24"/>
-      <c r="AV18" s="24"/>
-      <c r="AW18" s="24"/>
-      <c r="AX18" s="24"/>
-      <c r="AY18" s="24"/>
-      <c r="AZ18" s="24"/>
-      <c r="BA18" s="24"/>
-      <c r="BB18" s="24"/>
-      <c r="BC18" s="24"/>
-      <c r="BD18" s="24"/>
-      <c r="BE18" s="24"/>
-      <c r="BF18" s="24"/>
-      <c r="BG18" s="24"/>
-      <c r="BH18" s="24"/>
-      <c r="BI18" s="24"/>
+      <c r="A18" s="46"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="46"/>
+      <c r="J18" s="46"/>
+      <c r="K18" s="46"/>
+      <c r="L18" s="46"/>
+      <c r="M18" s="46"/>
+      <c r="N18" s="46"/>
+      <c r="O18" s="46"/>
+      <c r="P18" s="46"/>
+      <c r="Q18" s="46"/>
+      <c r="R18" s="46"/>
+      <c r="S18" s="46"/>
+      <c r="T18" s="46"/>
+      <c r="U18" s="46"/>
+      <c r="V18" s="46"/>
+      <c r="W18" s="46"/>
+      <c r="X18" s="46"/>
+      <c r="Y18" s="46"/>
+      <c r="Z18" s="46"/>
+      <c r="AA18" s="46"/>
+      <c r="AB18" s="46"/>
+      <c r="AC18" s="46"/>
+      <c r="AD18" s="46"/>
+      <c r="AE18" s="46"/>
+      <c r="AF18" s="46"/>
+      <c r="AG18" s="46"/>
+      <c r="AH18" s="46"/>
+      <c r="AI18" s="46"/>
+      <c r="AJ18" s="46"/>
+      <c r="AK18" s="46"/>
+      <c r="AL18" s="46"/>
+      <c r="AM18" s="46"/>
+      <c r="AN18" s="46"/>
+      <c r="AO18" s="46"/>
+      <c r="AP18" s="46"/>
+      <c r="AQ18" s="46"/>
+      <c r="AR18" s="46"/>
+      <c r="AS18" s="46"/>
+      <c r="AT18" s="46"/>
+      <c r="AU18" s="46"/>
+      <c r="AV18" s="46"/>
+      <c r="AW18" s="46"/>
+      <c r="AX18" s="46"/>
+      <c r="AY18" s="46"/>
+      <c r="AZ18" s="46"/>
+      <c r="BA18" s="46"/>
+      <c r="BB18" s="46"/>
+      <c r="BC18" s="46"/>
+      <c r="BD18" s="46"/>
+      <c r="BE18" s="46"/>
+      <c r="BF18" s="46"/>
+      <c r="BG18" s="46"/>
+      <c r="BH18" s="46"/>
+      <c r="BI18" s="46"/>
     </row>
     <row r="19" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="24"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="24"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="24"/>
-      <c r="Q19" s="24"/>
-      <c r="R19" s="24"/>
-      <c r="S19" s="24"/>
-      <c r="T19" s="24"/>
-      <c r="U19" s="24"/>
-      <c r="V19" s="24"/>
-      <c r="W19" s="24"/>
-      <c r="X19" s="24"/>
-      <c r="Y19" s="24"/>
-      <c r="Z19" s="24"/>
-      <c r="AA19" s="24"/>
-      <c r="AB19" s="24"/>
-      <c r="AC19" s="24"/>
-      <c r="AD19" s="24"/>
-      <c r="AE19" s="24"/>
-      <c r="AF19" s="24"/>
-      <c r="AG19" s="24"/>
-      <c r="AH19" s="24"/>
-      <c r="AI19" s="24"/>
-      <c r="AJ19" s="24"/>
-      <c r="AK19" s="24"/>
-      <c r="AL19" s="24"/>
-      <c r="AM19" s="24"/>
-      <c r="AN19" s="24"/>
-      <c r="AO19" s="24"/>
-      <c r="AP19" s="24"/>
-      <c r="AQ19" s="24"/>
-      <c r="AR19" s="24"/>
-      <c r="AS19" s="24"/>
-      <c r="AT19" s="24"/>
-      <c r="AU19" s="24"/>
-      <c r="AV19" s="24"/>
-      <c r="AW19" s="24"/>
-      <c r="AX19" s="24"/>
-      <c r="AY19" s="24"/>
-      <c r="AZ19" s="24"/>
-      <c r="BA19" s="24"/>
-      <c r="BB19" s="24"/>
-      <c r="BC19" s="24"/>
-      <c r="BD19" s="24"/>
-      <c r="BE19" s="24"/>
-      <c r="BF19" s="24"/>
-      <c r="BG19" s="24"/>
-      <c r="BH19" s="24"/>
-      <c r="BI19" s="24"/>
+      <c r="A19" s="46"/>
+      <c r="B19" s="46"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="46"/>
+      <c r="J19" s="46"/>
+      <c r="K19" s="46"/>
+      <c r="L19" s="46"/>
+      <c r="M19" s="46"/>
+      <c r="N19" s="46"/>
+      <c r="O19" s="46"/>
+      <c r="P19" s="46"/>
+      <c r="Q19" s="46"/>
+      <c r="R19" s="46"/>
+      <c r="S19" s="46"/>
+      <c r="T19" s="46"/>
+      <c r="U19" s="46"/>
+      <c r="V19" s="46"/>
+      <c r="W19" s="46"/>
+      <c r="X19" s="46"/>
+      <c r="Y19" s="46"/>
+      <c r="Z19" s="46"/>
+      <c r="AA19" s="46"/>
+      <c r="AB19" s="46"/>
+      <c r="AC19" s="46"/>
+      <c r="AD19" s="46"/>
+      <c r="AE19" s="46"/>
+      <c r="AF19" s="46"/>
+      <c r="AG19" s="46"/>
+      <c r="AH19" s="46"/>
+      <c r="AI19" s="46"/>
+      <c r="AJ19" s="46"/>
+      <c r="AK19" s="46"/>
+      <c r="AL19" s="46"/>
+      <c r="AM19" s="46"/>
+      <c r="AN19" s="46"/>
+      <c r="AO19" s="46"/>
+      <c r="AP19" s="46"/>
+      <c r="AQ19" s="46"/>
+      <c r="AR19" s="46"/>
+      <c r="AS19" s="46"/>
+      <c r="AT19" s="46"/>
+      <c r="AU19" s="46"/>
+      <c r="AV19" s="46"/>
+      <c r="AW19" s="46"/>
+      <c r="AX19" s="46"/>
+      <c r="AY19" s="46"/>
+      <c r="AZ19" s="46"/>
+      <c r="BA19" s="46"/>
+      <c r="BB19" s="46"/>
+      <c r="BC19" s="46"/>
+      <c r="BD19" s="46"/>
+      <c r="BE19" s="46"/>
+      <c r="BF19" s="46"/>
+      <c r="BG19" s="46"/>
+      <c r="BH19" s="46"/>
+      <c r="BI19" s="46"/>
     </row>
     <row r="20" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="24"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="24"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
-      <c r="N20" s="24"/>
-      <c r="O20" s="24"/>
-      <c r="P20" s="24"/>
-      <c r="Q20" s="24"/>
-      <c r="R20" s="24"/>
-      <c r="S20" s="24"/>
-      <c r="T20" s="24"/>
-      <c r="U20" s="24"/>
-      <c r="V20" s="24"/>
-      <c r="W20" s="24"/>
-      <c r="X20" s="24"/>
-      <c r="Y20" s="24"/>
-      <c r="Z20" s="24"/>
-      <c r="AA20" s="24"/>
-      <c r="AB20" s="24"/>
-      <c r="AC20" s="24"/>
-      <c r="AD20" s="24"/>
-      <c r="AE20" s="24"/>
-      <c r="AF20" s="24"/>
-      <c r="AG20" s="24"/>
-      <c r="AH20" s="24"/>
-      <c r="AI20" s="24"/>
-      <c r="AJ20" s="24"/>
-      <c r="AK20" s="24"/>
-      <c r="AL20" s="24"/>
-      <c r="AM20" s="24"/>
-      <c r="AN20" s="24"/>
-      <c r="AO20" s="24"/>
-      <c r="AP20" s="24"/>
-      <c r="AQ20" s="24"/>
-      <c r="AR20" s="24"/>
-      <c r="AS20" s="24"/>
-      <c r="AT20" s="24"/>
-      <c r="AU20" s="24"/>
-      <c r="AV20" s="24"/>
-      <c r="AW20" s="24"/>
-      <c r="AX20" s="24"/>
-      <c r="AY20" s="24"/>
-      <c r="AZ20" s="24"/>
-      <c r="BA20" s="24"/>
-      <c r="BB20" s="24"/>
-      <c r="BC20" s="24"/>
-      <c r="BD20" s="24"/>
-      <c r="BE20" s="24"/>
-      <c r="BF20" s="24"/>
-      <c r="BG20" s="24"/>
-      <c r="BH20" s="24"/>
-      <c r="BI20" s="24"/>
+      <c r="A20" s="46"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="46"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+      <c r="G20" s="46"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="46"/>
+      <c r="J20" s="46"/>
+      <c r="K20" s="46"/>
+      <c r="L20" s="46"/>
+      <c r="M20" s="46"/>
+      <c r="N20" s="46"/>
+      <c r="O20" s="46"/>
+      <c r="P20" s="46"/>
+      <c r="Q20" s="46"/>
+      <c r="R20" s="46"/>
+      <c r="S20" s="46"/>
+      <c r="T20" s="46"/>
+      <c r="U20" s="46"/>
+      <c r="V20" s="46"/>
+      <c r="W20" s="46"/>
+      <c r="X20" s="46"/>
+      <c r="Y20" s="46"/>
+      <c r="Z20" s="46"/>
+      <c r="AA20" s="46"/>
+      <c r="AB20" s="46"/>
+      <c r="AC20" s="46"/>
+      <c r="AD20" s="46"/>
+      <c r="AE20" s="46"/>
+      <c r="AF20" s="46"/>
+      <c r="AG20" s="46"/>
+      <c r="AH20" s="46"/>
+      <c r="AI20" s="46"/>
+      <c r="AJ20" s="46"/>
+      <c r="AK20" s="46"/>
+      <c r="AL20" s="46"/>
+      <c r="AM20" s="46"/>
+      <c r="AN20" s="46"/>
+      <c r="AO20" s="46"/>
+      <c r="AP20" s="46"/>
+      <c r="AQ20" s="46"/>
+      <c r="AR20" s="46"/>
+      <c r="AS20" s="46"/>
+      <c r="AT20" s="46"/>
+      <c r="AU20" s="46"/>
+      <c r="AV20" s="46"/>
+      <c r="AW20" s="46"/>
+      <c r="AX20" s="46"/>
+      <c r="AY20" s="46"/>
+      <c r="AZ20" s="46"/>
+      <c r="BA20" s="46"/>
+      <c r="BB20" s="46"/>
+      <c r="BC20" s="46"/>
+      <c r="BD20" s="46"/>
+      <c r="BE20" s="46"/>
+      <c r="BF20" s="46"/>
+      <c r="BG20" s="46"/>
+      <c r="BH20" s="46"/>
+      <c r="BI20" s="46"/>
     </row>
     <row r="21" spans="1:61" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="24"/>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="24"/>
-      <c r="N21" s="24"/>
-      <c r="O21" s="24"/>
-      <c r="P21" s="24"/>
-      <c r="Q21" s="24"/>
-      <c r="R21" s="24"/>
-      <c r="S21" s="24"/>
-      <c r="T21" s="24"/>
-      <c r="U21" s="24"/>
-      <c r="V21" s="24"/>
-      <c r="W21" s="24"/>
-      <c r="X21" s="24"/>
-      <c r="Y21" s="24"/>
-      <c r="Z21" s="24"/>
-      <c r="AA21" s="24"/>
-      <c r="AB21" s="24"/>
-      <c r="AC21" s="24"/>
-      <c r="AD21" s="24"/>
-      <c r="AE21" s="24"/>
-      <c r="AF21" s="24"/>
-      <c r="AG21" s="24"/>
-      <c r="AH21" s="24"/>
-      <c r="AI21" s="24"/>
-      <c r="AJ21" s="24"/>
-      <c r="AK21" s="24"/>
-      <c r="AL21" s="24"/>
-      <c r="AM21" s="24"/>
-      <c r="AN21" s="24"/>
-      <c r="AO21" s="24"/>
-      <c r="AP21" s="24"/>
-      <c r="AQ21" s="24"/>
-      <c r="AR21" s="24"/>
-      <c r="AS21" s="24"/>
-      <c r="AT21" s="24"/>
-      <c r="AU21" s="24"/>
-      <c r="AV21" s="24"/>
-      <c r="AW21" s="24"/>
-      <c r="AX21" s="24"/>
-      <c r="AY21" s="24"/>
-      <c r="AZ21" s="24"/>
-      <c r="BA21" s="24"/>
-      <c r="BB21" s="24"/>
-      <c r="BC21" s="24"/>
-      <c r="BD21" s="24"/>
-      <c r="BE21" s="24"/>
-      <c r="BF21" s="24"/>
-      <c r="BG21" s="24"/>
-      <c r="BH21" s="24"/>
-      <c r="BI21" s="24"/>
+      <c r="A21" s="46"/>
+      <c r="B21" s="46"/>
+      <c r="C21" s="46"/>
+      <c r="D21" s="46"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="46"/>
+      <c r="G21" s="46"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="46"/>
+      <c r="J21" s="46"/>
+      <c r="K21" s="46"/>
+      <c r="L21" s="46"/>
+      <c r="M21" s="46"/>
+      <c r="N21" s="46"/>
+      <c r="O21" s="46"/>
+      <c r="P21" s="46"/>
+      <c r="Q21" s="46"/>
+      <c r="R21" s="46"/>
+      <c r="S21" s="46"/>
+      <c r="T21" s="46"/>
+      <c r="U21" s="46"/>
+      <c r="V21" s="46"/>
+      <c r="W21" s="46"/>
+      <c r="X21" s="46"/>
+      <c r="Y21" s="46"/>
+      <c r="Z21" s="46"/>
+      <c r="AA21" s="46"/>
+      <c r="AB21" s="46"/>
+      <c r="AC21" s="46"/>
+      <c r="AD21" s="46"/>
+      <c r="AE21" s="46"/>
+      <c r="AF21" s="46"/>
+      <c r="AG21" s="46"/>
+      <c r="AH21" s="46"/>
+      <c r="AI21" s="46"/>
+      <c r="AJ21" s="46"/>
+      <c r="AK21" s="46"/>
+      <c r="AL21" s="46"/>
+      <c r="AM21" s="46"/>
+      <c r="AN21" s="46"/>
+      <c r="AO21" s="46"/>
+      <c r="AP21" s="46"/>
+      <c r="AQ21" s="46"/>
+      <c r="AR21" s="46"/>
+      <c r="AS21" s="46"/>
+      <c r="AT21" s="46"/>
+      <c r="AU21" s="46"/>
+      <c r="AV21" s="46"/>
+      <c r="AW21" s="46"/>
+      <c r="AX21" s="46"/>
+      <c r="AY21" s="46"/>
+      <c r="AZ21" s="46"/>
+      <c r="BA21" s="46"/>
+      <c r="BB21" s="46"/>
+      <c r="BC21" s="46"/>
+      <c r="BD21" s="46"/>
+      <c r="BE21" s="46"/>
+      <c r="BF21" s="46"/>
+      <c r="BG21" s="46"/>
+      <c r="BH21" s="46"/>
+      <c r="BI21" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="AO12:BI12"/>
-    <mergeCell ref="A9:J10"/>
-    <mergeCell ref="K9:T10"/>
-    <mergeCell ref="U9:AD10"/>
-    <mergeCell ref="AE9:AN10"/>
-    <mergeCell ref="AO9:BI10"/>
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="AT2:AZ2"/>
-    <mergeCell ref="BA2:BC2"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="R1:AA1"/>
-    <mergeCell ref="AB1:AD1"/>
-    <mergeCell ref="AE1:AP1"/>
-    <mergeCell ref="AQ1:AS1"/>
+    <mergeCell ref="A16:BI21"/>
+    <mergeCell ref="A15:BI15"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="K11:T11"/>
+    <mergeCell ref="U11:AD11"/>
+    <mergeCell ref="AE11:AN11"/>
+    <mergeCell ref="AO11:BI11"/>
+    <mergeCell ref="A13:J13"/>
+    <mergeCell ref="K13:T13"/>
+    <mergeCell ref="U13:AD13"/>
+    <mergeCell ref="AE13:AN13"/>
+    <mergeCell ref="AO13:BI13"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="K12:T12"/>
+    <mergeCell ref="U12:AD12"/>
+    <mergeCell ref="AE12:AN12"/>
+    <mergeCell ref="G4:BI4"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="K8:T8"/>
+    <mergeCell ref="U8:AD8"/>
+    <mergeCell ref="AE8:AN8"/>
+    <mergeCell ref="AO8:BI8"/>
     <mergeCell ref="BD2:BI2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A5:F5"/>
@@ -2893,28 +2841,20 @@
     <mergeCell ref="R2:AA2"/>
     <mergeCell ref="AB2:AD2"/>
     <mergeCell ref="AE2:AP2"/>
-    <mergeCell ref="G4:BI4"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="K8:T8"/>
-    <mergeCell ref="U8:AD8"/>
-    <mergeCell ref="AE8:AN8"/>
-    <mergeCell ref="AO8:BI8"/>
-    <mergeCell ref="A16:BI21"/>
-    <mergeCell ref="A15:BI15"/>
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="K11:T11"/>
-    <mergeCell ref="U11:AD11"/>
-    <mergeCell ref="AE11:AN11"/>
-    <mergeCell ref="AO11:BI11"/>
-    <mergeCell ref="A13:J13"/>
-    <mergeCell ref="K13:T13"/>
-    <mergeCell ref="U13:AD13"/>
-    <mergeCell ref="AE13:AN13"/>
-    <mergeCell ref="AO13:BI13"/>
-    <mergeCell ref="A12:J12"/>
-    <mergeCell ref="K12:T12"/>
-    <mergeCell ref="U12:AD12"/>
-    <mergeCell ref="AE12:AN12"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="AT2:AZ2"/>
+    <mergeCell ref="BA2:BC2"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="R1:AA1"/>
+    <mergeCell ref="AB1:AD1"/>
+    <mergeCell ref="AE1:AP1"/>
+    <mergeCell ref="AQ1:AS1"/>
+    <mergeCell ref="AO12:BI12"/>
+    <mergeCell ref="A9:J10"/>
+    <mergeCell ref="K9:T10"/>
+    <mergeCell ref="U9:AD10"/>
+    <mergeCell ref="AE9:AN10"/>
+    <mergeCell ref="AO9:BI10"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <printOptions horizontalCentered="1"/>
@@ -2926,93 +2866,93 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:IX45"/>
+  <dimension ref="A1:IX39"/>
   <sheetFormatPr defaultColWidth="2.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="16384" width="2.453125" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="44" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="32" t="s">
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="44"/>
+      <c r="L1" s="44"/>
+      <c r="M1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="31" t="s">
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+      <c r="R1" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="S1" s="31"/>
-      <c r="T1" s="31"/>
-      <c r="U1" s="31"/>
-      <c r="V1" s="31"/>
-      <c r="W1" s="31"/>
-      <c r="X1" s="31"/>
-      <c r="Y1" s="31"/>
-      <c r="Z1" s="31"/>
-      <c r="AA1" s="31"/>
-      <c r="AB1" s="32" t="s">
+      <c r="S1" s="40"/>
+      <c r="T1" s="40"/>
+      <c r="U1" s="40"/>
+      <c r="V1" s="40"/>
+      <c r="W1" s="40"/>
+      <c r="X1" s="40"/>
+      <c r="Y1" s="40"/>
+      <c r="Z1" s="40"/>
+      <c r="AA1" s="40"/>
+      <c r="AB1" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="AC1" s="32"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="31" t="str">
+      <c r="AC1" s="39"/>
+      <c r="AD1" s="39"/>
+      <c r="AE1" s="40" t="str">
         <f>クラス仕様!AE1</f>
         <v>商品検索</v>
       </c>
-      <c r="AF1" s="31"/>
-      <c r="AG1" s="31"/>
-      <c r="AH1" s="31"/>
-      <c r="AI1" s="31"/>
-      <c r="AJ1" s="31"/>
-      <c r="AK1" s="31"/>
-      <c r="AL1" s="31"/>
-      <c r="AM1" s="31"/>
-      <c r="AN1" s="31"/>
-      <c r="AO1" s="31"/>
-      <c r="AP1" s="31"/>
-      <c r="AQ1" s="32" t="s">
+      <c r="AF1" s="40"/>
+      <c r="AG1" s="40"/>
+      <c r="AH1" s="40"/>
+      <c r="AI1" s="40"/>
+      <c r="AJ1" s="40"/>
+      <c r="AK1" s="40"/>
+      <c r="AL1" s="40"/>
+      <c r="AM1" s="40"/>
+      <c r="AN1" s="40"/>
+      <c r="AO1" s="40"/>
+      <c r="AP1" s="40"/>
+      <c r="AQ1" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="AR1" s="32"/>
-      <c r="AS1" s="32"/>
-      <c r="AT1" s="31" t="s">
+      <c r="AR1" s="39"/>
+      <c r="AS1" s="39"/>
+      <c r="AT1" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="AU1" s="31"/>
-      <c r="AV1" s="31"/>
-      <c r="AW1" s="31"/>
-      <c r="AX1" s="31"/>
-      <c r="AY1" s="31"/>
-      <c r="AZ1" s="31"/>
-      <c r="BA1" s="32" t="s">
+      <c r="AU1" s="40"/>
+      <c r="AV1" s="40"/>
+      <c r="AW1" s="40"/>
+      <c r="AX1" s="40"/>
+      <c r="AY1" s="40"/>
+      <c r="AZ1" s="40"/>
+      <c r="BA1" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="BB1" s="32"/>
-      <c r="BC1" s="32"/>
-      <c r="BD1" s="29">
+      <c r="BB1" s="39"/>
+      <c r="BC1" s="39"/>
+      <c r="BD1" s="41">
         <v>45554</v>
       </c>
-      <c r="BE1" s="29"/>
-      <c r="BF1" s="29"/>
-      <c r="BG1" s="29"/>
-      <c r="BH1" s="29"/>
-      <c r="BI1" s="29"/>
+      <c r="BE1" s="41"/>
+      <c r="BF1" s="41"/>
+      <c r="BG1" s="41"/>
+      <c r="BH1" s="41"/>
+      <c r="BI1" s="41"/>
       <c r="BJ1" s="1"/>
       <c r="BK1" s="1"/>
       <c r="BL1" s="1"/>
@@ -3212,82 +3152,82 @@
       <c r="IX1" s="1"/>
     </row>
     <row r="2" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="30"/>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="32" t="s">
+      <c r="A2" s="44"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="32"/>
-      <c r="O2" s="32"/>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="32"/>
-      <c r="R2" s="33"/>
-      <c r="S2" s="33"/>
-      <c r="T2" s="33"/>
-      <c r="U2" s="33"/>
-      <c r="V2" s="33"/>
-      <c r="W2" s="33"/>
-      <c r="X2" s="33"/>
-      <c r="Y2" s="33"/>
-      <c r="Z2" s="33"/>
-      <c r="AA2" s="33"/>
-      <c r="AB2" s="32" t="s">
+      <c r="N2" s="39"/>
+      <c r="O2" s="39"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="39"/>
+      <c r="R2" s="45"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="45"/>
+      <c r="U2" s="45"/>
+      <c r="V2" s="45"/>
+      <c r="W2" s="45"/>
+      <c r="X2" s="45"/>
+      <c r="Y2" s="45"/>
+      <c r="Z2" s="45"/>
+      <c r="AA2" s="45"/>
+      <c r="AB2" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="AC2" s="32"/>
-      <c r="AD2" s="32"/>
-      <c r="AE2" s="31" t="str">
+      <c r="AC2" s="39"/>
+      <c r="AD2" s="39"/>
+      <c r="AE2" s="40" t="str">
         <f>クラス仕様!G5</f>
         <v>ConnectionUtil</v>
       </c>
-      <c r="AF2" s="31"/>
-      <c r="AG2" s="31"/>
-      <c r="AH2" s="31"/>
-      <c r="AI2" s="31"/>
-      <c r="AJ2" s="31"/>
-      <c r="AK2" s="31"/>
-      <c r="AL2" s="31"/>
-      <c r="AM2" s="31"/>
-      <c r="AN2" s="31"/>
-      <c r="AO2" s="31"/>
-      <c r="AP2" s="31"/>
-      <c r="AQ2" s="32" t="s">
+      <c r="AF2" s="40"/>
+      <c r="AG2" s="40"/>
+      <c r="AH2" s="40"/>
+      <c r="AI2" s="40"/>
+      <c r="AJ2" s="40"/>
+      <c r="AK2" s="40"/>
+      <c r="AL2" s="40"/>
+      <c r="AM2" s="40"/>
+      <c r="AN2" s="40"/>
+      <c r="AO2" s="40"/>
+      <c r="AP2" s="40"/>
+      <c r="AQ2" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="AR2" s="32"/>
-      <c r="AS2" s="32"/>
-      <c r="AT2" s="31" t="s">
+      <c r="AR2" s="39"/>
+      <c r="AS2" s="39"/>
+      <c r="AT2" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AU2" s="31"/>
-      <c r="AV2" s="31"/>
-      <c r="AW2" s="31"/>
-      <c r="AX2" s="31"/>
-      <c r="AY2" s="31"/>
-      <c r="AZ2" s="31"/>
-      <c r="BA2" s="32" t="s">
+      <c r="AU2" s="40"/>
+      <c r="AV2" s="40"/>
+      <c r="AW2" s="40"/>
+      <c r="AX2" s="40"/>
+      <c r="AY2" s="40"/>
+      <c r="AZ2" s="40"/>
+      <c r="BA2" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="BB2" s="32"/>
-      <c r="BC2" s="32"/>
-      <c r="BD2" s="51">
-        <v>45566</v>
+      <c r="BB2" s="39"/>
+      <c r="BC2" s="39"/>
+      <c r="BD2" s="48">
+        <v>45587</v>
       </c>
-      <c r="BE2" s="52"/>
-      <c r="BF2" s="52"/>
-      <c r="BG2" s="52"/>
-      <c r="BH2" s="52"/>
-      <c r="BI2" s="53"/>
+      <c r="BE2" s="49"/>
+      <c r="BF2" s="49"/>
+      <c r="BG2" s="49"/>
+      <c r="BH2" s="49"/>
+      <c r="BI2" s="50"/>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1"/>
       <c r="BL2" s="1"/>
@@ -3550,71 +3490,71 @@
       <c r="BI3" s="3"/>
     </row>
     <row r="4" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="25"/>
-      <c r="E4" s="25"/>
-      <c r="F4" s="25"/>
-      <c r="G4" s="28" t="s">
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="43" t="s">
         <v>55</v>
       </c>
-      <c r="H4" s="28"/>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28"/>
-      <c r="O4" s="28"/>
-      <c r="P4" s="28"/>
-      <c r="Q4" s="28"/>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="28"/>
-      <c r="U4" s="28"/>
-      <c r="V4" s="28"/>
-      <c r="W4" s="28"/>
-      <c r="X4" s="28"/>
-      <c r="Y4" s="28"/>
-      <c r="Z4" s="28"/>
-      <c r="AA4" s="28"/>
-      <c r="AB4" s="28"/>
-      <c r="AC4" s="28"/>
-      <c r="AD4" s="28"/>
-      <c r="AE4" s="28"/>
-      <c r="AF4" s="28"/>
-      <c r="AG4" s="28"/>
-      <c r="AH4" s="28"/>
-      <c r="AI4" s="28"/>
-      <c r="AJ4" s="28"/>
-      <c r="AK4" s="28"/>
-      <c r="AL4" s="28"/>
-      <c r="AM4" s="28"/>
-      <c r="AN4" s="28"/>
-      <c r="AO4" s="28"/>
-      <c r="AP4" s="28"/>
-      <c r="AQ4" s="28"/>
-      <c r="AR4" s="28"/>
-      <c r="AS4" s="28"/>
-      <c r="AT4" s="28"/>
-      <c r="AU4" s="28"/>
-      <c r="AV4" s="28"/>
-      <c r="AW4" s="28"/>
-      <c r="AX4" s="28"/>
-      <c r="AY4" s="28"/>
-      <c r="AZ4" s="28"/>
-      <c r="BA4" s="28"/>
-      <c r="BB4" s="28"/>
-      <c r="BC4" s="28"/>
-      <c r="BD4" s="28"/>
-      <c r="BE4" s="28"/>
-      <c r="BF4" s="28"/>
-      <c r="BG4" s="28"/>
-      <c r="BH4" s="28"/>
-      <c r="BI4" s="28"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="43"/>
+      <c r="J4" s="43"/>
+      <c r="K4" s="43"/>
+      <c r="L4" s="43"/>
+      <c r="M4" s="43"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="43"/>
+      <c r="T4" s="43"/>
+      <c r="U4" s="43"/>
+      <c r="V4" s="43"/>
+      <c r="W4" s="43"/>
+      <c r="X4" s="43"/>
+      <c r="Y4" s="43"/>
+      <c r="Z4" s="43"/>
+      <c r="AA4" s="43"/>
+      <c r="AB4" s="43"/>
+      <c r="AC4" s="43"/>
+      <c r="AD4" s="43"/>
+      <c r="AE4" s="43"/>
+      <c r="AF4" s="43"/>
+      <c r="AG4" s="43"/>
+      <c r="AH4" s="43"/>
+      <c r="AI4" s="43"/>
+      <c r="AJ4" s="43"/>
+      <c r="AK4" s="43"/>
+      <c r="AL4" s="43"/>
+      <c r="AM4" s="43"/>
+      <c r="AN4" s="43"/>
+      <c r="AO4" s="43"/>
+      <c r="AP4" s="43"/>
+      <c r="AQ4" s="43"/>
+      <c r="AR4" s="43"/>
+      <c r="AS4" s="43"/>
+      <c r="AT4" s="43"/>
+      <c r="AU4" s="43"/>
+      <c r="AV4" s="43"/>
+      <c r="AW4" s="43"/>
+      <c r="AX4" s="43"/>
+      <c r="AY4" s="43"/>
+      <c r="AZ4" s="43"/>
+      <c r="BA4" s="43"/>
+      <c r="BB4" s="43"/>
+      <c r="BC4" s="43"/>
+      <c r="BD4" s="43"/>
+      <c r="BE4" s="43"/>
+      <c r="BF4" s="43"/>
+      <c r="BG4" s="43"/>
+      <c r="BH4" s="43"/>
+      <c r="BI4" s="43"/>
       <c r="BJ4" s="1"/>
       <c r="BK4" s="1"/>
       <c r="BL4" s="1"/>
@@ -3814,71 +3754,71 @@
       <c r="IX4" s="1"/>
     </row>
     <row r="5" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="28" t="s">
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="28"/>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="28"/>
-      <c r="T5" s="28"/>
-      <c r="U5" s="28"/>
-      <c r="V5" s="28"/>
-      <c r="W5" s="28"/>
-      <c r="X5" s="28"/>
-      <c r="Y5" s="28"/>
-      <c r="Z5" s="28"/>
-      <c r="AA5" s="28"/>
-      <c r="AB5" s="28"/>
-      <c r="AC5" s="28"/>
-      <c r="AD5" s="28"/>
-      <c r="AE5" s="28"/>
-      <c r="AF5" s="28"/>
-      <c r="AG5" s="28"/>
-      <c r="AH5" s="28"/>
-      <c r="AI5" s="28"/>
-      <c r="AJ5" s="28"/>
-      <c r="AK5" s="28"/>
-      <c r="AL5" s="28"/>
-      <c r="AM5" s="28"/>
-      <c r="AN5" s="28"/>
-      <c r="AO5" s="28"/>
-      <c r="AP5" s="28"/>
-      <c r="AQ5" s="28"/>
-      <c r="AR5" s="28"/>
-      <c r="AS5" s="28"/>
-      <c r="AT5" s="28"/>
-      <c r="AU5" s="28"/>
-      <c r="AV5" s="28"/>
-      <c r="AW5" s="28"/>
-      <c r="AX5" s="28"/>
-      <c r="AY5" s="28"/>
-      <c r="AZ5" s="28"/>
-      <c r="BA5" s="28"/>
-      <c r="BB5" s="28"/>
-      <c r="BC5" s="28"/>
-      <c r="BD5" s="28"/>
-      <c r="BE5" s="28"/>
-      <c r="BF5" s="28"/>
-      <c r="BG5" s="28"/>
-      <c r="BH5" s="28"/>
-      <c r="BI5" s="28"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
+      <c r="J5" s="43"/>
+      <c r="K5" s="43"/>
+      <c r="L5" s="43"/>
+      <c r="M5" s="43"/>
+      <c r="N5" s="43"/>
+      <c r="O5" s="43"/>
+      <c r="P5" s="43"/>
+      <c r="Q5" s="43"/>
+      <c r="R5" s="43"/>
+      <c r="S5" s="43"/>
+      <c r="T5" s="43"/>
+      <c r="U5" s="43"/>
+      <c r="V5" s="43"/>
+      <c r="W5" s="43"/>
+      <c r="X5" s="43"/>
+      <c r="Y5" s="43"/>
+      <c r="Z5" s="43"/>
+      <c r="AA5" s="43"/>
+      <c r="AB5" s="43"/>
+      <c r="AC5" s="43"/>
+      <c r="AD5" s="43"/>
+      <c r="AE5" s="43"/>
+      <c r="AF5" s="43"/>
+      <c r="AG5" s="43"/>
+      <c r="AH5" s="43"/>
+      <c r="AI5" s="43"/>
+      <c r="AJ5" s="43"/>
+      <c r="AK5" s="43"/>
+      <c r="AL5" s="43"/>
+      <c r="AM5" s="43"/>
+      <c r="AN5" s="43"/>
+      <c r="AO5" s="43"/>
+      <c r="AP5" s="43"/>
+      <c r="AQ5" s="43"/>
+      <c r="AR5" s="43"/>
+      <c r="AS5" s="43"/>
+      <c r="AT5" s="43"/>
+      <c r="AU5" s="43"/>
+      <c r="AV5" s="43"/>
+      <c r="AW5" s="43"/>
+      <c r="AX5" s="43"/>
+      <c r="AY5" s="43"/>
+      <c r="AZ5" s="43"/>
+      <c r="BA5" s="43"/>
+      <c r="BB5" s="43"/>
+      <c r="BC5" s="43"/>
+      <c r="BD5" s="43"/>
+      <c r="BE5" s="43"/>
+      <c r="BF5" s="43"/>
+      <c r="BG5" s="43"/>
+      <c r="BH5" s="43"/>
+      <c r="BI5" s="43"/>
       <c r="BJ5" s="1"/>
       <c r="BK5" s="1"/>
       <c r="BL5" s="1"/>
@@ -4338,75 +4278,75 @@
       <c r="IX6" s="1"/>
     </row>
     <row r="7" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="51" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46" t="s">
+      <c r="B7" s="51"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51" t="s">
         <v>22</v>
       </c>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="46"/>
-      <c r="M7" s="46"/>
-      <c r="N7" s="46"/>
-      <c r="O7" s="46"/>
-      <c r="P7" s="46" t="s">
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
+      <c r="K7" s="51"/>
+      <c r="L7" s="51"/>
+      <c r="M7" s="51"/>
+      <c r="N7" s="51"/>
+      <c r="O7" s="51"/>
+      <c r="P7" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="Q7" s="46"/>
-      <c r="R7" s="46"/>
-      <c r="S7" s="46"/>
-      <c r="T7" s="46"/>
-      <c r="U7" s="46"/>
-      <c r="V7" s="46"/>
-      <c r="W7" s="46"/>
-      <c r="X7" s="46"/>
-      <c r="Y7" s="46"/>
-      <c r="Z7" s="46"/>
-      <c r="AA7" s="46"/>
-      <c r="AB7" s="46"/>
-      <c r="AC7" s="46"/>
-      <c r="AD7" s="46"/>
-      <c r="AE7" s="46" t="s">
+      <c r="Q7" s="51"/>
+      <c r="R7" s="51"/>
+      <c r="S7" s="51"/>
+      <c r="T7" s="51"/>
+      <c r="U7" s="51"/>
+      <c r="V7" s="51"/>
+      <c r="W7" s="51"/>
+      <c r="X7" s="51"/>
+      <c r="Y7" s="51"/>
+      <c r="Z7" s="51"/>
+      <c r="AA7" s="51"/>
+      <c r="AB7" s="51"/>
+      <c r="AC7" s="51"/>
+      <c r="AD7" s="51"/>
+      <c r="AE7" s="51" t="s">
         <v>17</v>
       </c>
-      <c r="AF7" s="46"/>
-      <c r="AG7" s="46"/>
-      <c r="AH7" s="46"/>
-      <c r="AI7" s="46"/>
-      <c r="AJ7" s="46"/>
-      <c r="AK7" s="46"/>
-      <c r="AL7" s="46"/>
-      <c r="AM7" s="46"/>
-      <c r="AN7" s="46"/>
-      <c r="AO7" s="46"/>
-      <c r="AP7" s="46"/>
-      <c r="AQ7" s="46"/>
-      <c r="AR7" s="46"/>
-      <c r="AS7" s="46"/>
-      <c r="AT7" s="46"/>
-      <c r="AU7" s="46"/>
-      <c r="AV7" s="46"/>
-      <c r="AW7" s="46"/>
-      <c r="AX7" s="46"/>
-      <c r="AY7" s="46"/>
-      <c r="AZ7" s="46"/>
-      <c r="BA7" s="46"/>
-      <c r="BB7" s="46"/>
-      <c r="BC7" s="46"/>
-      <c r="BD7" s="46"/>
-      <c r="BE7" s="46"/>
-      <c r="BF7" s="46"/>
-      <c r="BG7" s="46"/>
-      <c r="BH7" s="46"/>
-      <c r="BI7" s="46"/>
+      <c r="AF7" s="51"/>
+      <c r="AG7" s="51"/>
+      <c r="AH7" s="51"/>
+      <c r="AI7" s="51"/>
+      <c r="AJ7" s="51"/>
+      <c r="AK7" s="51"/>
+      <c r="AL7" s="51"/>
+      <c r="AM7" s="51"/>
+      <c r="AN7" s="51"/>
+      <c r="AO7" s="51"/>
+      <c r="AP7" s="51"/>
+      <c r="AQ7" s="51"/>
+      <c r="AR7" s="51"/>
+      <c r="AS7" s="51"/>
+      <c r="AT7" s="51"/>
+      <c r="AU7" s="51"/>
+      <c r="AV7" s="51"/>
+      <c r="AW7" s="51"/>
+      <c r="AX7" s="51"/>
+      <c r="AY7" s="51"/>
+      <c r="AZ7" s="51"/>
+      <c r="BA7" s="51"/>
+      <c r="BB7" s="51"/>
+      <c r="BC7" s="51"/>
+      <c r="BD7" s="51"/>
+      <c r="BE7" s="51"/>
+      <c r="BF7" s="51"/>
+      <c r="BG7" s="51"/>
+      <c r="BH7" s="51"/>
+      <c r="BI7" s="51"/>
       <c r="BJ7" s="1"/>
       <c r="BK7" s="1"/>
       <c r="BL7" s="1"/>
@@ -4606,71 +4546,71 @@
       <c r="IX7" s="1"/>
     </row>
     <row r="8" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="47" t="s">
+      <c r="A8" s="52" t="s">
         <v>58</v>
       </c>
-      <c r="B8" s="47"/>
-      <c r="C8" s="47"/>
-      <c r="D8" s="48" t="s">
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49"/>
-      <c r="K8" s="49"/>
-      <c r="L8" s="49"/>
-      <c r="M8" s="49"/>
-      <c r="N8" s="49"/>
-      <c r="O8" s="49"/>
-      <c r="P8" s="49"/>
-      <c r="Q8" s="49"/>
-      <c r="R8" s="49"/>
-      <c r="S8" s="49"/>
-      <c r="T8" s="49"/>
-      <c r="U8" s="49"/>
-      <c r="V8" s="49"/>
-      <c r="W8" s="49"/>
-      <c r="X8" s="49"/>
-      <c r="Y8" s="49"/>
-      <c r="Z8" s="49"/>
-      <c r="AA8" s="49"/>
-      <c r="AB8" s="49"/>
-      <c r="AC8" s="49"/>
-      <c r="AD8" s="49"/>
-      <c r="AE8" s="49"/>
-      <c r="AF8" s="49"/>
-      <c r="AG8" s="49"/>
-      <c r="AH8" s="49"/>
-      <c r="AI8" s="49"/>
-      <c r="AJ8" s="49"/>
-      <c r="AK8" s="49"/>
-      <c r="AL8" s="49"/>
-      <c r="AM8" s="49"/>
-      <c r="AN8" s="49"/>
-      <c r="AO8" s="49"/>
-      <c r="AP8" s="49"/>
-      <c r="AQ8" s="49"/>
-      <c r="AR8" s="49"/>
-      <c r="AS8" s="49"/>
-      <c r="AT8" s="49"/>
-      <c r="AU8" s="49"/>
-      <c r="AV8" s="49"/>
-      <c r="AW8" s="49"/>
-      <c r="AX8" s="49"/>
-      <c r="AY8" s="49"/>
-      <c r="AZ8" s="49"/>
-      <c r="BA8" s="49"/>
-      <c r="BB8" s="49"/>
-      <c r="BC8" s="49"/>
-      <c r="BD8" s="49"/>
-      <c r="BE8" s="49"/>
-      <c r="BF8" s="49"/>
-      <c r="BG8" s="49"/>
-      <c r="BH8" s="49"/>
-      <c r="BI8" s="50"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="54"/>
+      <c r="K8" s="54"/>
+      <c r="L8" s="54"/>
+      <c r="M8" s="54"/>
+      <c r="N8" s="54"/>
+      <c r="O8" s="54"/>
+      <c r="P8" s="54"/>
+      <c r="Q8" s="54"/>
+      <c r="R8" s="54"/>
+      <c r="S8" s="54"/>
+      <c r="T8" s="54"/>
+      <c r="U8" s="54"/>
+      <c r="V8" s="54"/>
+      <c r="W8" s="54"/>
+      <c r="X8" s="54"/>
+      <c r="Y8" s="54"/>
+      <c r="Z8" s="54"/>
+      <c r="AA8" s="54"/>
+      <c r="AB8" s="54"/>
+      <c r="AC8" s="54"/>
+      <c r="AD8" s="54"/>
+      <c r="AE8" s="54"/>
+      <c r="AF8" s="54"/>
+      <c r="AG8" s="54"/>
+      <c r="AH8" s="54"/>
+      <c r="AI8" s="54"/>
+      <c r="AJ8" s="54"/>
+      <c r="AK8" s="54"/>
+      <c r="AL8" s="54"/>
+      <c r="AM8" s="54"/>
+      <c r="AN8" s="54"/>
+      <c r="AO8" s="54"/>
+      <c r="AP8" s="54"/>
+      <c r="AQ8" s="54"/>
+      <c r="AR8" s="54"/>
+      <c r="AS8" s="54"/>
+      <c r="AT8" s="54"/>
+      <c r="AU8" s="54"/>
+      <c r="AV8" s="54"/>
+      <c r="AW8" s="54"/>
+      <c r="AX8" s="54"/>
+      <c r="AY8" s="54"/>
+      <c r="AZ8" s="54"/>
+      <c r="BA8" s="54"/>
+      <c r="BB8" s="54"/>
+      <c r="BC8" s="54"/>
+      <c r="BD8" s="54"/>
+      <c r="BE8" s="54"/>
+      <c r="BF8" s="54"/>
+      <c r="BG8" s="54"/>
+      <c r="BH8" s="54"/>
+      <c r="BI8" s="55"/>
       <c r="BJ8" s="1"/>
       <c r="BK8" s="1"/>
       <c r="BL8" s="1"/>
@@ -4870,75 +4810,75 @@
       <c r="IX8" s="1"/>
     </row>
     <row r="9" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="27" t="s">
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="27"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="27"/>
-      <c r="O9" s="27"/>
-      <c r="P9" s="27" t="s">
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="Q9" s="27"/>
-      <c r="R9" s="27"/>
-      <c r="S9" s="27"/>
-      <c r="T9" s="27"/>
-      <c r="U9" s="27"/>
-      <c r="V9" s="27"/>
-      <c r="W9" s="27"/>
-      <c r="X9" s="27"/>
-      <c r="Y9" s="27"/>
-      <c r="Z9" s="27"/>
-      <c r="AA9" s="27"/>
-      <c r="AB9" s="27"/>
-      <c r="AC9" s="27"/>
-      <c r="AD9" s="27"/>
-      <c r="AE9" s="27" t="s">
+      <c r="Q9" s="26"/>
+      <c r="R9" s="26"/>
+      <c r="S9" s="26"/>
+      <c r="T9" s="26"/>
+      <c r="U9" s="26"/>
+      <c r="V9" s="26"/>
+      <c r="W9" s="26"/>
+      <c r="X9" s="26"/>
+      <c r="Y9" s="26"/>
+      <c r="Z9" s="26"/>
+      <c r="AA9" s="26"/>
+      <c r="AB9" s="26"/>
+      <c r="AC9" s="26"/>
+      <c r="AD9" s="26"/>
+      <c r="AE9" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="AF9" s="27"/>
-      <c r="AG9" s="27"/>
-      <c r="AH9" s="27"/>
-      <c r="AI9" s="27"/>
-      <c r="AJ9" s="27"/>
-      <c r="AK9" s="27"/>
-      <c r="AL9" s="27"/>
-      <c r="AM9" s="27"/>
-      <c r="AN9" s="27"/>
-      <c r="AO9" s="27"/>
-      <c r="AP9" s="27"/>
-      <c r="AQ9" s="27"/>
-      <c r="AR9" s="27"/>
-      <c r="AS9" s="27"/>
-      <c r="AT9" s="27"/>
-      <c r="AU9" s="27"/>
-      <c r="AV9" s="27"/>
-      <c r="AW9" s="27"/>
-      <c r="AX9" s="27"/>
-      <c r="AY9" s="27"/>
-      <c r="AZ9" s="27"/>
-      <c r="BA9" s="27"/>
-      <c r="BB9" s="27"/>
-      <c r="BC9" s="27"/>
-      <c r="BD9" s="27"/>
-      <c r="BE9" s="27"/>
-      <c r="BF9" s="27"/>
-      <c r="BG9" s="27"/>
-      <c r="BH9" s="27"/>
-      <c r="BI9" s="27"/>
+      <c r="AF9" s="26"/>
+      <c r="AG9" s="26"/>
+      <c r="AH9" s="26"/>
+      <c r="AI9" s="26"/>
+      <c r="AJ9" s="26"/>
+      <c r="AK9" s="26"/>
+      <c r="AL9" s="26"/>
+      <c r="AM9" s="26"/>
+      <c r="AN9" s="26"/>
+      <c r="AO9" s="26"/>
+      <c r="AP9" s="26"/>
+      <c r="AQ9" s="26"/>
+      <c r="AR9" s="26"/>
+      <c r="AS9" s="26"/>
+      <c r="AT9" s="26"/>
+      <c r="AU9" s="26"/>
+      <c r="AV9" s="26"/>
+      <c r="AW9" s="26"/>
+      <c r="AX9" s="26"/>
+      <c r="AY9" s="26"/>
+      <c r="AZ9" s="26"/>
+      <c r="BA9" s="26"/>
+      <c r="BB9" s="26"/>
+      <c r="BC9" s="26"/>
+      <c r="BD9" s="26"/>
+      <c r="BE9" s="26"/>
+      <c r="BF9" s="26"/>
+      <c r="BG9" s="26"/>
+      <c r="BH9" s="26"/>
+      <c r="BI9" s="26"/>
       <c r="BJ9" s="1"/>
       <c r="BK9" s="1"/>
       <c r="BL9" s="1"/>
@@ -5138,75 +5078,75 @@
       <c r="IX9" s="1"/>
     </row>
     <row r="10" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="26" t="s">
+      <c r="A10" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-      <c r="D10" s="26" t="s">
-        <v>65</v>
+      <c r="B10" s="47"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="47" t="s">
+        <v>64</v>
       </c>
-      <c r="E10" s="26"/>
-      <c r="F10" s="26"/>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
-      <c r="J10" s="26"/>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="26"/>
-      <c r="O10" s="26"/>
-      <c r="P10" s="26" t="s">
+      <c r="E10" s="47"/>
+      <c r="F10" s="47"/>
+      <c r="G10" s="47"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="47"/>
+      <c r="K10" s="47"/>
+      <c r="L10" s="47"/>
+      <c r="M10" s="47"/>
+      <c r="N10" s="47"/>
+      <c r="O10" s="47"/>
+      <c r="P10" s="47" t="s">
         <v>31</v>
       </c>
-      <c r="Q10" s="26"/>
-      <c r="R10" s="26"/>
-      <c r="S10" s="26"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="26"/>
-      <c r="V10" s="26"/>
-      <c r="W10" s="26"/>
-      <c r="X10" s="26"/>
-      <c r="Y10" s="26"/>
-      <c r="Z10" s="26"/>
-      <c r="AA10" s="26"/>
-      <c r="AB10" s="26"/>
-      <c r="AC10" s="26"/>
-      <c r="AD10" s="26"/>
-      <c r="AE10" s="26" t="s">
+      <c r="Q10" s="47"/>
+      <c r="R10" s="47"/>
+      <c r="S10" s="47"/>
+      <c r="T10" s="47"/>
+      <c r="U10" s="47"/>
+      <c r="V10" s="47"/>
+      <c r="W10" s="47"/>
+      <c r="X10" s="47"/>
+      <c r="Y10" s="47"/>
+      <c r="Z10" s="47"/>
+      <c r="AA10" s="47"/>
+      <c r="AB10" s="47"/>
+      <c r="AC10" s="47"/>
+      <c r="AD10" s="47"/>
+      <c r="AE10" s="47" t="s">
         <v>32</v>
       </c>
-      <c r="AF10" s="26"/>
-      <c r="AG10" s="26"/>
-      <c r="AH10" s="26"/>
-      <c r="AI10" s="26"/>
-      <c r="AJ10" s="26"/>
-      <c r="AK10" s="26"/>
-      <c r="AL10" s="26"/>
-      <c r="AM10" s="26"/>
-      <c r="AN10" s="26"/>
-      <c r="AO10" s="26"/>
-      <c r="AP10" s="26"/>
-      <c r="AQ10" s="26"/>
-      <c r="AR10" s="26"/>
-      <c r="AS10" s="26"/>
-      <c r="AT10" s="26"/>
-      <c r="AU10" s="26"/>
-      <c r="AV10" s="26"/>
-      <c r="AW10" s="26"/>
-      <c r="AX10" s="26"/>
-      <c r="AY10" s="26"/>
-      <c r="AZ10" s="26"/>
-      <c r="BA10" s="26"/>
-      <c r="BB10" s="26"/>
-      <c r="BC10" s="26"/>
-      <c r="BD10" s="26"/>
-      <c r="BE10" s="26"/>
-      <c r="BF10" s="26"/>
-      <c r="BG10" s="26"/>
-      <c r="BH10" s="26"/>
-      <c r="BI10" s="26"/>
+      <c r="AF10" s="47"/>
+      <c r="AG10" s="47"/>
+      <c r="AH10" s="47"/>
+      <c r="AI10" s="47"/>
+      <c r="AJ10" s="47"/>
+      <c r="AK10" s="47"/>
+      <c r="AL10" s="47"/>
+      <c r="AM10" s="47"/>
+      <c r="AN10" s="47"/>
+      <c r="AO10" s="47"/>
+      <c r="AP10" s="47"/>
+      <c r="AQ10" s="47"/>
+      <c r="AR10" s="47"/>
+      <c r="AS10" s="47"/>
+      <c r="AT10" s="47"/>
+      <c r="AU10" s="47"/>
+      <c r="AV10" s="47"/>
+      <c r="AW10" s="47"/>
+      <c r="AX10" s="47"/>
+      <c r="AY10" s="47"/>
+      <c r="AZ10" s="47"/>
+      <c r="BA10" s="47"/>
+      <c r="BB10" s="47"/>
+      <c r="BC10" s="47"/>
+      <c r="BD10" s="47"/>
+      <c r="BE10" s="47"/>
+      <c r="BF10" s="47"/>
+      <c r="BG10" s="47"/>
+      <c r="BH10" s="47"/>
+      <c r="BI10" s="47"/>
       <c r="BJ10" s="1"/>
       <c r="BK10" s="1"/>
       <c r="BL10" s="1"/>
@@ -5406,75 +5346,75 @@
       <c r="IX10" s="1"/>
     </row>
     <row r="11" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="47" t="s">
+      <c r="A11" s="52" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="47"/>
-      <c r="C11" s="47"/>
-      <c r="D11" s="27" t="s">
-        <v>65</v>
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="26" t="s">
+        <v>64</v>
       </c>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27"/>
-      <c r="K11" s="27"/>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="27"/>
-      <c r="O11" s="27"/>
-      <c r="P11" s="27" t="s">
+      <c r="E11" s="26"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="26"/>
+      <c r="O11" s="26"/>
+      <c r="P11" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="Q11" s="27"/>
-      <c r="R11" s="27"/>
-      <c r="S11" s="27"/>
-      <c r="T11" s="27"/>
-      <c r="U11" s="27"/>
-      <c r="V11" s="27"/>
-      <c r="W11" s="27"/>
-      <c r="X11" s="27"/>
-      <c r="Y11" s="27"/>
-      <c r="Z11" s="27"/>
-      <c r="AA11" s="27"/>
-      <c r="AB11" s="27"/>
-      <c r="AC11" s="27"/>
-      <c r="AD11" s="27"/>
-      <c r="AE11" s="27" t="s">
+      <c r="Q11" s="26"/>
+      <c r="R11" s="26"/>
+      <c r="S11" s="26"/>
+      <c r="T11" s="26"/>
+      <c r="U11" s="26"/>
+      <c r="V11" s="26"/>
+      <c r="W11" s="26"/>
+      <c r="X11" s="26"/>
+      <c r="Y11" s="26"/>
+      <c r="Z11" s="26"/>
+      <c r="AA11" s="26"/>
+      <c r="AB11" s="26"/>
+      <c r="AC11" s="26"/>
+      <c r="AD11" s="26"/>
+      <c r="AE11" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="AF11" s="27"/>
-      <c r="AG11" s="27"/>
-      <c r="AH11" s="27"/>
-      <c r="AI11" s="27"/>
-      <c r="AJ11" s="27"/>
-      <c r="AK11" s="27"/>
-      <c r="AL11" s="27"/>
-      <c r="AM11" s="27"/>
-      <c r="AN11" s="27"/>
-      <c r="AO11" s="27"/>
-      <c r="AP11" s="27"/>
-      <c r="AQ11" s="27"/>
-      <c r="AR11" s="27"/>
-      <c r="AS11" s="27"/>
-      <c r="AT11" s="27"/>
-      <c r="AU11" s="27"/>
-      <c r="AV11" s="27"/>
-      <c r="AW11" s="27"/>
-      <c r="AX11" s="27"/>
-      <c r="AY11" s="27"/>
-      <c r="AZ11" s="27"/>
-      <c r="BA11" s="27"/>
-      <c r="BB11" s="27"/>
-      <c r="BC11" s="27"/>
-      <c r="BD11" s="27"/>
-      <c r="BE11" s="27"/>
-      <c r="BF11" s="27"/>
-      <c r="BG11" s="27"/>
-      <c r="BH11" s="27"/>
-      <c r="BI11" s="27"/>
+      <c r="AF11" s="26"/>
+      <c r="AG11" s="26"/>
+      <c r="AH11" s="26"/>
+      <c r="AI11" s="26"/>
+      <c r="AJ11" s="26"/>
+      <c r="AK11" s="26"/>
+      <c r="AL11" s="26"/>
+      <c r="AM11" s="26"/>
+      <c r="AN11" s="26"/>
+      <c r="AO11" s="26"/>
+      <c r="AP11" s="26"/>
+      <c r="AQ11" s="26"/>
+      <c r="AR11" s="26"/>
+      <c r="AS11" s="26"/>
+      <c r="AT11" s="26"/>
+      <c r="AU11" s="26"/>
+      <c r="AV11" s="26"/>
+      <c r="AW11" s="26"/>
+      <c r="AX11" s="26"/>
+      <c r="AY11" s="26"/>
+      <c r="AZ11" s="26"/>
+      <c r="BA11" s="26"/>
+      <c r="BB11" s="26"/>
+      <c r="BC11" s="26"/>
+      <c r="BD11" s="26"/>
+      <c r="BE11" s="26"/>
+      <c r="BF11" s="26"/>
+      <c r="BG11" s="26"/>
+      <c r="BH11" s="26"/>
+      <c r="BI11" s="26"/>
       <c r="BJ11" s="1"/>
       <c r="BK11" s="1"/>
       <c r="BL11" s="1"/>
@@ -5934,73 +5874,73 @@
       <c r="IX12" s="1"/>
     </row>
     <row r="13" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="46" t="s">
+      <c r="A13" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="46"/>
-      <c r="C13" s="46"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="46"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="46"/>
-      <c r="J13" s="46"/>
-      <c r="K13" s="46"/>
-      <c r="L13" s="46"/>
-      <c r="M13" s="46"/>
-      <c r="N13" s="46"/>
-      <c r="O13" s="46"/>
-      <c r="P13" s="46" t="s">
+      <c r="B13" s="51"/>
+      <c r="C13" s="51"/>
+      <c r="D13" s="51"/>
+      <c r="E13" s="51"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="51"/>
+      <c r="J13" s="51"/>
+      <c r="K13" s="51"/>
+      <c r="L13" s="51"/>
+      <c r="M13" s="51"/>
+      <c r="N13" s="51"/>
+      <c r="O13" s="51"/>
+      <c r="P13" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="Q13" s="46"/>
-      <c r="R13" s="46"/>
-      <c r="S13" s="46"/>
-      <c r="T13" s="46"/>
-      <c r="U13" s="46"/>
-      <c r="V13" s="46"/>
-      <c r="W13" s="46"/>
-      <c r="X13" s="46"/>
-      <c r="Y13" s="46"/>
-      <c r="Z13" s="46"/>
-      <c r="AA13" s="46"/>
-      <c r="AB13" s="46"/>
-      <c r="AC13" s="46"/>
-      <c r="AD13" s="46"/>
-      <c r="AE13" s="46"/>
-      <c r="AF13" s="46"/>
-      <c r="AG13" s="46"/>
-      <c r="AH13" s="46"/>
-      <c r="AI13" s="46"/>
-      <c r="AJ13" s="46"/>
-      <c r="AK13" s="46"/>
-      <c r="AL13" s="46"/>
-      <c r="AM13" s="46"/>
-      <c r="AN13" s="46"/>
-      <c r="AO13" s="46"/>
-      <c r="AP13" s="46"/>
-      <c r="AQ13" s="46"/>
-      <c r="AR13" s="46"/>
-      <c r="AS13" s="46"/>
-      <c r="AT13" s="46" t="s">
+      <c r="Q13" s="51"/>
+      <c r="R13" s="51"/>
+      <c r="S13" s="51"/>
+      <c r="T13" s="51"/>
+      <c r="U13" s="51"/>
+      <c r="V13" s="51"/>
+      <c r="W13" s="51"/>
+      <c r="X13" s="51"/>
+      <c r="Y13" s="51"/>
+      <c r="Z13" s="51"/>
+      <c r="AA13" s="51"/>
+      <c r="AB13" s="51"/>
+      <c r="AC13" s="51"/>
+      <c r="AD13" s="51"/>
+      <c r="AE13" s="51"/>
+      <c r="AF13" s="51"/>
+      <c r="AG13" s="51"/>
+      <c r="AH13" s="51"/>
+      <c r="AI13" s="51"/>
+      <c r="AJ13" s="51"/>
+      <c r="AK13" s="51"/>
+      <c r="AL13" s="51"/>
+      <c r="AM13" s="51"/>
+      <c r="AN13" s="51"/>
+      <c r="AO13" s="51"/>
+      <c r="AP13" s="51"/>
+      <c r="AQ13" s="51"/>
+      <c r="AR13" s="51"/>
+      <c r="AS13" s="51"/>
+      <c r="AT13" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="AU13" s="46"/>
-      <c r="AV13" s="46"/>
-      <c r="AW13" s="46"/>
-      <c r="AX13" s="46"/>
-      <c r="AY13" s="46"/>
-      <c r="AZ13" s="46"/>
-      <c r="BA13" s="46"/>
-      <c r="BB13" s="46"/>
-      <c r="BC13" s="46"/>
-      <c r="BD13" s="46"/>
-      <c r="BE13" s="46"/>
-      <c r="BF13" s="46"/>
-      <c r="BG13" s="46"/>
-      <c r="BH13" s="46"/>
-      <c r="BI13" s="46"/>
+      <c r="AU13" s="51"/>
+      <c r="AV13" s="51"/>
+      <c r="AW13" s="51"/>
+      <c r="AX13" s="51"/>
+      <c r="AY13" s="51"/>
+      <c r="AZ13" s="51"/>
+      <c r="BA13" s="51"/>
+      <c r="BB13" s="51"/>
+      <c r="BC13" s="51"/>
+      <c r="BD13" s="51"/>
+      <c r="BE13" s="51"/>
+      <c r="BF13" s="51"/>
+      <c r="BG13" s="51"/>
+      <c r="BH13" s="51"/>
+      <c r="BI13" s="51"/>
       <c r="BJ13" s="1"/>
       <c r="BK13" s="1"/>
       <c r="BL13" s="1"/>
@@ -6215,7 +6155,7 @@
       <c r="M14" s="7"/>
       <c r="N14" s="7"/>
       <c r="O14" s="8"/>
-      <c r="P14" s="54" t="s">
+      <c r="P14" s="23" t="s">
         <v>61</v>
       </c>
       <c r="Q14" s="9"/>
@@ -6739,7 +6679,7 @@
       <c r="M16" s="12"/>
       <c r="N16" s="12"/>
       <c r="O16" s="13"/>
-      <c r="P16" s="55" t="s">
+      <c r="P16" s="24" t="s">
         <v>62</v>
       </c>
       <c r="Q16" s="15"/>
@@ -7265,7 +7205,7 @@
       <c r="O18" s="13"/>
       <c r="P18" s="14"/>
       <c r="Q18" s="15" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="R18" s="15"/>
       <c r="S18" s="15"/>
@@ -7527,7 +7467,7 @@
       <c r="O19" s="13"/>
       <c r="P19" s="14"/>
       <c r="Q19" s="18" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="R19" s="18"/>
       <c r="S19" s="18"/>
@@ -7787,11 +7727,11 @@
       <c r="M20" s="12"/>
       <c r="N20" s="12"/>
       <c r="O20" s="13"/>
-      <c r="P20" s="14"/>
+      <c r="P20" s="24" t="s">
+        <v>65</v>
+      </c>
       <c r="Q20" s="18"/>
-      <c r="R20" s="18" t="s">
-        <v>66</v>
-      </c>
+      <c r="R20" s="18"/>
       <c r="S20" s="18"/>
       <c r="T20" s="15"/>
       <c r="U20" s="15"/>
@@ -8050,10 +7990,10 @@
       <c r="N21" s="12"/>
       <c r="O21" s="13"/>
       <c r="P21" s="14"/>
-      <c r="Q21" s="18"/>
-      <c r="R21" s="18" t="s">
-        <v>67</v>
+      <c r="Q21" s="18" t="s">
+        <v>66</v>
       </c>
+      <c r="R21" s="18"/>
       <c r="S21" s="18"/>
       <c r="T21" s="15"/>
       <c r="U21" s="15"/>
@@ -8312,10 +8252,10 @@
       <c r="N22" s="12"/>
       <c r="O22" s="13"/>
       <c r="P22" s="14"/>
-      <c r="Q22" s="18"/>
-      <c r="R22" s="18" t="s">
+      <c r="Q22" s="18" t="s">
         <v>68</v>
       </c>
+      <c r="R22" s="18"/>
       <c r="S22" s="18"/>
       <c r="T22" s="15"/>
       <c r="U22" s="15"/>
@@ -8573,15 +8513,15 @@
       <c r="M23" s="12"/>
       <c r="N23" s="12"/>
       <c r="O23" s="13"/>
-      <c r="P23" s="55" t="s">
-        <v>69</v>
+      <c r="P23" s="14"/>
+      <c r="Q23" s="15" t="s">
+        <v>70</v>
       </c>
-      <c r="Q23" s="18"/>
-      <c r="R23" s="18"/>
-      <c r="S23" s="18"/>
+      <c r="R23" s="15"/>
+      <c r="S23" s="15"/>
       <c r="T23" s="15"/>
       <c r="U23" s="15"/>
-      <c r="V23" s="15"/>
+      <c r="V23" s="18"/>
       <c r="W23" s="15"/>
       <c r="X23" s="15"/>
       <c r="Y23" s="15"/>
@@ -8822,7 +8762,7 @@
     <row r="24" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11"/>
       <c r="B24" s="17"/>
-      <c r="C24" s="18"/>
+      <c r="C24" s="12"/>
       <c r="D24" s="12"/>
       <c r="E24" s="12"/>
       <c r="F24" s="12"/>
@@ -8835,15 +8775,15 @@
       <c r="M24" s="12"/>
       <c r="N24" s="12"/>
       <c r="O24" s="13"/>
-      <c r="P24" s="14"/>
-      <c r="Q24" s="18" t="s">
-        <v>70</v>
+      <c r="P24" s="25" t="s">
+        <v>69</v>
       </c>
-      <c r="R24" s="18"/>
-      <c r="S24" s="18"/>
+      <c r="Q24" s="20"/>
+      <c r="R24" s="15"/>
+      <c r="S24" s="15"/>
       <c r="T24" s="15"/>
-      <c r="U24" s="15"/>
-      <c r="V24" s="15"/>
+      <c r="U24" s="18"/>
+      <c r="V24" s="18"/>
       <c r="W24" s="15"/>
       <c r="X24" s="15"/>
       <c r="Y24" s="15"/>
@@ -8867,8 +8807,10 @@
       <c r="AQ24" s="15"/>
       <c r="AR24" s="15"/>
       <c r="AS24" s="16"/>
-      <c r="AT24" s="11"/>
-      <c r="AU24" s="17"/>
+      <c r="AT24" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="AU24" s="12"/>
       <c r="AV24" s="12"/>
       <c r="AW24" s="12"/>
       <c r="AX24" s="12"/>
@@ -9084,7 +9026,7 @@
     <row r="25" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11"/>
       <c r="B25" s="17"/>
-      <c r="C25" s="18"/>
+      <c r="C25" s="12"/>
       <c r="D25" s="12"/>
       <c r="E25" s="12"/>
       <c r="F25" s="12"/>
@@ -9097,15 +9039,13 @@
       <c r="M25" s="12"/>
       <c r="N25" s="12"/>
       <c r="O25" s="13"/>
-      <c r="P25" s="14"/>
-      <c r="Q25" s="18" t="s">
-        <v>72</v>
-      </c>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="20"/>
       <c r="R25" s="18"/>
       <c r="S25" s="18"/>
-      <c r="T25" s="15"/>
-      <c r="U25" s="15"/>
-      <c r="V25" s="15"/>
+      <c r="T25" s="18"/>
+      <c r="U25" s="21"/>
+      <c r="V25" s="21"/>
       <c r="W25" s="15"/>
       <c r="X25" s="15"/>
       <c r="Y25" s="15"/>
@@ -9130,7 +9070,7 @@
       <c r="AR25" s="15"/>
       <c r="AS25" s="16"/>
       <c r="AT25" s="11"/>
-      <c r="AU25" s="17"/>
+      <c r="AU25" s="12"/>
       <c r="AV25" s="12"/>
       <c r="AW25" s="12"/>
       <c r="AX25" s="12"/>
@@ -9346,7 +9286,7 @@
     <row r="26" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11"/>
       <c r="B26" s="17"/>
-      <c r="C26" s="18"/>
+      <c r="C26" s="12"/>
       <c r="D26" s="12"/>
       <c r="E26" s="12"/>
       <c r="F26" s="12"/>
@@ -9359,15 +9299,13 @@
       <c r="M26" s="12"/>
       <c r="N26" s="12"/>
       <c r="O26" s="13"/>
-      <c r="P26" s="14"/>
-      <c r="Q26" s="15" t="s">
-        <v>73</v>
-      </c>
-      <c r="R26" s="15"/>
-      <c r="S26" s="15"/>
-      <c r="T26" s="15"/>
-      <c r="U26" s="15"/>
-      <c r="V26" s="18"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="20"/>
+      <c r="R26" s="18"/>
+      <c r="S26" s="18"/>
+      <c r="T26" s="18"/>
+      <c r="U26" s="21"/>
+      <c r="V26" s="21"/>
       <c r="W26" s="15"/>
       <c r="X26" s="15"/>
       <c r="Y26" s="15"/>
@@ -9392,7 +9330,7 @@
       <c r="AR26" s="15"/>
       <c r="AS26" s="16"/>
       <c r="AT26" s="11"/>
-      <c r="AU26" s="17"/>
+      <c r="AU26" s="12"/>
       <c r="AV26" s="12"/>
       <c r="AW26" s="12"/>
       <c r="AX26" s="12"/>
@@ -9609,9 +9547,9 @@
       <c r="A27" s="11"/>
       <c r="B27" s="17"/>
       <c r="C27" s="12"/>
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
       <c r="G27" s="12"/>
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
@@ -9621,15 +9559,13 @@
       <c r="M27" s="12"/>
       <c r="N27" s="12"/>
       <c r="O27" s="13"/>
-      <c r="P27" s="14"/>
-      <c r="Q27" s="15"/>
-      <c r="R27" s="15" t="s">
-        <v>75</v>
-      </c>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="20"/>
+      <c r="R27" s="15"/>
       <c r="S27" s="15"/>
       <c r="T27" s="15"/>
-      <c r="U27" s="15"/>
-      <c r="V27" s="15"/>
+      <c r="U27" s="18"/>
+      <c r="V27" s="18"/>
       <c r="W27" s="15"/>
       <c r="X27" s="15"/>
       <c r="Y27" s="15"/>
@@ -9883,15 +9819,13 @@
       <c r="M28" s="12"/>
       <c r="N28" s="12"/>
       <c r="O28" s="13"/>
-      <c r="P28" s="20"/>
-      <c r="Q28" s="21"/>
-      <c r="R28" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="S28" s="18"/>
-      <c r="T28" s="18"/>
-      <c r="U28" s="22"/>
-      <c r="V28" s="22"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="20"/>
+      <c r="R28" s="15"/>
+      <c r="S28" s="15"/>
+      <c r="T28" s="15"/>
+      <c r="U28" s="18"/>
+      <c r="V28" s="18"/>
       <c r="W28" s="15"/>
       <c r="X28" s="15"/>
       <c r="Y28" s="15"/>
@@ -10145,15 +10079,13 @@
       <c r="M29" s="12"/>
       <c r="N29" s="12"/>
       <c r="O29" s="13"/>
-      <c r="P29" s="20"/>
-      <c r="Q29" s="21"/>
-      <c r="R29" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="S29" s="18"/>
-      <c r="T29" s="18"/>
-      <c r="U29" s="22"/>
-      <c r="V29" s="22"/>
+      <c r="P29" s="19"/>
+      <c r="Q29" s="20"/>
+      <c r="R29" s="15"/>
+      <c r="S29" s="15"/>
+      <c r="T29" s="15"/>
+      <c r="U29" s="18"/>
+      <c r="V29" s="18"/>
       <c r="W29" s="15"/>
       <c r="X29" s="15"/>
       <c r="Y29" s="15"/>
@@ -10407,10 +10339,8 @@
       <c r="M30" s="12"/>
       <c r="N30" s="12"/>
       <c r="O30" s="13"/>
-      <c r="P30" s="56" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q30" s="21"/>
+      <c r="P30" s="19"/>
+      <c r="Q30" s="18"/>
       <c r="R30" s="15"/>
       <c r="S30" s="15"/>
       <c r="T30" s="15"/>
@@ -10439,9 +10369,7 @@
       <c r="AQ30" s="15"/>
       <c r="AR30" s="15"/>
       <c r="AS30" s="16"/>
-      <c r="AT30" s="11" t="s">
-        <v>49</v>
-      </c>
+      <c r="AT30" s="11"/>
       <c r="AU30" s="12"/>
       <c r="AV30" s="12"/>
       <c r="AW30" s="12"/>
@@ -10671,13 +10599,13 @@
       <c r="M31" s="12"/>
       <c r="N31" s="12"/>
       <c r="O31" s="13"/>
-      <c r="P31" s="20"/>
-      <c r="Q31" s="21"/>
-      <c r="R31" s="18"/>
-      <c r="S31" s="18"/>
-      <c r="T31" s="18"/>
-      <c r="U31" s="22"/>
-      <c r="V31" s="22"/>
+      <c r="P31" s="14"/>
+      <c r="Q31" s="15"/>
+      <c r="R31" s="15"/>
+      <c r="S31" s="15"/>
+      <c r="T31" s="15"/>
+      <c r="U31" s="18"/>
+      <c r="V31" s="18"/>
       <c r="W31" s="15"/>
       <c r="X31" s="15"/>
       <c r="Y31" s="15"/>
@@ -10931,13 +10859,13 @@
       <c r="M32" s="12"/>
       <c r="N32" s="12"/>
       <c r="O32" s="13"/>
-      <c r="P32" s="20"/>
-      <c r="Q32" s="21"/>
-      <c r="R32" s="18"/>
-      <c r="S32" s="18"/>
-      <c r="T32" s="18"/>
-      <c r="U32" s="22"/>
-      <c r="V32" s="22"/>
+      <c r="P32" s="14"/>
+      <c r="Q32" s="12"/>
+      <c r="R32" s="15"/>
+      <c r="S32" s="15"/>
+      <c r="T32" s="15"/>
+      <c r="U32" s="15"/>
+      <c r="V32" s="15"/>
       <c r="W32" s="15"/>
       <c r="X32" s="15"/>
       <c r="Y32" s="15"/>
@@ -11191,15 +11119,15 @@
       <c r="M33" s="12"/>
       <c r="N33" s="12"/>
       <c r="O33" s="13"/>
-      <c r="P33" s="20"/>
-      <c r="Q33" s="21"/>
+      <c r="P33" s="14"/>
+      <c r="Q33" s="15"/>
       <c r="R33" s="15"/>
       <c r="S33" s="15"/>
       <c r="T33" s="15"/>
-      <c r="U33" s="18"/>
-      <c r="V33" s="18"/>
+      <c r="U33" s="15"/>
+      <c r="V33" s="15"/>
       <c r="W33" s="15"/>
-      <c r="X33" s="15"/>
+      <c r="X33" s="18"/>
       <c r="Y33" s="15"/>
       <c r="Z33" s="15"/>
       <c r="AA33" s="15"/>
@@ -11451,13 +11379,13 @@
       <c r="M34" s="12"/>
       <c r="N34" s="12"/>
       <c r="O34" s="13"/>
-      <c r="P34" s="20"/>
-      <c r="Q34" s="21"/>
+      <c r="P34" s="14"/>
+      <c r="Q34" s="15"/>
       <c r="R34" s="15"/>
       <c r="S34" s="15"/>
       <c r="T34" s="15"/>
-      <c r="U34" s="18"/>
-      <c r="V34" s="18"/>
+      <c r="U34" s="15"/>
+      <c r="V34" s="15"/>
       <c r="W34" s="15"/>
       <c r="X34" s="15"/>
       <c r="Y34" s="15"/>
@@ -11697,12 +11625,12 @@
     </row>
     <row r="35" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
+      <c r="B35" s="18"/>
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
       <c r="J35" s="12"/>
@@ -11711,13 +11639,13 @@
       <c r="M35" s="12"/>
       <c r="N35" s="12"/>
       <c r="O35" s="13"/>
-      <c r="P35" s="20"/>
-      <c r="Q35" s="21"/>
+      <c r="P35" s="14"/>
+      <c r="Q35" s="15"/>
       <c r="R35" s="15"/>
       <c r="S35" s="15"/>
       <c r="T35" s="15"/>
-      <c r="U35" s="18"/>
-      <c r="V35" s="18"/>
+      <c r="U35" s="15"/>
+      <c r="V35" s="15"/>
       <c r="W35" s="15"/>
       <c r="X35" s="15"/>
       <c r="Y35" s="15"/>
@@ -11743,7 +11671,7 @@
       <c r="AS35" s="16"/>
       <c r="AT35" s="11"/>
       <c r="AU35" s="12"/>
-      <c r="AV35" s="12"/>
+      <c r="AV35" s="17"/>
       <c r="AW35" s="12"/>
       <c r="AX35" s="12"/>
       <c r="AY35" s="12"/>
@@ -11957,7 +11885,7 @@
     </row>
     <row r="36" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11"/>
-      <c r="B36" s="17"/>
+      <c r="B36" s="12"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
       <c r="E36" s="12"/>
@@ -11971,13 +11899,13 @@
       <c r="M36" s="12"/>
       <c r="N36" s="12"/>
       <c r="O36" s="13"/>
-      <c r="P36" s="20"/>
-      <c r="Q36" s="18"/>
+      <c r="P36" s="22"/>
+      <c r="Q36" s="15"/>
       <c r="R36" s="15"/>
       <c r="S36" s="15"/>
       <c r="T36" s="15"/>
-      <c r="U36" s="18"/>
-      <c r="V36" s="18"/>
+      <c r="U36" s="15"/>
+      <c r="V36" s="15"/>
       <c r="W36" s="15"/>
       <c r="X36" s="15"/>
       <c r="Y36" s="15"/>
@@ -12217,7 +12145,7 @@
     </row>
     <row r="37" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="11"/>
-      <c r="B37" s="17"/>
+      <c r="B37" s="12"/>
       <c r="C37" s="12"/>
       <c r="D37" s="12"/>
       <c r="E37" s="12"/>
@@ -12236,8 +12164,8 @@
       <c r="R37" s="15"/>
       <c r="S37" s="15"/>
       <c r="T37" s="15"/>
-      <c r="U37" s="18"/>
-      <c r="V37" s="18"/>
+      <c r="U37" s="15"/>
+      <c r="V37" s="15"/>
       <c r="W37" s="15"/>
       <c r="X37" s="15"/>
       <c r="Y37" s="15"/>
@@ -12477,7 +12405,7 @@
     </row>
     <row r="38" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="11"/>
-      <c r="B38" s="17"/>
+      <c r="B38" s="12"/>
       <c r="C38" s="12"/>
       <c r="D38" s="12"/>
       <c r="E38" s="12"/>
@@ -12492,7 +12420,7 @@
       <c r="N38" s="12"/>
       <c r="O38" s="13"/>
       <c r="P38" s="14"/>
-      <c r="Q38" s="12"/>
+      <c r="Q38" s="15"/>
       <c r="R38" s="15"/>
       <c r="S38" s="15"/>
       <c r="T38" s="15"/>
@@ -12736,67 +12664,67 @@
       <c r="IX38" s="1"/>
     </row>
     <row r="39" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="11"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="12"/>
-      <c r="J39" s="12"/>
-      <c r="K39" s="12"/>
-      <c r="L39" s="12"/>
-      <c r="M39" s="12"/>
-      <c r="N39" s="12"/>
-      <c r="O39" s="13"/>
-      <c r="P39" s="14"/>
-      <c r="Q39" s="15"/>
-      <c r="R39" s="15"/>
-      <c r="S39" s="15"/>
-      <c r="T39" s="15"/>
-      <c r="U39" s="15"/>
-      <c r="V39" s="15"/>
-      <c r="W39" s="15"/>
-      <c r="X39" s="18"/>
-      <c r="Y39" s="15"/>
-      <c r="Z39" s="15"/>
-      <c r="AA39" s="15"/>
-      <c r="AB39" s="15"/>
-      <c r="AC39" s="15"/>
-      <c r="AD39" s="15"/>
-      <c r="AE39" s="15"/>
-      <c r="AF39" s="15"/>
-      <c r="AG39" s="15"/>
-      <c r="AH39" s="15"/>
-      <c r="AI39" s="15"/>
-      <c r="AJ39" s="15"/>
-      <c r="AK39" s="15"/>
-      <c r="AL39" s="15"/>
-      <c r="AM39" s="15"/>
-      <c r="AN39" s="15"/>
-      <c r="AO39" s="15"/>
-      <c r="AP39" s="15"/>
-      <c r="AQ39" s="15"/>
-      <c r="AR39" s="15"/>
-      <c r="AS39" s="16"/>
-      <c r="AT39" s="11"/>
-      <c r="AU39" s="12"/>
-      <c r="AV39" s="12"/>
-      <c r="AW39" s="12"/>
-      <c r="AX39" s="12"/>
-      <c r="AY39" s="12"/>
-      <c r="AZ39" s="12"/>
-      <c r="BA39" s="12"/>
-      <c r="BB39" s="12"/>
-      <c r="BC39" s="12"/>
-      <c r="BD39" s="12"/>
-      <c r="BE39" s="12"/>
-      <c r="BF39" s="12"/>
-      <c r="BG39" s="12"/>
-      <c r="BH39" s="12"/>
-      <c r="BI39" s="13"/>
+      <c r="A39" s="5"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+      <c r="K39" s="5"/>
+      <c r="L39" s="5"/>
+      <c r="M39" s="5"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+      <c r="S39" s="5"/>
+      <c r="T39" s="5"/>
+      <c r="U39" s="5"/>
+      <c r="V39" s="5"/>
+      <c r="W39" s="5"/>
+      <c r="X39" s="5"/>
+      <c r="Y39" s="5"/>
+      <c r="Z39" s="5"/>
+      <c r="AA39" s="5"/>
+      <c r="AB39" s="5"/>
+      <c r="AC39" s="5"/>
+      <c r="AD39" s="5"/>
+      <c r="AE39" s="5"/>
+      <c r="AF39" s="5"/>
+      <c r="AG39" s="5"/>
+      <c r="AH39" s="5"/>
+      <c r="AI39" s="5"/>
+      <c r="AJ39" s="5"/>
+      <c r="AK39" s="5"/>
+      <c r="AL39" s="5"/>
+      <c r="AM39" s="5"/>
+      <c r="AN39" s="5"/>
+      <c r="AO39" s="5"/>
+      <c r="AP39" s="5"/>
+      <c r="AQ39" s="5"/>
+      <c r="AR39" s="5"/>
+      <c r="AS39" s="5"/>
+      <c r="AT39" s="5"/>
+      <c r="AU39" s="5"/>
+      <c r="AV39" s="5"/>
+      <c r="AW39" s="5"/>
+      <c r="AX39" s="5"/>
+      <c r="AY39" s="5"/>
+      <c r="AZ39" s="5"/>
+      <c r="BA39" s="5"/>
+      <c r="BB39" s="5"/>
+      <c r="BC39" s="5"/>
+      <c r="BD39" s="5"/>
+      <c r="BE39" s="5"/>
+      <c r="BF39" s="5"/>
+      <c r="BG39" s="5"/>
+      <c r="BH39" s="5"/>
+      <c r="BI39" s="5"/>
       <c r="BJ39" s="1"/>
       <c r="BK39" s="1"/>
       <c r="BL39" s="1"/>
@@ -12995,1573 +12923,29 @@
       <c r="IW39" s="1"/>
       <c r="IX39" s="1"/>
     </row>
-    <row r="40" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="11"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="12"/>
-      <c r="J40" s="12"/>
-      <c r="K40" s="12"/>
-      <c r="L40" s="12"/>
-      <c r="M40" s="12"/>
-      <c r="N40" s="12"/>
-      <c r="O40" s="13"/>
-      <c r="P40" s="14"/>
-      <c r="Q40" s="15"/>
-      <c r="R40" s="15"/>
-      <c r="S40" s="15"/>
-      <c r="T40" s="15"/>
-      <c r="U40" s="15"/>
-      <c r="V40" s="15"/>
-      <c r="W40" s="15"/>
-      <c r="X40" s="15"/>
-      <c r="Y40" s="15"/>
-      <c r="Z40" s="15"/>
-      <c r="AA40" s="15"/>
-      <c r="AB40" s="15"/>
-      <c r="AC40" s="15"/>
-      <c r="AD40" s="15"/>
-      <c r="AE40" s="15"/>
-      <c r="AF40" s="15"/>
-      <c r="AG40" s="15"/>
-      <c r="AH40" s="15"/>
-      <c r="AI40" s="15"/>
-      <c r="AJ40" s="15"/>
-      <c r="AK40" s="15"/>
-      <c r="AL40" s="15"/>
-      <c r="AM40" s="15"/>
-      <c r="AN40" s="15"/>
-      <c r="AO40" s="15"/>
-      <c r="AP40" s="15"/>
-      <c r="AQ40" s="15"/>
-      <c r="AR40" s="15"/>
-      <c r="AS40" s="16"/>
-      <c r="AT40" s="11"/>
-      <c r="AU40" s="12"/>
-      <c r="AV40" s="12"/>
-      <c r="AW40" s="12"/>
-      <c r="AX40" s="12"/>
-      <c r="AY40" s="12"/>
-      <c r="AZ40" s="12"/>
-      <c r="BA40" s="12"/>
-      <c r="BB40" s="12"/>
-      <c r="BC40" s="12"/>
-      <c r="BD40" s="12"/>
-      <c r="BE40" s="12"/>
-      <c r="BF40" s="12"/>
-      <c r="BG40" s="12"/>
-      <c r="BH40" s="12"/>
-      <c r="BI40" s="13"/>
-      <c r="BJ40" s="1"/>
-      <c r="BK40" s="1"/>
-      <c r="BL40" s="1"/>
-      <c r="BM40" s="1"/>
-      <c r="BN40" s="1"/>
-      <c r="BO40" s="1"/>
-      <c r="BP40" s="1"/>
-      <c r="BQ40" s="1"/>
-      <c r="BR40" s="1"/>
-      <c r="BS40" s="1"/>
-      <c r="BT40" s="1"/>
-      <c r="BU40" s="1"/>
-      <c r="BV40" s="1"/>
-      <c r="BW40" s="1"/>
-      <c r="BX40" s="1"/>
-      <c r="BY40" s="1"/>
-      <c r="BZ40" s="1"/>
-      <c r="CA40" s="1"/>
-      <c r="CB40" s="1"/>
-      <c r="CC40" s="1"/>
-      <c r="CD40" s="1"/>
-      <c r="CE40" s="1"/>
-      <c r="CF40" s="1"/>
-      <c r="CG40" s="1"/>
-      <c r="CH40" s="1"/>
-      <c r="CI40" s="1"/>
-      <c r="CJ40" s="1"/>
-      <c r="CK40" s="1"/>
-      <c r="CL40" s="1"/>
-      <c r="CM40" s="1"/>
-      <c r="CN40" s="1"/>
-      <c r="CO40" s="1"/>
-      <c r="CP40" s="1"/>
-      <c r="CQ40" s="1"/>
-      <c r="CR40" s="1"/>
-      <c r="CS40" s="1"/>
-      <c r="CT40" s="1"/>
-      <c r="CU40" s="1"/>
-      <c r="CV40" s="1"/>
-      <c r="CW40" s="1"/>
-      <c r="CX40" s="1"/>
-      <c r="CY40" s="1"/>
-      <c r="CZ40" s="1"/>
-      <c r="DA40" s="1"/>
-      <c r="DB40" s="1"/>
-      <c r="DC40" s="1"/>
-      <c r="DD40" s="1"/>
-      <c r="DE40" s="1"/>
-      <c r="DF40" s="1"/>
-      <c r="DG40" s="1"/>
-      <c r="DH40" s="1"/>
-      <c r="DI40" s="1"/>
-      <c r="DJ40" s="1"/>
-      <c r="DK40" s="1"/>
-      <c r="DL40" s="1"/>
-      <c r="DM40" s="1"/>
-      <c r="DN40" s="1"/>
-      <c r="DO40" s="1"/>
-      <c r="DP40" s="1"/>
-      <c r="DQ40" s="1"/>
-      <c r="DR40" s="1"/>
-      <c r="DS40" s="1"/>
-      <c r="DT40" s="1"/>
-      <c r="DU40" s="1"/>
-      <c r="DV40" s="1"/>
-      <c r="DW40" s="1"/>
-      <c r="DX40" s="1"/>
-      <c r="DY40" s="1"/>
-      <c r="DZ40" s="1"/>
-      <c r="EA40" s="1"/>
-      <c r="EB40" s="1"/>
-      <c r="EC40" s="1"/>
-      <c r="ED40" s="1"/>
-      <c r="EE40" s="1"/>
-      <c r="EF40" s="1"/>
-      <c r="EG40" s="1"/>
-      <c r="EH40" s="1"/>
-      <c r="EI40" s="1"/>
-      <c r="EJ40" s="1"/>
-      <c r="EK40" s="1"/>
-      <c r="EL40" s="1"/>
-      <c r="EM40" s="1"/>
-      <c r="EN40" s="1"/>
-      <c r="EO40" s="1"/>
-      <c r="EP40" s="1"/>
-      <c r="EQ40" s="1"/>
-      <c r="ER40" s="1"/>
-      <c r="ES40" s="1"/>
-      <c r="ET40" s="1"/>
-      <c r="EU40" s="1"/>
-      <c r="EV40" s="1"/>
-      <c r="EW40" s="1"/>
-      <c r="EX40" s="1"/>
-      <c r="EY40" s="1"/>
-      <c r="EZ40" s="1"/>
-      <c r="FA40" s="1"/>
-      <c r="FB40" s="1"/>
-      <c r="FC40" s="1"/>
-      <c r="FD40" s="1"/>
-      <c r="FE40" s="1"/>
-      <c r="FF40" s="1"/>
-      <c r="FG40" s="1"/>
-      <c r="FH40" s="1"/>
-      <c r="FI40" s="1"/>
-      <c r="FJ40" s="1"/>
-      <c r="FK40" s="1"/>
-      <c r="FL40" s="1"/>
-      <c r="FM40" s="1"/>
-      <c r="FN40" s="1"/>
-      <c r="FO40" s="1"/>
-      <c r="FP40" s="1"/>
-      <c r="FQ40" s="1"/>
-      <c r="FR40" s="1"/>
-      <c r="FS40" s="1"/>
-      <c r="FT40" s="1"/>
-      <c r="FU40" s="1"/>
-      <c r="FV40" s="1"/>
-      <c r="FW40" s="1"/>
-      <c r="FX40" s="1"/>
-      <c r="FY40" s="1"/>
-      <c r="FZ40" s="1"/>
-      <c r="GA40" s="1"/>
-      <c r="GB40" s="1"/>
-      <c r="GC40" s="1"/>
-      <c r="GD40" s="1"/>
-      <c r="GE40" s="1"/>
-      <c r="GF40" s="1"/>
-      <c r="GG40" s="1"/>
-      <c r="GH40" s="1"/>
-      <c r="GI40" s="1"/>
-      <c r="GJ40" s="1"/>
-      <c r="GK40" s="1"/>
-      <c r="GL40" s="1"/>
-      <c r="GM40" s="1"/>
-      <c r="GN40" s="1"/>
-      <c r="GO40" s="1"/>
-      <c r="GP40" s="1"/>
-      <c r="GQ40" s="1"/>
-      <c r="GR40" s="1"/>
-      <c r="GS40" s="1"/>
-      <c r="GT40" s="1"/>
-      <c r="GU40" s="1"/>
-      <c r="GV40" s="1"/>
-      <c r="GW40" s="1"/>
-      <c r="GX40" s="1"/>
-      <c r="GY40" s="1"/>
-      <c r="GZ40" s="1"/>
-      <c r="HA40" s="1"/>
-      <c r="HB40" s="1"/>
-      <c r="HC40" s="1"/>
-      <c r="HD40" s="1"/>
-      <c r="HE40" s="1"/>
-      <c r="HF40" s="1"/>
-      <c r="HG40" s="1"/>
-      <c r="HH40" s="1"/>
-      <c r="HI40" s="1"/>
-      <c r="HJ40" s="1"/>
-      <c r="HK40" s="1"/>
-      <c r="HL40" s="1"/>
-      <c r="HM40" s="1"/>
-      <c r="HN40" s="1"/>
-      <c r="HO40" s="1"/>
-      <c r="HP40" s="1"/>
-      <c r="HQ40" s="1"/>
-      <c r="HR40" s="1"/>
-      <c r="HS40" s="1"/>
-      <c r="HT40" s="1"/>
-      <c r="HU40" s="1"/>
-      <c r="HV40" s="1"/>
-      <c r="HW40" s="1"/>
-      <c r="HX40" s="1"/>
-      <c r="HY40" s="1"/>
-      <c r="HZ40" s="1"/>
-      <c r="IA40" s="1"/>
-      <c r="IB40" s="1"/>
-      <c r="IC40" s="1"/>
-      <c r="ID40" s="1"/>
-      <c r="IE40" s="1"/>
-      <c r="IF40" s="1"/>
-      <c r="IG40" s="1"/>
-      <c r="IH40" s="1"/>
-      <c r="II40" s="1"/>
-      <c r="IJ40" s="1"/>
-      <c r="IK40" s="1"/>
-      <c r="IL40" s="1"/>
-      <c r="IM40" s="1"/>
-      <c r="IN40" s="1"/>
-      <c r="IO40" s="1"/>
-      <c r="IP40" s="1"/>
-      <c r="IQ40" s="1"/>
-      <c r="IR40" s="1"/>
-      <c r="IS40" s="1"/>
-      <c r="IT40" s="1"/>
-      <c r="IU40" s="1"/>
-      <c r="IV40" s="1"/>
-      <c r="IW40" s="1"/>
-      <c r="IX40" s="1"/>
-    </row>
-    <row r="41" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="11"/>
-      <c r="B41" s="18"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="12"/>
-      <c r="J41" s="12"/>
-      <c r="K41" s="12"/>
-      <c r="L41" s="12"/>
-      <c r="M41" s="12"/>
-      <c r="N41" s="12"/>
-      <c r="O41" s="13"/>
-      <c r="P41" s="14"/>
-      <c r="Q41" s="15"/>
-      <c r="R41" s="15"/>
-      <c r="S41" s="15"/>
-      <c r="T41" s="15"/>
-      <c r="U41" s="15"/>
-      <c r="V41" s="15"/>
-      <c r="W41" s="15"/>
-      <c r="X41" s="15"/>
-      <c r="Y41" s="15"/>
-      <c r="Z41" s="15"/>
-      <c r="AA41" s="15"/>
-      <c r="AB41" s="15"/>
-      <c r="AC41" s="15"/>
-      <c r="AD41" s="15"/>
-      <c r="AE41" s="15"/>
-      <c r="AF41" s="15"/>
-      <c r="AG41" s="15"/>
-      <c r="AH41" s="15"/>
-      <c r="AI41" s="15"/>
-      <c r="AJ41" s="15"/>
-      <c r="AK41" s="15"/>
-      <c r="AL41" s="15"/>
-      <c r="AM41" s="15"/>
-      <c r="AN41" s="15"/>
-      <c r="AO41" s="15"/>
-      <c r="AP41" s="15"/>
-      <c r="AQ41" s="15"/>
-      <c r="AR41" s="15"/>
-      <c r="AS41" s="16"/>
-      <c r="AT41" s="11"/>
-      <c r="AU41" s="12"/>
-      <c r="AV41" s="17"/>
-      <c r="AW41" s="12"/>
-      <c r="AX41" s="12"/>
-      <c r="AY41" s="12"/>
-      <c r="AZ41" s="12"/>
-      <c r="BA41" s="12"/>
-      <c r="BB41" s="12"/>
-      <c r="BC41" s="12"/>
-      <c r="BD41" s="12"/>
-      <c r="BE41" s="12"/>
-      <c r="BF41" s="12"/>
-      <c r="BG41" s="12"/>
-      <c r="BH41" s="12"/>
-      <c r="BI41" s="13"/>
-      <c r="BJ41" s="1"/>
-      <c r="BK41" s="1"/>
-      <c r="BL41" s="1"/>
-      <c r="BM41" s="1"/>
-      <c r="BN41" s="1"/>
-      <c r="BO41" s="1"/>
-      <c r="BP41" s="1"/>
-      <c r="BQ41" s="1"/>
-      <c r="BR41" s="1"/>
-      <c r="BS41" s="1"/>
-      <c r="BT41" s="1"/>
-      <c r="BU41" s="1"/>
-      <c r="BV41" s="1"/>
-      <c r="BW41" s="1"/>
-      <c r="BX41" s="1"/>
-      <c r="BY41" s="1"/>
-      <c r="BZ41" s="1"/>
-      <c r="CA41" s="1"/>
-      <c r="CB41" s="1"/>
-      <c r="CC41" s="1"/>
-      <c r="CD41" s="1"/>
-      <c r="CE41" s="1"/>
-      <c r="CF41" s="1"/>
-      <c r="CG41" s="1"/>
-      <c r="CH41" s="1"/>
-      <c r="CI41" s="1"/>
-      <c r="CJ41" s="1"/>
-      <c r="CK41" s="1"/>
-      <c r="CL41" s="1"/>
-      <c r="CM41" s="1"/>
-      <c r="CN41" s="1"/>
-      <c r="CO41" s="1"/>
-      <c r="CP41" s="1"/>
-      <c r="CQ41" s="1"/>
-      <c r="CR41" s="1"/>
-      <c r="CS41" s="1"/>
-      <c r="CT41" s="1"/>
-      <c r="CU41" s="1"/>
-      <c r="CV41" s="1"/>
-      <c r="CW41" s="1"/>
-      <c r="CX41" s="1"/>
-      <c r="CY41" s="1"/>
-      <c r="CZ41" s="1"/>
-      <c r="DA41" s="1"/>
-      <c r="DB41" s="1"/>
-      <c r="DC41" s="1"/>
-      <c r="DD41" s="1"/>
-      <c r="DE41" s="1"/>
-      <c r="DF41" s="1"/>
-      <c r="DG41" s="1"/>
-      <c r="DH41" s="1"/>
-      <c r="DI41" s="1"/>
-      <c r="DJ41" s="1"/>
-      <c r="DK41" s="1"/>
-      <c r="DL41" s="1"/>
-      <c r="DM41" s="1"/>
-      <c r="DN41" s="1"/>
-      <c r="DO41" s="1"/>
-      <c r="DP41" s="1"/>
-      <c r="DQ41" s="1"/>
-      <c r="DR41" s="1"/>
-      <c r="DS41" s="1"/>
-      <c r="DT41" s="1"/>
-      <c r="DU41" s="1"/>
-      <c r="DV41" s="1"/>
-      <c r="DW41" s="1"/>
-      <c r="DX41" s="1"/>
-      <c r="DY41" s="1"/>
-      <c r="DZ41" s="1"/>
-      <c r="EA41" s="1"/>
-      <c r="EB41" s="1"/>
-      <c r="EC41" s="1"/>
-      <c r="ED41" s="1"/>
-      <c r="EE41" s="1"/>
-      <c r="EF41" s="1"/>
-      <c r="EG41" s="1"/>
-      <c r="EH41" s="1"/>
-      <c r="EI41" s="1"/>
-      <c r="EJ41" s="1"/>
-      <c r="EK41" s="1"/>
-      <c r="EL41" s="1"/>
-      <c r="EM41" s="1"/>
-      <c r="EN41" s="1"/>
-      <c r="EO41" s="1"/>
-      <c r="EP41" s="1"/>
-      <c r="EQ41" s="1"/>
-      <c r="ER41" s="1"/>
-      <c r="ES41" s="1"/>
-      <c r="ET41" s="1"/>
-      <c r="EU41" s="1"/>
-      <c r="EV41" s="1"/>
-      <c r="EW41" s="1"/>
-      <c r="EX41" s="1"/>
-      <c r="EY41" s="1"/>
-      <c r="EZ41" s="1"/>
-      <c r="FA41" s="1"/>
-      <c r="FB41" s="1"/>
-      <c r="FC41" s="1"/>
-      <c r="FD41" s="1"/>
-      <c r="FE41" s="1"/>
-      <c r="FF41" s="1"/>
-      <c r="FG41" s="1"/>
-      <c r="FH41" s="1"/>
-      <c r="FI41" s="1"/>
-      <c r="FJ41" s="1"/>
-      <c r="FK41" s="1"/>
-      <c r="FL41" s="1"/>
-      <c r="FM41" s="1"/>
-      <c r="FN41" s="1"/>
-      <c r="FO41" s="1"/>
-      <c r="FP41" s="1"/>
-      <c r="FQ41" s="1"/>
-      <c r="FR41" s="1"/>
-      <c r="FS41" s="1"/>
-      <c r="FT41" s="1"/>
-      <c r="FU41" s="1"/>
-      <c r="FV41" s="1"/>
-      <c r="FW41" s="1"/>
-      <c r="FX41" s="1"/>
-      <c r="FY41" s="1"/>
-      <c r="FZ41" s="1"/>
-      <c r="GA41" s="1"/>
-      <c r="GB41" s="1"/>
-      <c r="GC41" s="1"/>
-      <c r="GD41" s="1"/>
-      <c r="GE41" s="1"/>
-      <c r="GF41" s="1"/>
-      <c r="GG41" s="1"/>
-      <c r="GH41" s="1"/>
-      <c r="GI41" s="1"/>
-      <c r="GJ41" s="1"/>
-      <c r="GK41" s="1"/>
-      <c r="GL41" s="1"/>
-      <c r="GM41" s="1"/>
-      <c r="GN41" s="1"/>
-      <c r="GO41" s="1"/>
-      <c r="GP41" s="1"/>
-      <c r="GQ41" s="1"/>
-      <c r="GR41" s="1"/>
-      <c r="GS41" s="1"/>
-      <c r="GT41" s="1"/>
-      <c r="GU41" s="1"/>
-      <c r="GV41" s="1"/>
-      <c r="GW41" s="1"/>
-      <c r="GX41" s="1"/>
-      <c r="GY41" s="1"/>
-      <c r="GZ41" s="1"/>
-      <c r="HA41" s="1"/>
-      <c r="HB41" s="1"/>
-      <c r="HC41" s="1"/>
-      <c r="HD41" s="1"/>
-      <c r="HE41" s="1"/>
-      <c r="HF41" s="1"/>
-      <c r="HG41" s="1"/>
-      <c r="HH41" s="1"/>
-      <c r="HI41" s="1"/>
-      <c r="HJ41" s="1"/>
-      <c r="HK41" s="1"/>
-      <c r="HL41" s="1"/>
-      <c r="HM41" s="1"/>
-      <c r="HN41" s="1"/>
-      <c r="HO41" s="1"/>
-      <c r="HP41" s="1"/>
-      <c r="HQ41" s="1"/>
-      <c r="HR41" s="1"/>
-      <c r="HS41" s="1"/>
-      <c r="HT41" s="1"/>
-      <c r="HU41" s="1"/>
-      <c r="HV41" s="1"/>
-      <c r="HW41" s="1"/>
-      <c r="HX41" s="1"/>
-      <c r="HY41" s="1"/>
-      <c r="HZ41" s="1"/>
-      <c r="IA41" s="1"/>
-      <c r="IB41" s="1"/>
-      <c r="IC41" s="1"/>
-      <c r="ID41" s="1"/>
-      <c r="IE41" s="1"/>
-      <c r="IF41" s="1"/>
-      <c r="IG41" s="1"/>
-      <c r="IH41" s="1"/>
-      <c r="II41" s="1"/>
-      <c r="IJ41" s="1"/>
-      <c r="IK41" s="1"/>
-      <c r="IL41" s="1"/>
-      <c r="IM41" s="1"/>
-      <c r="IN41" s="1"/>
-      <c r="IO41" s="1"/>
-      <c r="IP41" s="1"/>
-      <c r="IQ41" s="1"/>
-      <c r="IR41" s="1"/>
-      <c r="IS41" s="1"/>
-      <c r="IT41" s="1"/>
-      <c r="IU41" s="1"/>
-      <c r="IV41" s="1"/>
-      <c r="IW41" s="1"/>
-      <c r="IX41" s="1"/>
-    </row>
-    <row r="42" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="11"/>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="12"/>
-      <c r="J42" s="12"/>
-      <c r="K42" s="12"/>
-      <c r="L42" s="12"/>
-      <c r="M42" s="12"/>
-      <c r="N42" s="12"/>
-      <c r="O42" s="13"/>
-      <c r="P42" s="23"/>
-      <c r="Q42" s="15"/>
-      <c r="R42" s="15"/>
-      <c r="S42" s="15"/>
-      <c r="T42" s="15"/>
-      <c r="U42" s="15"/>
-      <c r="V42" s="15"/>
-      <c r="W42" s="15"/>
-      <c r="X42" s="15"/>
-      <c r="Y42" s="15"/>
-      <c r="Z42" s="15"/>
-      <c r="AA42" s="15"/>
-      <c r="AB42" s="15"/>
-      <c r="AC42" s="15"/>
-      <c r="AD42" s="15"/>
-      <c r="AE42" s="15"/>
-      <c r="AF42" s="15"/>
-      <c r="AG42" s="15"/>
-      <c r="AH42" s="15"/>
-      <c r="AI42" s="15"/>
-      <c r="AJ42" s="15"/>
-      <c r="AK42" s="15"/>
-      <c r="AL42" s="15"/>
-      <c r="AM42" s="15"/>
-      <c r="AN42" s="15"/>
-      <c r="AO42" s="15"/>
-      <c r="AP42" s="15"/>
-      <c r="AQ42" s="15"/>
-      <c r="AR42" s="15"/>
-      <c r="AS42" s="16"/>
-      <c r="AT42" s="11"/>
-      <c r="AU42" s="12"/>
-      <c r="AV42" s="12"/>
-      <c r="AW42" s="12"/>
-      <c r="AX42" s="12"/>
-      <c r="AY42" s="12"/>
-      <c r="AZ42" s="12"/>
-      <c r="BA42" s="12"/>
-      <c r="BB42" s="12"/>
-      <c r="BC42" s="12"/>
-      <c r="BD42" s="12"/>
-      <c r="BE42" s="12"/>
-      <c r="BF42" s="12"/>
-      <c r="BG42" s="12"/>
-      <c r="BH42" s="12"/>
-      <c r="BI42" s="13"/>
-      <c r="BJ42" s="1"/>
-      <c r="BK42" s="1"/>
-      <c r="BL42" s="1"/>
-      <c r="BM42" s="1"/>
-      <c r="BN42" s="1"/>
-      <c r="BO42" s="1"/>
-      <c r="BP42" s="1"/>
-      <c r="BQ42" s="1"/>
-      <c r="BR42" s="1"/>
-      <c r="BS42" s="1"/>
-      <c r="BT42" s="1"/>
-      <c r="BU42" s="1"/>
-      <c r="BV42" s="1"/>
-      <c r="BW42" s="1"/>
-      <c r="BX42" s="1"/>
-      <c r="BY42" s="1"/>
-      <c r="BZ42" s="1"/>
-      <c r="CA42" s="1"/>
-      <c r="CB42" s="1"/>
-      <c r="CC42" s="1"/>
-      <c r="CD42" s="1"/>
-      <c r="CE42" s="1"/>
-      <c r="CF42" s="1"/>
-      <c r="CG42" s="1"/>
-      <c r="CH42" s="1"/>
-      <c r="CI42" s="1"/>
-      <c r="CJ42" s="1"/>
-      <c r="CK42" s="1"/>
-      <c r="CL42" s="1"/>
-      <c r="CM42" s="1"/>
-      <c r="CN42" s="1"/>
-      <c r="CO42" s="1"/>
-      <c r="CP42" s="1"/>
-      <c r="CQ42" s="1"/>
-      <c r="CR42" s="1"/>
-      <c r="CS42" s="1"/>
-      <c r="CT42" s="1"/>
-      <c r="CU42" s="1"/>
-      <c r="CV42" s="1"/>
-      <c r="CW42" s="1"/>
-      <c r="CX42" s="1"/>
-      <c r="CY42" s="1"/>
-      <c r="CZ42" s="1"/>
-      <c r="DA42" s="1"/>
-      <c r="DB42" s="1"/>
-      <c r="DC42" s="1"/>
-      <c r="DD42" s="1"/>
-      <c r="DE42" s="1"/>
-      <c r="DF42" s="1"/>
-      <c r="DG42" s="1"/>
-      <c r="DH42" s="1"/>
-      <c r="DI42" s="1"/>
-      <c r="DJ42" s="1"/>
-      <c r="DK42" s="1"/>
-      <c r="DL42" s="1"/>
-      <c r="DM42" s="1"/>
-      <c r="DN42" s="1"/>
-      <c r="DO42" s="1"/>
-      <c r="DP42" s="1"/>
-      <c r="DQ42" s="1"/>
-      <c r="DR42" s="1"/>
-      <c r="DS42" s="1"/>
-      <c r="DT42" s="1"/>
-      <c r="DU42" s="1"/>
-      <c r="DV42" s="1"/>
-      <c r="DW42" s="1"/>
-      <c r="DX42" s="1"/>
-      <c r="DY42" s="1"/>
-      <c r="DZ42" s="1"/>
-      <c r="EA42" s="1"/>
-      <c r="EB42" s="1"/>
-      <c r="EC42" s="1"/>
-      <c r="ED42" s="1"/>
-      <c r="EE42" s="1"/>
-      <c r="EF42" s="1"/>
-      <c r="EG42" s="1"/>
-      <c r="EH42" s="1"/>
-      <c r="EI42" s="1"/>
-      <c r="EJ42" s="1"/>
-      <c r="EK42" s="1"/>
-      <c r="EL42" s="1"/>
-      <c r="EM42" s="1"/>
-      <c r="EN42" s="1"/>
-      <c r="EO42" s="1"/>
-      <c r="EP42" s="1"/>
-      <c r="EQ42" s="1"/>
-      <c r="ER42" s="1"/>
-      <c r="ES42" s="1"/>
-      <c r="ET42" s="1"/>
-      <c r="EU42" s="1"/>
-      <c r="EV42" s="1"/>
-      <c r="EW42" s="1"/>
-      <c r="EX42" s="1"/>
-      <c r="EY42" s="1"/>
-      <c r="EZ42" s="1"/>
-      <c r="FA42" s="1"/>
-      <c r="FB42" s="1"/>
-      <c r="FC42" s="1"/>
-      <c r="FD42" s="1"/>
-      <c r="FE42" s="1"/>
-      <c r="FF42" s="1"/>
-      <c r="FG42" s="1"/>
-      <c r="FH42" s="1"/>
-      <c r="FI42" s="1"/>
-      <c r="FJ42" s="1"/>
-      <c r="FK42" s="1"/>
-      <c r="FL42" s="1"/>
-      <c r="FM42" s="1"/>
-      <c r="FN42" s="1"/>
-      <c r="FO42" s="1"/>
-      <c r="FP42" s="1"/>
-      <c r="FQ42" s="1"/>
-      <c r="FR42" s="1"/>
-      <c r="FS42" s="1"/>
-      <c r="FT42" s="1"/>
-      <c r="FU42" s="1"/>
-      <c r="FV42" s="1"/>
-      <c r="FW42" s="1"/>
-      <c r="FX42" s="1"/>
-      <c r="FY42" s="1"/>
-      <c r="FZ42" s="1"/>
-      <c r="GA42" s="1"/>
-      <c r="GB42" s="1"/>
-      <c r="GC42" s="1"/>
-      <c r="GD42" s="1"/>
-      <c r="GE42" s="1"/>
-      <c r="GF42" s="1"/>
-      <c r="GG42" s="1"/>
-      <c r="GH42" s="1"/>
-      <c r="GI42" s="1"/>
-      <c r="GJ42" s="1"/>
-      <c r="GK42" s="1"/>
-      <c r="GL42" s="1"/>
-      <c r="GM42" s="1"/>
-      <c r="GN42" s="1"/>
-      <c r="GO42" s="1"/>
-      <c r="GP42" s="1"/>
-      <c r="GQ42" s="1"/>
-      <c r="GR42" s="1"/>
-      <c r="GS42" s="1"/>
-      <c r="GT42" s="1"/>
-      <c r="GU42" s="1"/>
-      <c r="GV42" s="1"/>
-      <c r="GW42" s="1"/>
-      <c r="GX42" s="1"/>
-      <c r="GY42" s="1"/>
-      <c r="GZ42" s="1"/>
-      <c r="HA42" s="1"/>
-      <c r="HB42" s="1"/>
-      <c r="HC42" s="1"/>
-      <c r="HD42" s="1"/>
-      <c r="HE42" s="1"/>
-      <c r="HF42" s="1"/>
-      <c r="HG42" s="1"/>
-      <c r="HH42" s="1"/>
-      <c r="HI42" s="1"/>
-      <c r="HJ42" s="1"/>
-      <c r="HK42" s="1"/>
-      <c r="HL42" s="1"/>
-      <c r="HM42" s="1"/>
-      <c r="HN42" s="1"/>
-      <c r="HO42" s="1"/>
-      <c r="HP42" s="1"/>
-      <c r="HQ42" s="1"/>
-      <c r="HR42" s="1"/>
-      <c r="HS42" s="1"/>
-      <c r="HT42" s="1"/>
-      <c r="HU42" s="1"/>
-      <c r="HV42" s="1"/>
-      <c r="HW42" s="1"/>
-      <c r="HX42" s="1"/>
-      <c r="HY42" s="1"/>
-      <c r="HZ42" s="1"/>
-      <c r="IA42" s="1"/>
-      <c r="IB42" s="1"/>
-      <c r="IC42" s="1"/>
-      <c r="ID42" s="1"/>
-      <c r="IE42" s="1"/>
-      <c r="IF42" s="1"/>
-      <c r="IG42" s="1"/>
-      <c r="IH42" s="1"/>
-      <c r="II42" s="1"/>
-      <c r="IJ42" s="1"/>
-      <c r="IK42" s="1"/>
-      <c r="IL42" s="1"/>
-      <c r="IM42" s="1"/>
-      <c r="IN42" s="1"/>
-      <c r="IO42" s="1"/>
-      <c r="IP42" s="1"/>
-      <c r="IQ42" s="1"/>
-      <c r="IR42" s="1"/>
-      <c r="IS42" s="1"/>
-      <c r="IT42" s="1"/>
-      <c r="IU42" s="1"/>
-      <c r="IV42" s="1"/>
-      <c r="IW42" s="1"/>
-      <c r="IX42" s="1"/>
-    </row>
-    <row r="43" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="11"/>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="12"/>
-      <c r="J43" s="12"/>
-      <c r="K43" s="12"/>
-      <c r="L43" s="12"/>
-      <c r="M43" s="12"/>
-      <c r="N43" s="12"/>
-      <c r="O43" s="13"/>
-      <c r="P43" s="14"/>
-      <c r="Q43" s="15"/>
-      <c r="R43" s="15"/>
-      <c r="S43" s="15"/>
-      <c r="T43" s="15"/>
-      <c r="U43" s="15"/>
-      <c r="V43" s="15"/>
-      <c r="W43" s="15"/>
-      <c r="X43" s="15"/>
-      <c r="Y43" s="15"/>
-      <c r="Z43" s="15"/>
-      <c r="AA43" s="15"/>
-      <c r="AB43" s="15"/>
-      <c r="AC43" s="15"/>
-      <c r="AD43" s="15"/>
-      <c r="AE43" s="15"/>
-      <c r="AF43" s="15"/>
-      <c r="AG43" s="15"/>
-      <c r="AH43" s="15"/>
-      <c r="AI43" s="15"/>
-      <c r="AJ43" s="15"/>
-      <c r="AK43" s="15"/>
-      <c r="AL43" s="15"/>
-      <c r="AM43" s="15"/>
-      <c r="AN43" s="15"/>
-      <c r="AO43" s="15"/>
-      <c r="AP43" s="15"/>
-      <c r="AQ43" s="15"/>
-      <c r="AR43" s="15"/>
-      <c r="AS43" s="16"/>
-      <c r="AT43" s="11"/>
-      <c r="AU43" s="12"/>
-      <c r="AV43" s="12"/>
-      <c r="AW43" s="12"/>
-      <c r="AX43" s="12"/>
-      <c r="AY43" s="12"/>
-      <c r="AZ43" s="12"/>
-      <c r="BA43" s="12"/>
-      <c r="BB43" s="12"/>
-      <c r="BC43" s="12"/>
-      <c r="BD43" s="12"/>
-      <c r="BE43" s="12"/>
-      <c r="BF43" s="12"/>
-      <c r="BG43" s="12"/>
-      <c r="BH43" s="12"/>
-      <c r="BI43" s="13"/>
-      <c r="BJ43" s="1"/>
-      <c r="BK43" s="1"/>
-      <c r="BL43" s="1"/>
-      <c r="BM43" s="1"/>
-      <c r="BN43" s="1"/>
-      <c r="BO43" s="1"/>
-      <c r="BP43" s="1"/>
-      <c r="BQ43" s="1"/>
-      <c r="BR43" s="1"/>
-      <c r="BS43" s="1"/>
-      <c r="BT43" s="1"/>
-      <c r="BU43" s="1"/>
-      <c r="BV43" s="1"/>
-      <c r="BW43" s="1"/>
-      <c r="BX43" s="1"/>
-      <c r="BY43" s="1"/>
-      <c r="BZ43" s="1"/>
-      <c r="CA43" s="1"/>
-      <c r="CB43" s="1"/>
-      <c r="CC43" s="1"/>
-      <c r="CD43" s="1"/>
-      <c r="CE43" s="1"/>
-      <c r="CF43" s="1"/>
-      <c r="CG43" s="1"/>
-      <c r="CH43" s="1"/>
-      <c r="CI43" s="1"/>
-      <c r="CJ43" s="1"/>
-      <c r="CK43" s="1"/>
-      <c r="CL43" s="1"/>
-      <c r="CM43" s="1"/>
-      <c r="CN43" s="1"/>
-      <c r="CO43" s="1"/>
-      <c r="CP43" s="1"/>
-      <c r="CQ43" s="1"/>
-      <c r="CR43" s="1"/>
-      <c r="CS43" s="1"/>
-      <c r="CT43" s="1"/>
-      <c r="CU43" s="1"/>
-      <c r="CV43" s="1"/>
-      <c r="CW43" s="1"/>
-      <c r="CX43" s="1"/>
-      <c r="CY43" s="1"/>
-      <c r="CZ43" s="1"/>
-      <c r="DA43" s="1"/>
-      <c r="DB43" s="1"/>
-      <c r="DC43" s="1"/>
-      <c r="DD43" s="1"/>
-      <c r="DE43" s="1"/>
-      <c r="DF43" s="1"/>
-      <c r="DG43" s="1"/>
-      <c r="DH43" s="1"/>
-      <c r="DI43" s="1"/>
-      <c r="DJ43" s="1"/>
-      <c r="DK43" s="1"/>
-      <c r="DL43" s="1"/>
-      <c r="DM43" s="1"/>
-      <c r="DN43" s="1"/>
-      <c r="DO43" s="1"/>
-      <c r="DP43" s="1"/>
-      <c r="DQ43" s="1"/>
-      <c r="DR43" s="1"/>
-      <c r="DS43" s="1"/>
-      <c r="DT43" s="1"/>
-      <c r="DU43" s="1"/>
-      <c r="DV43" s="1"/>
-      <c r="DW43" s="1"/>
-      <c r="DX43" s="1"/>
-      <c r="DY43" s="1"/>
-      <c r="DZ43" s="1"/>
-      <c r="EA43" s="1"/>
-      <c r="EB43" s="1"/>
-      <c r="EC43" s="1"/>
-      <c r="ED43" s="1"/>
-      <c r="EE43" s="1"/>
-      <c r="EF43" s="1"/>
-      <c r="EG43" s="1"/>
-      <c r="EH43" s="1"/>
-      <c r="EI43" s="1"/>
-      <c r="EJ43" s="1"/>
-      <c r="EK43" s="1"/>
-      <c r="EL43" s="1"/>
-      <c r="EM43" s="1"/>
-      <c r="EN43" s="1"/>
-      <c r="EO43" s="1"/>
-      <c r="EP43" s="1"/>
-      <c r="EQ43" s="1"/>
-      <c r="ER43" s="1"/>
-      <c r="ES43" s="1"/>
-      <c r="ET43" s="1"/>
-      <c r="EU43" s="1"/>
-      <c r="EV43" s="1"/>
-      <c r="EW43" s="1"/>
-      <c r="EX43" s="1"/>
-      <c r="EY43" s="1"/>
-      <c r="EZ43" s="1"/>
-      <c r="FA43" s="1"/>
-      <c r="FB43" s="1"/>
-      <c r="FC43" s="1"/>
-      <c r="FD43" s="1"/>
-      <c r="FE43" s="1"/>
-      <c r="FF43" s="1"/>
-      <c r="FG43" s="1"/>
-      <c r="FH43" s="1"/>
-      <c r="FI43" s="1"/>
-      <c r="FJ43" s="1"/>
-      <c r="FK43" s="1"/>
-      <c r="FL43" s="1"/>
-      <c r="FM43" s="1"/>
-      <c r="FN43" s="1"/>
-      <c r="FO43" s="1"/>
-      <c r="FP43" s="1"/>
-      <c r="FQ43" s="1"/>
-      <c r="FR43" s="1"/>
-      <c r="FS43" s="1"/>
-      <c r="FT43" s="1"/>
-      <c r="FU43" s="1"/>
-      <c r="FV43" s="1"/>
-      <c r="FW43" s="1"/>
-      <c r="FX43" s="1"/>
-      <c r="FY43" s="1"/>
-      <c r="FZ43" s="1"/>
-      <c r="GA43" s="1"/>
-      <c r="GB43" s="1"/>
-      <c r="GC43" s="1"/>
-      <c r="GD43" s="1"/>
-      <c r="GE43" s="1"/>
-      <c r="GF43" s="1"/>
-      <c r="GG43" s="1"/>
-      <c r="GH43" s="1"/>
-      <c r="GI43" s="1"/>
-      <c r="GJ43" s="1"/>
-      <c r="GK43" s="1"/>
-      <c r="GL43" s="1"/>
-      <c r="GM43" s="1"/>
-      <c r="GN43" s="1"/>
-      <c r="GO43" s="1"/>
-      <c r="GP43" s="1"/>
-      <c r="GQ43" s="1"/>
-      <c r="GR43" s="1"/>
-      <c r="GS43" s="1"/>
-      <c r="GT43" s="1"/>
-      <c r="GU43" s="1"/>
-      <c r="GV43" s="1"/>
-      <c r="GW43" s="1"/>
-      <c r="GX43" s="1"/>
-      <c r="GY43" s="1"/>
-      <c r="GZ43" s="1"/>
-      <c r="HA43" s="1"/>
-      <c r="HB43" s="1"/>
-      <c r="HC43" s="1"/>
-      <c r="HD43" s="1"/>
-      <c r="HE43" s="1"/>
-      <c r="HF43" s="1"/>
-      <c r="HG43" s="1"/>
-      <c r="HH43" s="1"/>
-      <c r="HI43" s="1"/>
-      <c r="HJ43" s="1"/>
-      <c r="HK43" s="1"/>
-      <c r="HL43" s="1"/>
-      <c r="HM43" s="1"/>
-      <c r="HN43" s="1"/>
-      <c r="HO43" s="1"/>
-      <c r="HP43" s="1"/>
-      <c r="HQ43" s="1"/>
-      <c r="HR43" s="1"/>
-      <c r="HS43" s="1"/>
-      <c r="HT43" s="1"/>
-      <c r="HU43" s="1"/>
-      <c r="HV43" s="1"/>
-      <c r="HW43" s="1"/>
-      <c r="HX43" s="1"/>
-      <c r="HY43" s="1"/>
-      <c r="HZ43" s="1"/>
-      <c r="IA43" s="1"/>
-      <c r="IB43" s="1"/>
-      <c r="IC43" s="1"/>
-      <c r="ID43" s="1"/>
-      <c r="IE43" s="1"/>
-      <c r="IF43" s="1"/>
-      <c r="IG43" s="1"/>
-      <c r="IH43" s="1"/>
-      <c r="II43" s="1"/>
-      <c r="IJ43" s="1"/>
-      <c r="IK43" s="1"/>
-      <c r="IL43" s="1"/>
-      <c r="IM43" s="1"/>
-      <c r="IN43" s="1"/>
-      <c r="IO43" s="1"/>
-      <c r="IP43" s="1"/>
-      <c r="IQ43" s="1"/>
-      <c r="IR43" s="1"/>
-      <c r="IS43" s="1"/>
-      <c r="IT43" s="1"/>
-      <c r="IU43" s="1"/>
-      <c r="IV43" s="1"/>
-      <c r="IW43" s="1"/>
-      <c r="IX43" s="1"/>
-    </row>
-    <row r="44" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="11"/>
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="12"/>
-      <c r="I44" s="12"/>
-      <c r="J44" s="12"/>
-      <c r="K44" s="12"/>
-      <c r="L44" s="12"/>
-      <c r="M44" s="12"/>
-      <c r="N44" s="12"/>
-      <c r="O44" s="13"/>
-      <c r="P44" s="14"/>
-      <c r="Q44" s="15"/>
-      <c r="R44" s="15"/>
-      <c r="S44" s="15"/>
-      <c r="T44" s="15"/>
-      <c r="U44" s="15"/>
-      <c r="V44" s="15"/>
-      <c r="W44" s="15"/>
-      <c r="X44" s="15"/>
-      <c r="Y44" s="15"/>
-      <c r="Z44" s="15"/>
-      <c r="AA44" s="15"/>
-      <c r="AB44" s="15"/>
-      <c r="AC44" s="15"/>
-      <c r="AD44" s="15"/>
-      <c r="AE44" s="15"/>
-      <c r="AF44" s="15"/>
-      <c r="AG44" s="15"/>
-      <c r="AH44" s="15"/>
-      <c r="AI44" s="15"/>
-      <c r="AJ44" s="15"/>
-      <c r="AK44" s="15"/>
-      <c r="AL44" s="15"/>
-      <c r="AM44" s="15"/>
-      <c r="AN44" s="15"/>
-      <c r="AO44" s="15"/>
-      <c r="AP44" s="15"/>
-      <c r="AQ44" s="15"/>
-      <c r="AR44" s="15"/>
-      <c r="AS44" s="16"/>
-      <c r="AT44" s="11"/>
-      <c r="AU44" s="12"/>
-      <c r="AV44" s="12"/>
-      <c r="AW44" s="12"/>
-      <c r="AX44" s="12"/>
-      <c r="AY44" s="12"/>
-      <c r="AZ44" s="12"/>
-      <c r="BA44" s="12"/>
-      <c r="BB44" s="12"/>
-      <c r="BC44" s="12"/>
-      <c r="BD44" s="12"/>
-      <c r="BE44" s="12"/>
-      <c r="BF44" s="12"/>
-      <c r="BG44" s="12"/>
-      <c r="BH44" s="12"/>
-      <c r="BI44" s="13"/>
-      <c r="BJ44" s="1"/>
-      <c r="BK44" s="1"/>
-      <c r="BL44" s="1"/>
-      <c r="BM44" s="1"/>
-      <c r="BN44" s="1"/>
-      <c r="BO44" s="1"/>
-      <c r="BP44" s="1"/>
-      <c r="BQ44" s="1"/>
-      <c r="BR44" s="1"/>
-      <c r="BS44" s="1"/>
-      <c r="BT44" s="1"/>
-      <c r="BU44" s="1"/>
-      <c r="BV44" s="1"/>
-      <c r="BW44" s="1"/>
-      <c r="BX44" s="1"/>
-      <c r="BY44" s="1"/>
-      <c r="BZ44" s="1"/>
-      <c r="CA44" s="1"/>
-      <c r="CB44" s="1"/>
-      <c r="CC44" s="1"/>
-      <c r="CD44" s="1"/>
-      <c r="CE44" s="1"/>
-      <c r="CF44" s="1"/>
-      <c r="CG44" s="1"/>
-      <c r="CH44" s="1"/>
-      <c r="CI44" s="1"/>
-      <c r="CJ44" s="1"/>
-      <c r="CK44" s="1"/>
-      <c r="CL44" s="1"/>
-      <c r="CM44" s="1"/>
-      <c r="CN44" s="1"/>
-      <c r="CO44" s="1"/>
-      <c r="CP44" s="1"/>
-      <c r="CQ44" s="1"/>
-      <c r="CR44" s="1"/>
-      <c r="CS44" s="1"/>
-      <c r="CT44" s="1"/>
-      <c r="CU44" s="1"/>
-      <c r="CV44" s="1"/>
-      <c r="CW44" s="1"/>
-      <c r="CX44" s="1"/>
-      <c r="CY44" s="1"/>
-      <c r="CZ44" s="1"/>
-      <c r="DA44" s="1"/>
-      <c r="DB44" s="1"/>
-      <c r="DC44" s="1"/>
-      <c r="DD44" s="1"/>
-      <c r="DE44" s="1"/>
-      <c r="DF44" s="1"/>
-      <c r="DG44" s="1"/>
-      <c r="DH44" s="1"/>
-      <c r="DI44" s="1"/>
-      <c r="DJ44" s="1"/>
-      <c r="DK44" s="1"/>
-      <c r="DL44" s="1"/>
-      <c r="DM44" s="1"/>
-      <c r="DN44" s="1"/>
-      <c r="DO44" s="1"/>
-      <c r="DP44" s="1"/>
-      <c r="DQ44" s="1"/>
-      <c r="DR44" s="1"/>
-      <c r="DS44" s="1"/>
-      <c r="DT44" s="1"/>
-      <c r="DU44" s="1"/>
-      <c r="DV44" s="1"/>
-      <c r="DW44" s="1"/>
-      <c r="DX44" s="1"/>
-      <c r="DY44" s="1"/>
-      <c r="DZ44" s="1"/>
-      <c r="EA44" s="1"/>
-      <c r="EB44" s="1"/>
-      <c r="EC44" s="1"/>
-      <c r="ED44" s="1"/>
-      <c r="EE44" s="1"/>
-      <c r="EF44" s="1"/>
-      <c r="EG44" s="1"/>
-      <c r="EH44" s="1"/>
-      <c r="EI44" s="1"/>
-      <c r="EJ44" s="1"/>
-      <c r="EK44" s="1"/>
-      <c r="EL44" s="1"/>
-      <c r="EM44" s="1"/>
-      <c r="EN44" s="1"/>
-      <c r="EO44" s="1"/>
-      <c r="EP44" s="1"/>
-      <c r="EQ44" s="1"/>
-      <c r="ER44" s="1"/>
-      <c r="ES44" s="1"/>
-      <c r="ET44" s="1"/>
-      <c r="EU44" s="1"/>
-      <c r="EV44" s="1"/>
-      <c r="EW44" s="1"/>
-      <c r="EX44" s="1"/>
-      <c r="EY44" s="1"/>
-      <c r="EZ44" s="1"/>
-      <c r="FA44" s="1"/>
-      <c r="FB44" s="1"/>
-      <c r="FC44" s="1"/>
-      <c r="FD44" s="1"/>
-      <c r="FE44" s="1"/>
-      <c r="FF44" s="1"/>
-      <c r="FG44" s="1"/>
-      <c r="FH44" s="1"/>
-      <c r="FI44" s="1"/>
-      <c r="FJ44" s="1"/>
-      <c r="FK44" s="1"/>
-      <c r="FL44" s="1"/>
-      <c r="FM44" s="1"/>
-      <c r="FN44" s="1"/>
-      <c r="FO44" s="1"/>
-      <c r="FP44" s="1"/>
-      <c r="FQ44" s="1"/>
-      <c r="FR44" s="1"/>
-      <c r="FS44" s="1"/>
-      <c r="FT44" s="1"/>
-      <c r="FU44" s="1"/>
-      <c r="FV44" s="1"/>
-      <c r="FW44" s="1"/>
-      <c r="FX44" s="1"/>
-      <c r="FY44" s="1"/>
-      <c r="FZ44" s="1"/>
-      <c r="GA44" s="1"/>
-      <c r="GB44" s="1"/>
-      <c r="GC44" s="1"/>
-      <c r="GD44" s="1"/>
-      <c r="GE44" s="1"/>
-      <c r="GF44" s="1"/>
-      <c r="GG44" s="1"/>
-      <c r="GH44" s="1"/>
-      <c r="GI44" s="1"/>
-      <c r="GJ44" s="1"/>
-      <c r="GK44" s="1"/>
-      <c r="GL44" s="1"/>
-      <c r="GM44" s="1"/>
-      <c r="GN44" s="1"/>
-      <c r="GO44" s="1"/>
-      <c r="GP44" s="1"/>
-      <c r="GQ44" s="1"/>
-      <c r="GR44" s="1"/>
-      <c r="GS44" s="1"/>
-      <c r="GT44" s="1"/>
-      <c r="GU44" s="1"/>
-      <c r="GV44" s="1"/>
-      <c r="GW44" s="1"/>
-      <c r="GX44" s="1"/>
-      <c r="GY44" s="1"/>
-      <c r="GZ44" s="1"/>
-      <c r="HA44" s="1"/>
-      <c r="HB44" s="1"/>
-      <c r="HC44" s="1"/>
-      <c r="HD44" s="1"/>
-      <c r="HE44" s="1"/>
-      <c r="HF44" s="1"/>
-      <c r="HG44" s="1"/>
-      <c r="HH44" s="1"/>
-      <c r="HI44" s="1"/>
-      <c r="HJ44" s="1"/>
-      <c r="HK44" s="1"/>
-      <c r="HL44" s="1"/>
-      <c r="HM44" s="1"/>
-      <c r="HN44" s="1"/>
-      <c r="HO44" s="1"/>
-      <c r="HP44" s="1"/>
-      <c r="HQ44" s="1"/>
-      <c r="HR44" s="1"/>
-      <c r="HS44" s="1"/>
-      <c r="HT44" s="1"/>
-      <c r="HU44" s="1"/>
-      <c r="HV44" s="1"/>
-      <c r="HW44" s="1"/>
-      <c r="HX44" s="1"/>
-      <c r="HY44" s="1"/>
-      <c r="HZ44" s="1"/>
-      <c r="IA44" s="1"/>
-      <c r="IB44" s="1"/>
-      <c r="IC44" s="1"/>
-      <c r="ID44" s="1"/>
-      <c r="IE44" s="1"/>
-      <c r="IF44" s="1"/>
-      <c r="IG44" s="1"/>
-      <c r="IH44" s="1"/>
-      <c r="II44" s="1"/>
-      <c r="IJ44" s="1"/>
-      <c r="IK44" s="1"/>
-      <c r="IL44" s="1"/>
-      <c r="IM44" s="1"/>
-      <c r="IN44" s="1"/>
-      <c r="IO44" s="1"/>
-      <c r="IP44" s="1"/>
-      <c r="IQ44" s="1"/>
-      <c r="IR44" s="1"/>
-      <c r="IS44" s="1"/>
-      <c r="IT44" s="1"/>
-      <c r="IU44" s="1"/>
-      <c r="IV44" s="1"/>
-      <c r="IW44" s="1"/>
-      <c r="IX44" s="1"/>
-    </row>
-    <row r="45" spans="1:258" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="5"/>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
-      <c r="J45" s="5"/>
-      <c r="K45" s="5"/>
-      <c r="L45" s="5"/>
-      <c r="M45" s="5"/>
-      <c r="N45" s="5"/>
-      <c r="O45" s="5"/>
-      <c r="P45" s="5"/>
-      <c r="Q45" s="5"/>
-      <c r="R45" s="5"/>
-      <c r="S45" s="5"/>
-      <c r="T45" s="5"/>
-      <c r="U45" s="5"/>
-      <c r="V45" s="5"/>
-      <c r="W45" s="5"/>
-      <c r="X45" s="5"/>
-      <c r="Y45" s="5"/>
-      <c r="Z45" s="5"/>
-      <c r="AA45" s="5"/>
-      <c r="AB45" s="5"/>
-      <c r="AC45" s="5"/>
-      <c r="AD45" s="5"/>
-      <c r="AE45" s="5"/>
-      <c r="AF45" s="5"/>
-      <c r="AG45" s="5"/>
-      <c r="AH45" s="5"/>
-      <c r="AI45" s="5"/>
-      <c r="AJ45" s="5"/>
-      <c r="AK45" s="5"/>
-      <c r="AL45" s="5"/>
-      <c r="AM45" s="5"/>
-      <c r="AN45" s="5"/>
-      <c r="AO45" s="5"/>
-      <c r="AP45" s="5"/>
-      <c r="AQ45" s="5"/>
-      <c r="AR45" s="5"/>
-      <c r="AS45" s="5"/>
-      <c r="AT45" s="5"/>
-      <c r="AU45" s="5"/>
-      <c r="AV45" s="5"/>
-      <c r="AW45" s="5"/>
-      <c r="AX45" s="5"/>
-      <c r="AY45" s="5"/>
-      <c r="AZ45" s="5"/>
-      <c r="BA45" s="5"/>
-      <c r="BB45" s="5"/>
-      <c r="BC45" s="5"/>
-      <c r="BD45" s="5"/>
-      <c r="BE45" s="5"/>
-      <c r="BF45" s="5"/>
-      <c r="BG45" s="5"/>
-      <c r="BH45" s="5"/>
-      <c r="BI45" s="5"/>
-      <c r="BJ45" s="1"/>
-      <c r="BK45" s="1"/>
-      <c r="BL45" s="1"/>
-      <c r="BM45" s="1"/>
-      <c r="BN45" s="1"/>
-      <c r="BO45" s="1"/>
-      <c r="BP45" s="1"/>
-      <c r="BQ45" s="1"/>
-      <c r="BR45" s="1"/>
-      <c r="BS45" s="1"/>
-      <c r="BT45" s="1"/>
-      <c r="BU45" s="1"/>
-      <c r="BV45" s="1"/>
-      <c r="BW45" s="1"/>
-      <c r="BX45" s="1"/>
-      <c r="BY45" s="1"/>
-      <c r="BZ45" s="1"/>
-      <c r="CA45" s="1"/>
-      <c r="CB45" s="1"/>
-      <c r="CC45" s="1"/>
-      <c r="CD45" s="1"/>
-      <c r="CE45" s="1"/>
-      <c r="CF45" s="1"/>
-      <c r="CG45" s="1"/>
-      <c r="CH45" s="1"/>
-      <c r="CI45" s="1"/>
-      <c r="CJ45" s="1"/>
-      <c r="CK45" s="1"/>
-      <c r="CL45" s="1"/>
-      <c r="CM45" s="1"/>
-      <c r="CN45" s="1"/>
-      <c r="CO45" s="1"/>
-      <c r="CP45" s="1"/>
-      <c r="CQ45" s="1"/>
-      <c r="CR45" s="1"/>
-      <c r="CS45" s="1"/>
-      <c r="CT45" s="1"/>
-      <c r="CU45" s="1"/>
-      <c r="CV45" s="1"/>
-      <c r="CW45" s="1"/>
-      <c r="CX45" s="1"/>
-      <c r="CY45" s="1"/>
-      <c r="CZ45" s="1"/>
-      <c r="DA45" s="1"/>
-      <c r="DB45" s="1"/>
-      <c r="DC45" s="1"/>
-      <c r="DD45" s="1"/>
-      <c r="DE45" s="1"/>
-      <c r="DF45" s="1"/>
-      <c r="DG45" s="1"/>
-      <c r="DH45" s="1"/>
-      <c r="DI45" s="1"/>
-      <c r="DJ45" s="1"/>
-      <c r="DK45" s="1"/>
-      <c r="DL45" s="1"/>
-      <c r="DM45" s="1"/>
-      <c r="DN45" s="1"/>
-      <c r="DO45" s="1"/>
-      <c r="DP45" s="1"/>
-      <c r="DQ45" s="1"/>
-      <c r="DR45" s="1"/>
-      <c r="DS45" s="1"/>
-      <c r="DT45" s="1"/>
-      <c r="DU45" s="1"/>
-      <c r="DV45" s="1"/>
-      <c r="DW45" s="1"/>
-      <c r="DX45" s="1"/>
-      <c r="DY45" s="1"/>
-      <c r="DZ45" s="1"/>
-      <c r="EA45" s="1"/>
-      <c r="EB45" s="1"/>
-      <c r="EC45" s="1"/>
-      <c r="ED45" s="1"/>
-      <c r="EE45" s="1"/>
-      <c r="EF45" s="1"/>
-      <c r="EG45" s="1"/>
-      <c r="EH45" s="1"/>
-      <c r="EI45" s="1"/>
-      <c r="EJ45" s="1"/>
-      <c r="EK45" s="1"/>
-      <c r="EL45" s="1"/>
-      <c r="EM45" s="1"/>
-      <c r="EN45" s="1"/>
-      <c r="EO45" s="1"/>
-      <c r="EP45" s="1"/>
-      <c r="EQ45" s="1"/>
-      <c r="ER45" s="1"/>
-      <c r="ES45" s="1"/>
-      <c r="ET45" s="1"/>
-      <c r="EU45" s="1"/>
-      <c r="EV45" s="1"/>
-      <c r="EW45" s="1"/>
-      <c r="EX45" s="1"/>
-      <c r="EY45" s="1"/>
-      <c r="EZ45" s="1"/>
-      <c r="FA45" s="1"/>
-      <c r="FB45" s="1"/>
-      <c r="FC45" s="1"/>
-      <c r="FD45" s="1"/>
-      <c r="FE45" s="1"/>
-      <c r="FF45" s="1"/>
-      <c r="FG45" s="1"/>
-      <c r="FH45" s="1"/>
-      <c r="FI45" s="1"/>
-      <c r="FJ45" s="1"/>
-      <c r="FK45" s="1"/>
-      <c r="FL45" s="1"/>
-      <c r="FM45" s="1"/>
-      <c r="FN45" s="1"/>
-      <c r="FO45" s="1"/>
-      <c r="FP45" s="1"/>
-      <c r="FQ45" s="1"/>
-      <c r="FR45" s="1"/>
-      <c r="FS45" s="1"/>
-      <c r="FT45" s="1"/>
-      <c r="FU45" s="1"/>
-      <c r="FV45" s="1"/>
-      <c r="FW45" s="1"/>
-      <c r="FX45" s="1"/>
-      <c r="FY45" s="1"/>
-      <c r="FZ45" s="1"/>
-      <c r="GA45" s="1"/>
-      <c r="GB45" s="1"/>
-      <c r="GC45" s="1"/>
-      <c r="GD45" s="1"/>
-      <c r="GE45" s="1"/>
-      <c r="GF45" s="1"/>
-      <c r="GG45" s="1"/>
-      <c r="GH45" s="1"/>
-      <c r="GI45" s="1"/>
-      <c r="GJ45" s="1"/>
-      <c r="GK45" s="1"/>
-      <c r="GL45" s="1"/>
-      <c r="GM45" s="1"/>
-      <c r="GN45" s="1"/>
-      <c r="GO45" s="1"/>
-      <c r="GP45" s="1"/>
-      <c r="GQ45" s="1"/>
-      <c r="GR45" s="1"/>
-      <c r="GS45" s="1"/>
-      <c r="GT45" s="1"/>
-      <c r="GU45" s="1"/>
-      <c r="GV45" s="1"/>
-      <c r="GW45" s="1"/>
-      <c r="GX45" s="1"/>
-      <c r="GY45" s="1"/>
-      <c r="GZ45" s="1"/>
-      <c r="HA45" s="1"/>
-      <c r="HB45" s="1"/>
-      <c r="HC45" s="1"/>
-      <c r="HD45" s="1"/>
-      <c r="HE45" s="1"/>
-      <c r="HF45" s="1"/>
-      <c r="HG45" s="1"/>
-      <c r="HH45" s="1"/>
-      <c r="HI45" s="1"/>
-      <c r="HJ45" s="1"/>
-      <c r="HK45" s="1"/>
-      <c r="HL45" s="1"/>
-      <c r="HM45" s="1"/>
-      <c r="HN45" s="1"/>
-      <c r="HO45" s="1"/>
-      <c r="HP45" s="1"/>
-      <c r="HQ45" s="1"/>
-      <c r="HR45" s="1"/>
-      <c r="HS45" s="1"/>
-      <c r="HT45" s="1"/>
-      <c r="HU45" s="1"/>
-      <c r="HV45" s="1"/>
-      <c r="HW45" s="1"/>
-      <c r="HX45" s="1"/>
-      <c r="HY45" s="1"/>
-      <c r="HZ45" s="1"/>
-      <c r="IA45" s="1"/>
-      <c r="IB45" s="1"/>
-      <c r="IC45" s="1"/>
-      <c r="ID45" s="1"/>
-      <c r="IE45" s="1"/>
-      <c r="IF45" s="1"/>
-      <c r="IG45" s="1"/>
-      <c r="IH45" s="1"/>
-      <c r="II45" s="1"/>
-      <c r="IJ45" s="1"/>
-      <c r="IK45" s="1"/>
-      <c r="IL45" s="1"/>
-      <c r="IM45" s="1"/>
-      <c r="IN45" s="1"/>
-      <c r="IO45" s="1"/>
-      <c r="IP45" s="1"/>
-      <c r="IQ45" s="1"/>
-      <c r="IR45" s="1"/>
-      <c r="IS45" s="1"/>
-      <c r="IT45" s="1"/>
-      <c r="IU45" s="1"/>
-      <c r="IV45" s="1"/>
-      <c r="IW45" s="1"/>
-      <c r="IX45" s="1"/>
-    </row>
   </sheetData>
   <mergeCells count="42">
-    <mergeCell ref="R2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
-    <mergeCell ref="AE2:AP2"/>
-    <mergeCell ref="AQ2:AS2"/>
-    <mergeCell ref="AT2:AZ2"/>
+    <mergeCell ref="A13:O13"/>
+    <mergeCell ref="P13:AS13"/>
+    <mergeCell ref="AT13:BI13"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="D10:O10"/>
+    <mergeCell ref="P10:AD10"/>
+    <mergeCell ref="AE10:BI10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D11:O11"/>
+    <mergeCell ref="P11:AD11"/>
+    <mergeCell ref="AE11:BI11"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="D7:O7"/>
+    <mergeCell ref="P7:AD7"/>
+    <mergeCell ref="AE7:BI7"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:O9"/>
+    <mergeCell ref="P9:AD9"/>
+    <mergeCell ref="AE9:BI9"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="D8:BI8"/>
     <mergeCell ref="BA2:BC2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="G4:BI4"/>
@@ -14578,27 +12962,11 @@
     <mergeCell ref="AT1:AZ1"/>
     <mergeCell ref="BA1:BC1"/>
     <mergeCell ref="BD1:BI1"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="D7:O7"/>
-    <mergeCell ref="P7:AD7"/>
-    <mergeCell ref="AE7:BI7"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="D9:O9"/>
-    <mergeCell ref="P9:AD9"/>
-    <mergeCell ref="AE9:BI9"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="D8:BI8"/>
-    <mergeCell ref="A13:O13"/>
-    <mergeCell ref="P13:AS13"/>
-    <mergeCell ref="AT13:BI13"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="D10:O10"/>
-    <mergeCell ref="P10:AD10"/>
-    <mergeCell ref="AE10:BI10"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D11:O11"/>
-    <mergeCell ref="P11:AD11"/>
-    <mergeCell ref="AE11:BI11"/>
+    <mergeCell ref="R2:AA2"/>
+    <mergeCell ref="AB2:AD2"/>
+    <mergeCell ref="AE2:AP2"/>
+    <mergeCell ref="AQ2:AS2"/>
+    <mergeCell ref="AT2:AZ2"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="2">
@@ -14617,21 +12985,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100F5656D937027614D93C88AB71AE3D10C" ma:contentTypeVersion="2" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="b60c200d0ae5f270a77b0ce61d313f15">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="75fae816-41bf-471e-909f-5205fc9f8b57" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="893732230ae29545b6addaf499a489b1" ns2:_="">
     <xsd:import namespace="75fae816-41bf-471e-909f-5205fc9f8b57"/>
@@ -14763,24 +13116,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DACC66-2E68-4C7A-B35E-6653173BD294}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15C41A43-257B-41D4-8214-E3B2119882CE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7560E91F-1ABF-4BEF-A078-A8FA5AD9AA18}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -14796,4 +13147,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15C41A43-257B-41D4-8214-E3B2119882CE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DACC66-2E68-4C7A-B35E-6653173BD294}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>